--- a/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
+++ b/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Value Investing\Zegona Communications Plc - ZEG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC66050-8C08-43E1-99F4-DB653A640A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932CA8D0-BB85-4E38-8684-EA7D8FBED28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15600" activeTab="1" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
   </bookViews>
   <sheets>
     <sheet name="Dividendo + Preferentes" sheetId="1" r:id="rId1"/>
@@ -53,19 +53,10 @@
     <t>Deuda</t>
   </si>
   <si>
-    <t>Venta FibreCo Telefónica</t>
-  </si>
-  <si>
-    <t>Venta FibreCo MásOrange</t>
-  </si>
-  <si>
     <t>Equity</t>
   </si>
   <si>
     <t>Número de acciones inicial</t>
-  </si>
-  <si>
-    <t>Preferentes canceladas</t>
   </si>
   <si>
     <t>Número de acciones final</t>
@@ -96,9 +87,6 @@
       </rPr>
       <t>)</t>
     </r>
-  </si>
-  <si>
-    <t>Caja</t>
   </si>
   <si>
     <t>Pago Dividendo</t>
@@ -230,12 +218,24 @@
       <t>)</t>
     </r>
   </si>
+  <si>
+    <t>Preferentes canceladas (-)</t>
+  </si>
+  <si>
+    <t>Caja (-)</t>
+  </si>
+  <si>
+    <t>Venta FibreCo Telefónica (-)</t>
+  </si>
+  <si>
+    <t>Venta FibreCo MásOrange (-)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,13 +248,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -292,13 +285,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -677,7 +669,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <f>-47</f>
@@ -698,7 +690,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <f>-140</f>
@@ -719,7 +711,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <f>SUM(B2:B4)</f>
@@ -782,7 +774,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <f>260</f>
@@ -803,7 +795,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <f>538</f>
@@ -824,7 +816,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <f>1776</f>
@@ -845,7 +837,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <f>1405</f>
@@ -866,28 +858,28 @@
     </row>
     <row r="12" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="5">
+        <v>18</v>
+      </c>
+      <c r="B12">
         <f>B7-B8-B9-B10+B11</f>
         <v>2631</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12">
         <f t="shared" ref="C12:E12" si="4">C7-C8-C9-C10+C11</f>
         <v>2631</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12">
         <f t="shared" si="4"/>
         <v>2631</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12">
         <f t="shared" si="4"/>
         <v>2631</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B13">
         <f>B6-B12</f>
@@ -908,7 +900,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B14" s="2">
         <f>759209905/1000000</f>
@@ -929,35 +921,35 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B15" s="2">
-        <f>-523240603/1000000</f>
-        <v>-523.24060299999996</v>
+        <f>523240603/1000000</f>
+        <v>523.24060299999996</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" ref="C15:E15" si="7">-523240603/1000000</f>
-        <v>-523.24060299999996</v>
+        <f t="shared" ref="C15:E15" si="7">523240603/1000000</f>
+        <v>523.24060299999996</v>
       </c>
       <c r="D15" s="2">
         <f t="shared" si="7"/>
-        <v>-523.24060299999996</v>
+        <v>523.24060299999996</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="7"/>
-        <v>-523.24060299999996</v>
+        <v>523.24060299999996</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B16" s="2">
-        <f>B14+B15</f>
+        <f>B14-B15</f>
         <v>235.96930200000008</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" ref="C16:E16" si="8">C14+C15</f>
+        <f t="shared" ref="C16:E16" si="8">C14-C15</f>
         <v>235.96930200000008</v>
       </c>
       <c r="D16" s="2">
@@ -971,7 +963,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B17" s="1">
         <f>B13/B16</f>
@@ -992,7 +984,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <f>1.18</f>
@@ -1013,7 +1005,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B19" s="1">
         <f>B17/B18</f>
@@ -1034,7 +1026,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B20">
         <f>1.57</f>
@@ -1054,8 +1046,8 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>26</v>
+      <c r="A21" t="s">
+        <v>22</v>
       </c>
       <c r="B21" s="1">
         <f>B19+B20</f>
@@ -1076,7 +1068,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2">
         <f>B21*100</f>
@@ -1097,7 +1089,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B23">
         <v>595</v>
@@ -1114,7 +1106,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B24" s="3">
         <f>B22/B23-1</f>
@@ -1185,7 +1177,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <f>-47</f>
@@ -1206,7 +1198,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <f>-140</f>
@@ -1227,7 +1219,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <f>SUM(B2:B4)</f>
@@ -1290,7 +1282,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <f>260</f>
@@ -1311,7 +1303,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <f>538</f>
@@ -1332,7 +1324,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <f>1776</f>
@@ -1353,7 +1345,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <f>967</f>
@@ -1374,7 +1366,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <f>B7-B8-B9-B10+B11</f>
@@ -1395,7 +1387,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B13">
         <f>B6-B12</f>
@@ -1416,7 +1408,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B14" s="2">
         <f>759209905/1000000</f>
@@ -1437,35 +1429,35 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B15" s="2">
-        <f>-523240603/1000000</f>
-        <v>-523.24060299999996</v>
+        <f>523240603/1000000</f>
+        <v>523.24060299999996</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" ref="C15:E15" si="7">-523240603/1000000</f>
-        <v>-523.24060299999996</v>
+        <f t="shared" ref="C15:E15" si="7">523240603/1000000</f>
+        <v>523.24060299999996</v>
       </c>
       <c r="D15" s="2">
         <f t="shared" si="7"/>
-        <v>-523.24060299999996</v>
+        <v>523.24060299999996</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="7"/>
-        <v>-523.24060299999996</v>
+        <v>523.24060299999996</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B16" s="2">
-        <f>B14+B15</f>
+        <f>B14-B15</f>
         <v>235.96930200000008</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" ref="C16:E16" si="8">C14+C15</f>
+        <f t="shared" ref="C16:E16" si="8">C14-C15</f>
         <v>235.96930200000008</v>
       </c>
       <c r="D16" s="2">
@@ -1479,7 +1471,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B17" s="1">
         <f>B13/B16</f>
@@ -1500,7 +1492,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B18">
         <f>1.18</f>
@@ -1521,7 +1513,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B19" s="1">
         <f>B17/B18</f>
@@ -1542,7 +1534,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1559,7 +1551,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1">
         <f>B19+B20</f>
@@ -1580,7 +1572,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2">
         <f>B21*100</f>
@@ -1601,7 +1593,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B23">
         <v>595</v>
@@ -1618,7 +1610,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B24" s="3">
         <f>B22/B23-1</f>
@@ -1689,7 +1681,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <f>320</f>
@@ -1710,7 +1702,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <f>-47</f>
@@ -1731,7 +1723,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <f>-140</f>
@@ -1752,7 +1744,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <f>SUM(B2:B5)</f>
@@ -1815,7 +1807,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <f>260</f>
@@ -1836,7 +1828,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B10">
         <f>538</f>
@@ -1857,7 +1849,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B11">
         <f>1776</f>
@@ -1878,7 +1870,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B12">
         <f>967</f>
@@ -1899,7 +1891,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <f>B8-B9-B10-B11+B12</f>
@@ -1920,7 +1912,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B14">
         <f>B7-B13</f>
@@ -1941,7 +1933,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B15" s="2">
         <f>759209905/1000000</f>
@@ -1962,35 +1954,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B16" s="2">
-        <f>-523240603/1000000</f>
-        <v>-523.24060299999996</v>
+        <f>523240603/1000000</f>
+        <v>523.24060299999996</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" ref="C16:E16" si="7">-523240603/1000000</f>
-        <v>-523.24060299999996</v>
+        <f t="shared" ref="C16:E16" si="7">523240603/1000000</f>
+        <v>523.24060299999996</v>
       </c>
       <c r="D16" s="2">
         <f t="shared" si="7"/>
-        <v>-523.24060299999996</v>
+        <v>523.24060299999996</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="7"/>
-        <v>-523.24060299999996</v>
+        <v>523.24060299999996</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B17" s="2">
-        <f>B15+B16</f>
+        <f>B15-B16</f>
         <v>235.96930200000008</v>
       </c>
       <c r="C17" s="2">
-        <f t="shared" ref="C17:E17" si="8">C15+C16</f>
+        <f t="shared" ref="C17:E17" si="8">C15-C16</f>
         <v>235.96930200000008</v>
       </c>
       <c r="D17" s="2">
@@ -2004,7 +1996,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B18" s="1">
         <f>B14/B17</f>
@@ -2025,7 +2017,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B19">
         <f>1.18</f>
@@ -2046,7 +2038,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B20" s="1">
         <f>B18/B19</f>
@@ -2067,7 +2059,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2084,7 +2076,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B22" s="1">
         <f>B20+B21</f>
@@ -2105,7 +2097,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B23" s="2">
         <f>B22*100</f>
@@ -2126,7 +2118,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B24">
         <v>595</v>
@@ -2143,7 +2135,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B25" s="3">
         <f>B23/B24-1</f>
@@ -2218,7 +2210,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <f>-50</f>
@@ -2239,7 +2231,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <f>-50</f>
@@ -2260,7 +2252,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <f>SUM(B2:B4)</f>
@@ -2323,7 +2315,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <f>260</f>
@@ -2344,7 +2336,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <f>538</f>
@@ -2365,7 +2357,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B10">
         <f>1776</f>
@@ -2386,7 +2378,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <f>1405</f>
@@ -2407,7 +2399,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <f>B7-B8-B9-B10+B11</f>
@@ -2428,7 +2420,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B13">
         <f>B6-B12</f>
@@ -2449,7 +2441,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B14" s="2">
         <f>759209905/1000000</f>
@@ -2470,35 +2462,35 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B15" s="2">
-        <f>-523240603/1000000</f>
-        <v>-523.24060299999996</v>
+        <f>523240603/1000000</f>
+        <v>523.24060299999996</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" ref="C15:E15" si="6">-523240603/1000000</f>
-        <v>-523.24060299999996</v>
+        <f t="shared" ref="C15:E15" si="6">523240603/1000000</f>
+        <v>523.24060299999996</v>
       </c>
       <c r="D15" s="2">
         <f t="shared" si="6"/>
-        <v>-523.24060299999996</v>
+        <v>523.24060299999996</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="6"/>
-        <v>-523.24060299999996</v>
+        <v>523.24060299999996</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B16" s="2">
-        <f>B14+B15</f>
+        <f>B14-B15</f>
         <v>235.96930200000008</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" ref="C16:E16" si="7">C14+C15</f>
+        <f t="shared" ref="C16:E16" si="7">C14-C15</f>
         <v>235.96930200000008</v>
       </c>
       <c r="D16" s="2">
@@ -2511,8 +2503,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>10</v>
+      <c r="A17" t="s">
+        <v>7</v>
       </c>
       <c r="B17" s="1">
         <f>B13/B16</f>
@@ -2533,49 +2525,49 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B18">
-        <f>1.18</f>
-        <v>1.18</v>
+        <f>1.2</f>
+        <v>1.2</v>
       </c>
       <c r="C18">
-        <f t="shared" ref="C18:E18" si="9">1.18</f>
-        <v>1.18</v>
+        <f t="shared" ref="C18:E18" si="9">1.2</f>
+        <v>1.2</v>
       </c>
       <c r="D18">
         <f t="shared" si="9"/>
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="E18">
         <f t="shared" si="9"/>
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>25</v>
+      <c r="A19" t="s">
+        <v>21</v>
       </c>
       <c r="B19" s="1">
         <f>B17/B18</f>
-        <v>7.7897233989374532</v>
+        <v>7.6598946756218291</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" ref="C19:E19" si="10">C17/C18</f>
-        <v>12.099390562941576</v>
+        <v>11.897734053559217</v>
       </c>
       <c r="D19" s="1">
         <f t="shared" si="10"/>
-        <v>16.409057726945701</v>
+        <v>16.135573431496606</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="10"/>
-        <v>20.718724890949822</v>
+        <v>20.373412809433994</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>15</v>
+      <c r="A20" t="s">
+        <v>11</v>
       </c>
       <c r="B20">
         <f>1.57</f>
@@ -2596,49 +2588,49 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1">
         <f>B19+B20</f>
-        <v>9.3597233989374526</v>
+        <v>9.2298946756218285</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" ref="C21:E21" si="12">C19+C20</f>
-        <v>13.669390562941576</v>
+        <v>13.467734053559218</v>
       </c>
       <c r="D21" s="1">
         <f t="shared" si="12"/>
-        <v>17.979057726945701</v>
+        <v>17.705573431496607</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" si="12"/>
-        <v>22.288724890949823</v>
+        <v>21.943412809433994</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2">
         <f>B21*100</f>
-        <v>935.97233989374524</v>
+        <v>922.98946756218288</v>
       </c>
       <c r="C22" s="2">
         <f t="shared" ref="C22:E22" si="13">C21*100</f>
-        <v>1366.9390562941576</v>
+        <v>1346.7734053559218</v>
       </c>
       <c r="D22" s="2">
         <f t="shared" si="13"/>
-        <v>1797.90577269457</v>
+        <v>1770.5573431496607</v>
       </c>
       <c r="E22" s="2">
         <f t="shared" si="13"/>
-        <v>2228.8724890949825</v>
+        <v>2194.3412809433994</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B23">
         <v>595</v>
@@ -2655,23 +2647,23 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B24" s="3">
         <f>B22/B23-1</f>
-        <v>0.57306275612394164</v>
+        <v>0.55124280262551739</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" ref="C24:E24" si="14">C22/C23-1</f>
-        <v>1.2973765652002647</v>
+        <v>1.2634847148839023</v>
       </c>
       <c r="D24" s="3">
         <f t="shared" si="14"/>
-        <v>2.0216903742765884</v>
+        <v>1.9757266271422869</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" si="14"/>
-        <v>2.7460041833529116</v>
+        <v>2.6879685394006714</v>
       </c>
     </row>
   </sheetData>

--- a/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
+++ b/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Value Investing\Zegona Communications Plc - ZEG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932CA8D0-BB85-4E38-8684-EA7D8FBED28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8479BE20-CB32-46E0-AFF9-E1305212B8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15600" activeTab="1" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15600" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
   </bookViews>
   <sheets>
     <sheet name="Dividendo + Preferentes" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="28">
   <si>
     <t>EV/EBITDAaL</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>Venta FibreCo MásOrange (-)</t>
+  </si>
+  <si>
+    <t>Covenant financiero (2,25xEBITDAaL)</t>
   </si>
 </sst>
 </file>
@@ -625,1018 +628,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FC67936-1270-4D10-AE0F-8072EC119D20}">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>4</v>
-      </c>
-      <c r="C1">
-        <v>5</v>
-      </c>
-      <c r="D1">
-        <v>6</v>
-      </c>
-      <c r="E1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1236</v>
-      </c>
-      <c r="C2">
-        <v>1236</v>
-      </c>
-      <c r="D2">
-        <v>1236</v>
-      </c>
-      <c r="E2">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3">
-        <f>-47</f>
-        <v>-47</v>
-      </c>
-      <c r="C3">
-        <f t="shared" ref="C3:E3" si="0">-47</f>
-        <v>-47</v>
-      </c>
-      <c r="D3">
-        <f t="shared" si="0"/>
-        <v>-47</v>
-      </c>
-      <c r="E3">
-        <f t="shared" si="0"/>
-        <v>-47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4">
-        <f>-140</f>
-        <v>-140</v>
-      </c>
-      <c r="C4">
-        <f t="shared" ref="C4:E4" si="1">-140</f>
-        <v>-140</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="1"/>
-        <v>-140</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="1"/>
-        <v>-140</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5">
-        <f>SUM(B2:B4)</f>
-        <v>1049</v>
-      </c>
-      <c r="C5">
-        <f t="shared" ref="C5:E5" si="2">SUM(C2:C4)</f>
-        <v>1049</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="2"/>
-        <v>1049</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="2"/>
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <f>B5*B1</f>
-        <v>4196</v>
-      </c>
-      <c r="C6">
-        <f t="shared" ref="C6:E6" si="3">C5*C1</f>
-        <v>5245</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="3"/>
-        <v>6294</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="3"/>
-        <v>7343</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7">
-        <f>3800</f>
-        <v>3800</v>
-      </c>
-      <c r="C7">
-        <f>3800</f>
-        <v>3800</v>
-      </c>
-      <c r="D7">
-        <f>3800</f>
-        <v>3800</v>
-      </c>
-      <c r="E7">
-        <f>3800</f>
-        <v>3800</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8">
-        <f>260</f>
-        <v>260</v>
-      </c>
-      <c r="C8">
-        <f>260</f>
-        <v>260</v>
-      </c>
-      <c r="D8">
-        <f>260</f>
-        <v>260</v>
-      </c>
-      <c r="E8">
-        <f>260</f>
-        <v>260</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9">
-        <f>538</f>
-        <v>538</v>
-      </c>
-      <c r="C9">
-        <f>538</f>
-        <v>538</v>
-      </c>
-      <c r="D9">
-        <f>538</f>
-        <v>538</v>
-      </c>
-      <c r="E9">
-        <f>538</f>
-        <v>538</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-      <c r="C10">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-      <c r="D10">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-      <c r="E10">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <f>1405</f>
-        <v>1405</v>
-      </c>
-      <c r="C11">
-        <f>1405</f>
-        <v>1405</v>
-      </c>
-      <c r="D11">
-        <f>1405</f>
-        <v>1405</v>
-      </c>
-      <c r="E11">
-        <f>1405</f>
-        <v>1405</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12">
-        <f>B7-B8-B9-B10+B11</f>
-        <v>2631</v>
-      </c>
-      <c r="C12">
-        <f t="shared" ref="C12:E12" si="4">C7-C8-C9-C10+C11</f>
-        <v>2631</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="4"/>
-        <v>2631</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="4"/>
-        <v>2631</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <f>B6-B12</f>
-        <v>1565</v>
-      </c>
-      <c r="C13">
-        <f t="shared" ref="C13:E13" si="5">C6-C12</f>
-        <v>2614</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="5"/>
-        <v>3663</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="5"/>
-        <v>4712</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="2">
-        <f>759209905/1000000</f>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="C14" s="2">
-        <f t="shared" ref="C14:E14" si="6">759209905/1000000</f>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="D14" s="2">
-        <f t="shared" si="6"/>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="E14" s="2">
-        <f t="shared" si="6"/>
-        <v>759.20990500000005</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="2">
-        <f>523240603/1000000</f>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="C15" s="2">
-        <f t="shared" ref="C15:E15" si="7">523240603/1000000</f>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="D15" s="2">
-        <f t="shared" si="7"/>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="E15" s="2">
-        <f t="shared" si="7"/>
-        <v>523.24060299999996</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2">
-        <f>B14-B15</f>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="C16" s="2">
-        <f t="shared" ref="C16:E16" si="8">C14-C15</f>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="D16" s="2">
-        <f t="shared" si="8"/>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="E16" s="2">
-        <f t="shared" si="8"/>
-        <v>235.96930200000008</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="1">
-        <f>B13/B16</f>
-        <v>6.632218626472012</v>
-      </c>
-      <c r="C17" s="1">
-        <f t="shared" ref="C17:E17" si="9">C13/C16</f>
-        <v>11.077712133928332</v>
-      </c>
-      <c r="D17" s="1">
-        <f t="shared" si="9"/>
-        <v>15.523205641384653</v>
-      </c>
-      <c r="E17" s="1">
-        <f t="shared" si="9"/>
-        <v>19.968699148840972</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18">
-        <f>1.18</f>
-        <v>1.18</v>
-      </c>
-      <c r="C18">
-        <f t="shared" ref="C18:E18" si="10">1.18</f>
-        <v>1.18</v>
-      </c>
-      <c r="D18">
-        <f t="shared" si="10"/>
-        <v>1.18</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="10"/>
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="1">
-        <f>B17/B18</f>
-        <v>5.6205242597220444</v>
-      </c>
-      <c r="C19" s="1">
-        <f t="shared" ref="C19:E19" si="11">C17/C18</f>
-        <v>9.3878916389223157</v>
-      </c>
-      <c r="D19" s="1">
-        <f t="shared" si="11"/>
-        <v>13.155259018122587</v>
-      </c>
-      <c r="E19" s="1">
-        <f t="shared" si="11"/>
-        <v>16.922626397322858</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20">
-        <f>1.57</f>
-        <v>1.57</v>
-      </c>
-      <c r="C20">
-        <f t="shared" ref="C20:E20" si="12">1.57</f>
-        <v>1.57</v>
-      </c>
-      <c r="D20">
-        <f t="shared" si="12"/>
-        <v>1.57</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="12"/>
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="1">
-        <f>B19+B20</f>
-        <v>7.1905242597220447</v>
-      </c>
-      <c r="C21" s="1">
-        <f t="shared" ref="C21:E21" si="13">C19+C20</f>
-        <v>10.957891638922316</v>
-      </c>
-      <c r="D21" s="1">
-        <f t="shared" si="13"/>
-        <v>14.725259018122587</v>
-      </c>
-      <c r="E21" s="1">
-        <f t="shared" si="13"/>
-        <v>18.492626397322859</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2">
-        <f>B21*100</f>
-        <v>719.05242597220445</v>
-      </c>
-      <c r="C22" s="2">
-        <f t="shared" ref="C22:E22" si="14">C21*100</f>
-        <v>1095.7891638922315</v>
-      </c>
-      <c r="D22" s="2">
-        <f t="shared" si="14"/>
-        <v>1472.5259018122588</v>
-      </c>
-      <c r="E22" s="2">
-        <f t="shared" si="14"/>
-        <v>1849.2626397322858</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23">
-        <v>595</v>
-      </c>
-      <c r="C23">
-        <v>595</v>
-      </c>
-      <c r="D23">
-        <v>595</v>
-      </c>
-      <c r="E23">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="3">
-        <f>B22/B23-1</f>
-        <v>0.20849147222219244</v>
-      </c>
-      <c r="C24" s="3">
-        <f t="shared" ref="C24:E24" si="15">C22/C23-1</f>
-        <v>0.84166246032307823</v>
-      </c>
-      <c r="D24" s="3">
-        <f t="shared" si="15"/>
-        <v>1.4748334484239645</v>
-      </c>
-      <c r="E24" s="3">
-        <f t="shared" si="15"/>
-        <v>2.1080044365248503</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{740D45DC-A80B-4615-953A-F453DF4F4E26}">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>4</v>
-      </c>
-      <c r="C1">
-        <v>5</v>
-      </c>
-      <c r="D1">
-        <v>6</v>
-      </c>
-      <c r="E1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1236</v>
-      </c>
-      <c r="C2">
-        <v>1236</v>
-      </c>
-      <c r="D2">
-        <v>1236</v>
-      </c>
-      <c r="E2">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3">
-        <f>-47</f>
-        <v>-47</v>
-      </c>
-      <c r="C3">
-        <f t="shared" ref="C3:E3" si="0">-47</f>
-        <v>-47</v>
-      </c>
-      <c r="D3">
-        <f t="shared" si="0"/>
-        <v>-47</v>
-      </c>
-      <c r="E3">
-        <f t="shared" si="0"/>
-        <v>-47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4">
-        <f>-140</f>
-        <v>-140</v>
-      </c>
-      <c r="C4">
-        <f t="shared" ref="C4:E4" si="1">-140</f>
-        <v>-140</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="1"/>
-        <v>-140</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="1"/>
-        <v>-140</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5">
-        <f>SUM(B2:B4)</f>
-        <v>1049</v>
-      </c>
-      <c r="C5">
-        <f t="shared" ref="C5:E5" si="2">SUM(C2:C4)</f>
-        <v>1049</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="2"/>
-        <v>1049</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="2"/>
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <f>B5*B1</f>
-        <v>4196</v>
-      </c>
-      <c r="C6">
-        <f t="shared" ref="C6:E6" si="3">C5*C1</f>
-        <v>5245</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="3"/>
-        <v>6294</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="3"/>
-        <v>7343</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7">
-        <f>3800</f>
-        <v>3800</v>
-      </c>
-      <c r="C7">
-        <f>3800</f>
-        <v>3800</v>
-      </c>
-      <c r="D7">
-        <f>3800</f>
-        <v>3800</v>
-      </c>
-      <c r="E7">
-        <f>3800</f>
-        <v>3800</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8">
-        <f>260</f>
-        <v>260</v>
-      </c>
-      <c r="C8">
-        <f>260</f>
-        <v>260</v>
-      </c>
-      <c r="D8">
-        <f>260</f>
-        <v>260</v>
-      </c>
-      <c r="E8">
-        <f>260</f>
-        <v>260</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9">
-        <f>538</f>
-        <v>538</v>
-      </c>
-      <c r="C9">
-        <f>538</f>
-        <v>538</v>
-      </c>
-      <c r="D9">
-        <f>538</f>
-        <v>538</v>
-      </c>
-      <c r="E9">
-        <f>538</f>
-        <v>538</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-      <c r="C10">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-      <c r="D10">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-      <c r="E10">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <f>967</f>
-        <v>967</v>
-      </c>
-      <c r="C11">
-        <f>967</f>
-        <v>967</v>
-      </c>
-      <c r="D11">
-        <f>967</f>
-        <v>967</v>
-      </c>
-      <c r="E11">
-        <f>967</f>
-        <v>967</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12">
-        <f>B7-B8-B9-B10+B11</f>
-        <v>2193</v>
-      </c>
-      <c r="C12">
-        <f t="shared" ref="C12:E12" si="4">C7-C8-C9-C10+C11</f>
-        <v>2193</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="4"/>
-        <v>2193</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="4"/>
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <f>B6-B12</f>
-        <v>2003</v>
-      </c>
-      <c r="C13">
-        <f t="shared" ref="C13:E13" si="5">C6-C12</f>
-        <v>3052</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="5"/>
-        <v>4101</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="5"/>
-        <v>5150</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="2">
-        <f>759209905/1000000</f>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="C14" s="2">
-        <f t="shared" ref="C14:E14" si="6">759209905/1000000</f>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="D14" s="2">
-        <f t="shared" si="6"/>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="E14" s="2">
-        <f t="shared" si="6"/>
-        <v>759.20990500000005</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="2">
-        <f>523240603/1000000</f>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="C15" s="2">
-        <f t="shared" ref="C15:E15" si="7">523240603/1000000</f>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="D15" s="2">
-        <f t="shared" si="7"/>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="E15" s="2">
-        <f t="shared" si="7"/>
-        <v>523.24060299999996</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2">
-        <f>B14-B15</f>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="C16" s="2">
-        <f t="shared" ref="C16:E16" si="8">C14-C15</f>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="D16" s="2">
-        <f t="shared" si="8"/>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="E16" s="2">
-        <f t="shared" si="8"/>
-        <v>235.96930200000008</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="1">
-        <f>B13/B16</f>
-        <v>8.4883922740085875</v>
-      </c>
-      <c r="C17" s="1">
-        <f t="shared" ref="C17:E17" si="9">C13/C16</f>
-        <v>12.933885781464909</v>
-      </c>
-      <c r="D17" s="1">
-        <f t="shared" si="9"/>
-        <v>17.379379288921228</v>
-      </c>
-      <c r="E17" s="1">
-        <f t="shared" si="9"/>
-        <v>21.824872796377548</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18">
-        <f>1.18</f>
-        <v>1.18</v>
-      </c>
-      <c r="C18">
-        <f t="shared" ref="C18:E18" si="10">1.18</f>
-        <v>1.18</v>
-      </c>
-      <c r="D18">
-        <f t="shared" si="10"/>
-        <v>1.18</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="10"/>
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="1">
-        <f>B17/B18</f>
-        <v>7.1935527745835488</v>
-      </c>
-      <c r="C19" s="1">
-        <f t="shared" ref="C19:E19" si="11">C17/C18</f>
-        <v>10.960920153783821</v>
-      </c>
-      <c r="D19" s="1">
-        <f t="shared" si="11"/>
-        <v>14.728287532984092</v>
-      </c>
-      <c r="E19" s="1">
-        <f t="shared" si="11"/>
-        <v>18.495654912184364</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="1">
-        <f>B19+B20</f>
-        <v>7.1935527745835488</v>
-      </c>
-      <c r="C21" s="1">
-        <f t="shared" ref="C21:E21" si="12">C19+C20</f>
-        <v>10.960920153783821</v>
-      </c>
-      <c r="D21" s="1">
-        <f t="shared" si="12"/>
-        <v>14.728287532984092</v>
-      </c>
-      <c r="E21" s="1">
-        <f t="shared" si="12"/>
-        <v>18.495654912184364</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2">
-        <f>B21*100</f>
-        <v>719.35527745835486</v>
-      </c>
-      <c r="C22" s="2">
-        <f t="shared" ref="C22:E22" si="13">C21*100</f>
-        <v>1096.092015378382</v>
-      </c>
-      <c r="D22" s="2">
-        <f t="shared" si="13"/>
-        <v>1472.8287532984093</v>
-      </c>
-      <c r="E22" s="2">
-        <f t="shared" si="13"/>
-        <v>1849.5654912184364</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23">
-        <v>595</v>
-      </c>
-      <c r="C23">
-        <v>595</v>
-      </c>
-      <c r="D23">
-        <v>595</v>
-      </c>
-      <c r="E23">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="3">
-        <f>B22/B23-1</f>
-        <v>0.20900046631656277</v>
-      </c>
-      <c r="C24" s="3">
-        <f t="shared" ref="C24:E24" si="14">C22/C23-1</f>
-        <v>0.84217145441744878</v>
-      </c>
-      <c r="D24" s="3">
-        <f t="shared" si="14"/>
-        <v>1.4753424425183348</v>
-      </c>
-      <c r="E24" s="3">
-        <f t="shared" si="14"/>
-        <v>2.1085134306192206</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE8E3C78-B090-4354-8285-FB4151D5E6FA}">
   <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1681,6 +672,1060 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <f>-47</f>
+        <v>-47</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:E3" si="0">-47</f>
+        <v>-47</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="0"/>
+        <v>-47</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="0"/>
+        <v>-47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <f>-140</f>
+        <v>-140</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:E4" si="1">-140</f>
+        <v>-140</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
+        <v>-140</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>-140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <f>SUM(B2:B4)</f>
+        <v>1049</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ref="C5:E5" si="2">SUM(C2:C4)</f>
+        <v>1049</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="2"/>
+        <v>1049</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="2"/>
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <f>B5*B1</f>
+        <v>4196</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:E6" si="3">C5*C1</f>
+        <v>5245</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="3"/>
+        <v>6294</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="3"/>
+        <v>7343</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2">
+        <f>2.25*B5</f>
+        <v>2360.25</v>
+      </c>
+      <c r="C7" s="2">
+        <f t="shared" ref="C7:E7" si="4">2.25*C5</f>
+        <v>2360.25</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="4"/>
+        <v>2360.25</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="4"/>
+        <v>2360.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="C8">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="D8">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="E8">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="C9">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="D9">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="E9">
+        <f>260</f>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="C10">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="D10">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="E10">
+        <f>538</f>
+        <v>538</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
+        <f>2160</f>
+        <v>2160</v>
+      </c>
+      <c r="C11">
+        <f>2160</f>
+        <v>2160</v>
+      </c>
+      <c r="D11">
+        <f>2160</f>
+        <v>2160</v>
+      </c>
+      <c r="E11">
+        <f>2160</f>
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="C12">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="D12">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="E12">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <f>B8-B9-B10-B11+B12</f>
+        <v>2247</v>
+      </c>
+      <c r="C13">
+        <f t="shared" ref="C13:E13" si="5">C8-C9-C10-C11+C12</f>
+        <v>2247</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="5"/>
+        <v>2247</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="5"/>
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <f>B6-B13</f>
+        <v>1949</v>
+      </c>
+      <c r="C14">
+        <f t="shared" ref="C14:E14" si="6">C6-C13</f>
+        <v>2998</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="6"/>
+        <v>4047</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="6"/>
+        <v>5096</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="2">
+        <f>759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="C15" s="2">
+        <f t="shared" ref="C15:E15" si="7">759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="7"/>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" si="7"/>
+        <v>759.20990500000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="2">
+        <f>523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="C16" s="2">
+        <f t="shared" ref="C16:E16" si="8">523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="8"/>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="8"/>
+        <v>523.24060299999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2">
+        <f>B15-B16</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="C17" s="2">
+        <f t="shared" ref="C17:E17" si="9">C15-C16</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="9"/>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="E17" s="2">
+        <f t="shared" si="9"/>
+        <v>235.96930200000008</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="1">
+        <f>B14/B17</f>
+        <v>8.2595489475999688</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" ref="C18:E18" si="10">C14/C17</f>
+        <v>12.705042455056288</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="10"/>
+        <v>17.15053596251261</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="10"/>
+        <v>21.596029469968929</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19">
+        <f>1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="C19">
+        <f t="shared" ref="C19:E19" si="11">1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="11"/>
+        <v>1.18</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="11"/>
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="1">
+        <f>B18/B19</f>
+        <v>6.9996177522033634</v>
+      </c>
+      <c r="C20" s="1">
+        <f t="shared" ref="C20:E20" si="12">C18/C19</f>
+        <v>10.766985131403635</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="12"/>
+        <v>14.534352510603908</v>
+      </c>
+      <c r="E20" s="1">
+        <f t="shared" si="12"/>
+        <v>18.301719889804179</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <f>1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="C21">
+        <f t="shared" ref="C21:E21" si="13">1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="13"/>
+        <v>1.57</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="13"/>
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="1">
+        <f>B20+B21</f>
+        <v>8.5696177522033636</v>
+      </c>
+      <c r="C22" s="1">
+        <f t="shared" ref="C22:E22" si="14">C20+C21</f>
+        <v>12.336985131403635</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="14"/>
+        <v>16.104352510603906</v>
+      </c>
+      <c r="E22" s="1">
+        <f t="shared" si="14"/>
+        <v>19.871719889804179</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2">
+        <f>B22*100</f>
+        <v>856.96177522033634</v>
+      </c>
+      <c r="C23" s="2">
+        <f t="shared" ref="C23:E23" si="15">C22*100</f>
+        <v>1233.6985131403635</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="15"/>
+        <v>1610.4352510603906</v>
+      </c>
+      <c r="E23" s="2">
+        <f t="shared" si="15"/>
+        <v>1987.1719889804178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24">
+        <v>595</v>
+      </c>
+      <c r="C24">
+        <v>595</v>
+      </c>
+      <c r="D24">
+        <v>595</v>
+      </c>
+      <c r="E24">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="3">
+        <f>B23/B24-1</f>
+        <v>0.44027189112661569</v>
+      </c>
+      <c r="C25" s="3">
+        <f t="shared" ref="C25:E25" si="16">C23/C24-1</f>
+        <v>1.0734428792275015</v>
+      </c>
+      <c r="D25" s="3">
+        <f t="shared" si="16"/>
+        <v>1.7066138673283873</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="16"/>
+        <v>2.3397848554292735</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{740D45DC-A80B-4615-953A-F453DF4F4E26}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>4</v>
+      </c>
+      <c r="C1">
+        <v>5</v>
+      </c>
+      <c r="D1">
+        <v>6</v>
+      </c>
+      <c r="E1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1236</v>
+      </c>
+      <c r="C2">
+        <v>1236</v>
+      </c>
+      <c r="D2">
+        <v>1236</v>
+      </c>
+      <c r="E2">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <f>-47</f>
+        <v>-47</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:E3" si="0">-47</f>
+        <v>-47</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="0"/>
+        <v>-47</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="0"/>
+        <v>-47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <f>-140</f>
+        <v>-140</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:E4" si="1">-140</f>
+        <v>-140</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
+        <v>-140</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>-140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <f>SUM(B2:B4)</f>
+        <v>1049</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ref="C5:E5" si="2">SUM(C2:C4)</f>
+        <v>1049</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="2"/>
+        <v>1049</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="2"/>
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <f>B5*B1</f>
+        <v>4196</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:E6" si="3">C5*C1</f>
+        <v>5245</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="3"/>
+        <v>6294</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="3"/>
+        <v>7343</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2">
+        <f>2.25*B5</f>
+        <v>2360.25</v>
+      </c>
+      <c r="C7" s="2">
+        <f t="shared" ref="C7:E7" si="4">2.25*C5</f>
+        <v>2360.25</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="4"/>
+        <v>2360.25</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="4"/>
+        <v>2360.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="C8">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="D8">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="E8">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="C9">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="D9">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="E9">
+        <f>260</f>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="C10">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="D10">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="E10">
+        <f>538</f>
+        <v>538</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
+        <f>1776</f>
+        <v>1776</v>
+      </c>
+      <c r="C11">
+        <f>1776</f>
+        <v>1776</v>
+      </c>
+      <c r="D11">
+        <f>1776</f>
+        <v>1776</v>
+      </c>
+      <c r="E11">
+        <f>1776</f>
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <f>967</f>
+        <v>967</v>
+      </c>
+      <c r="C12">
+        <f>967</f>
+        <v>967</v>
+      </c>
+      <c r="D12">
+        <f>967</f>
+        <v>967</v>
+      </c>
+      <c r="E12">
+        <f>967</f>
+        <v>967</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <f>B8-B9-B10-B11+B12</f>
+        <v>2193</v>
+      </c>
+      <c r="C13">
+        <f t="shared" ref="C13:E13" si="5">C8-C9-C10-C11+C12</f>
+        <v>2193</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="5"/>
+        <v>2193</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="5"/>
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <f>B6-B13</f>
+        <v>2003</v>
+      </c>
+      <c r="C14">
+        <f t="shared" ref="C14:E14" si="6">C6-C13</f>
+        <v>3052</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="6"/>
+        <v>4101</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="6"/>
+        <v>5150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="2">
+        <f>759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="C15" s="2">
+        <f t="shared" ref="C15:E15" si="7">759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="7"/>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" si="7"/>
+        <v>759.20990500000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="2">
+        <f>523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="C16" s="2">
+        <f t="shared" ref="C16:E16" si="8">523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="8"/>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="8"/>
+        <v>523.24060299999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2">
+        <f>B15-B16</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="C17" s="2">
+        <f t="shared" ref="C17:E17" si="9">C15-C16</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="9"/>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="E17" s="2">
+        <f t="shared" si="9"/>
+        <v>235.96930200000008</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="1">
+        <f>B14/B17</f>
+        <v>8.4883922740085875</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" ref="C18:E18" si="10">C14/C17</f>
+        <v>12.933885781464909</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="10"/>
+        <v>17.379379288921228</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="10"/>
+        <v>21.824872796377548</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19">
+        <f>1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="C19">
+        <f t="shared" ref="C19:E19" si="11">1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="11"/>
+        <v>1.18</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="11"/>
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="1">
+        <f>B18/B19</f>
+        <v>7.1935527745835488</v>
+      </c>
+      <c r="C20" s="1">
+        <f t="shared" ref="C20:E20" si="12">C18/C19</f>
+        <v>10.960920153783821</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="12"/>
+        <v>14.728287532984092</v>
+      </c>
+      <c r="E20" s="1">
+        <f t="shared" si="12"/>
+        <v>18.495654912184364</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <f>B20+B21</f>
+        <v>7.1935527745835488</v>
+      </c>
+      <c r="C22" s="1">
+        <f t="shared" ref="C22:E22" si="13">C20+C21</f>
+        <v>10.960920153783821</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="13"/>
+        <v>14.728287532984092</v>
+      </c>
+      <c r="E22" s="1">
+        <f t="shared" si="13"/>
+        <v>18.495654912184364</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2">
+        <f>B22*100</f>
+        <v>719.35527745835486</v>
+      </c>
+      <c r="C23" s="2">
+        <f t="shared" ref="C23:E23" si="14">C22*100</f>
+        <v>1096.092015378382</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="14"/>
+        <v>1472.8287532984093</v>
+      </c>
+      <c r="E23" s="2">
+        <f t="shared" si="14"/>
+        <v>1849.5654912184364</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24">
+        <v>595</v>
+      </c>
+      <c r="C24">
+        <v>595</v>
+      </c>
+      <c r="D24">
+        <v>595</v>
+      </c>
+      <c r="E24">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="3">
+        <f>B23/B24-1</f>
+        <v>0.20900046631656277</v>
+      </c>
+      <c r="C25" s="3">
+        <f t="shared" ref="C25:E25" si="15">C23/C24-1</f>
+        <v>0.84217145441744878</v>
+      </c>
+      <c r="D25" s="3">
+        <f t="shared" si="15"/>
+        <v>1.4753424425183348</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="15"/>
+        <v>2.1085134306192206</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE8E3C78-B090-4354-8285-FB4151D5E6FA}">
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>4</v>
+      </c>
+      <c r="C1">
+        <v>5</v>
+      </c>
+      <c r="D1">
+        <v>6</v>
+      </c>
+      <c r="E1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1236</v>
+      </c>
+      <c r="C2">
+        <v>1236</v>
+      </c>
+      <c r="D2">
+        <v>1236</v>
+      </c>
+      <c r="E2">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3">
@@ -1785,372 +1830,393 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="2">
+        <f>2.25*B6</f>
+        <v>3080.25</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" ref="C8:E8" si="4">2.25*C6</f>
+        <v>3080.25</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="4"/>
+        <v>3080.25</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="4"/>
+        <v>3080.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <f>3800</f>
         <v>3800</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <f>3800</f>
         <v>3800</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <f>3800</f>
         <v>3800</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <f>3800</f>
         <v>3800</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>24</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <f>260</f>
         <v>260</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <f>260</f>
         <v>260</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <f>260</f>
         <v>260</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <f>260</f>
         <v>260</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>25</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <f>538</f>
         <v>538</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <f>538</f>
         <v>538</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <f>538</f>
         <v>538</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <f>538</f>
         <v>538</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>26</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <f>1776</f>
         <v>1776</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <f>1776</f>
         <v>1776</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <f>1776</f>
         <v>1776</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <f>1776</f>
         <v>1776</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <f>967</f>
         <v>967</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <f>967</f>
         <v>967</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <f>967</f>
         <v>967</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <f>967</f>
         <v>967</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13">
-        <f>B8-B9-B10-B11+B12</f>
-        <v>2193</v>
-      </c>
-      <c r="C13">
-        <f t="shared" ref="C13:E13" si="4">C8-C9-C10-C11+C12</f>
-        <v>2193</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="4"/>
-        <v>2193</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="4"/>
-        <v>2193</v>
-      </c>
-    </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B14">
-        <f>B7-B13</f>
-        <v>3283</v>
+        <f>B9-B10-B11-B12+B13</f>
+        <v>2193</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:E14" si="5">C7-C13</f>
-        <v>4652</v>
+        <f t="shared" ref="C14:E14" si="5">C9-C10-C11-C12+C13</f>
+        <v>2193</v>
       </c>
       <c r="D14">
         <f t="shared" si="5"/>
-        <v>6021</v>
+        <v>2193</v>
       </c>
       <c r="E14">
         <f t="shared" si="5"/>
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <f>B7-B14</f>
+        <v>3283</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:E15" si="6">C7-C14</f>
+        <v>4652</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="6"/>
+        <v>6021</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="6"/>
         <v>7390</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B16" s="2">
         <f>759209905/1000000</f>
         <v>759.20990500000005</v>
       </c>
-      <c r="C15" s="2">
-        <f t="shared" ref="C15:E15" si="6">759209905/1000000</f>
+      <c r="C16" s="2">
+        <f t="shared" ref="C16:E16" si="7">759209905/1000000</f>
         <v>759.20990500000005</v>
       </c>
-      <c r="D15" s="2">
-        <f t="shared" si="6"/>
+      <c r="D16" s="2">
+        <f t="shared" si="7"/>
         <v>759.20990500000005</v>
       </c>
-      <c r="E15" s="2">
-        <f t="shared" si="6"/>
+      <c r="E16" s="2">
+        <f t="shared" si="7"/>
         <v>759.20990500000005</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B17" s="2">
         <f>523240603/1000000</f>
         <v>523.24060299999996</v>
       </c>
-      <c r="C16" s="2">
-        <f t="shared" ref="C16:E16" si="7">523240603/1000000</f>
+      <c r="C17" s="2">
+        <f t="shared" ref="C17:E17" si="8">523240603/1000000</f>
         <v>523.24060299999996</v>
-      </c>
-      <c r="D16" s="2">
-        <f t="shared" si="7"/>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="E16" s="2">
-        <f t="shared" si="7"/>
-        <v>523.24060299999996</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="2">
-        <f>B15-B16</f>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="C17" s="2">
-        <f t="shared" ref="C17:E17" si="8">C15-C16</f>
-        <v>235.96930200000008</v>
       </c>
       <c r="D17" s="2">
         <f t="shared" si="8"/>
-        <v>235.96930200000008</v>
+        <v>523.24060299999996</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="8"/>
+        <v>523.24060299999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="2">
+        <f>B16-B17</f>
         <v>235.96930200000008</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="C18" s="2">
+        <f t="shared" ref="C18:E18" si="9">C16-C17</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="9"/>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="9"/>
+        <v>235.96930200000008</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="1">
-        <f>B14/B17</f>
+      <c r="B19" s="1">
+        <f>B15/B18</f>
         <v>13.912826677768445</v>
       </c>
-      <c r="C18" s="1">
-        <f t="shared" ref="C18:E18" si="9">C14/C17</f>
+      <c r="C19" s="1">
+        <f t="shared" ref="C19:E19" si="10">C15/C18</f>
         <v>19.714428786164728</v>
       </c>
-      <c r="D18" s="1">
-        <f t="shared" si="9"/>
+      <c r="D19" s="1">
+        <f t="shared" si="10"/>
         <v>25.516030894561013</v>
       </c>
-      <c r="E18" s="1">
-        <f t="shared" si="9"/>
+      <c r="E19" s="1">
+        <f t="shared" si="10"/>
         <v>31.317633002957297</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B19">
+      <c r="B20">
         <f>1.18</f>
         <v>1.18</v>
       </c>
-      <c r="C19">
-        <f t="shared" ref="C19:E19" si="10">1.18</f>
+      <c r="C20">
+        <f t="shared" ref="C20:E20" si="11">1.18</f>
         <v>1.18</v>
       </c>
-      <c r="D19">
-        <f t="shared" si="10"/>
+      <c r="D20">
+        <f t="shared" si="11"/>
         <v>1.18</v>
       </c>
-      <c r="E19">
-        <f t="shared" si="10"/>
+      <c r="E20">
+        <f t="shared" si="11"/>
         <v>1.18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="1">
-        <f>B18/B19</f>
-        <v>11.790531082854615</v>
-      </c>
-      <c r="C20" s="1">
-        <f t="shared" ref="C20:E20" si="11">C18/C19</f>
-        <v>16.707143039122652</v>
-      </c>
-      <c r="D20" s="1">
-        <f t="shared" si="11"/>
-        <v>21.623754995390691</v>
-      </c>
-      <c r="E20" s="1">
-        <f t="shared" si="11"/>
-        <v>26.540366951658729</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="1">
-        <f>B20+B21</f>
+        <v>8</v>
+      </c>
+      <c r="B21" s="1">
+        <f>B19/B20</f>
         <v>11.790531082854615</v>
       </c>
-      <c r="C22" s="1">
-        <f t="shared" ref="C22:E22" si="12">C20+C21</f>
+      <c r="C21" s="1">
+        <f t="shared" ref="C21:E21" si="12">C19/C20</f>
         <v>16.707143039122652</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D21" s="1">
         <f t="shared" si="12"/>
         <v>21.623754995390691</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E21" s="1">
         <f t="shared" si="12"/>
         <v>26.540366951658729</v>
       </c>
     </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="2">
-        <f>B22*100</f>
-        <v>1179.0531082854616</v>
-      </c>
-      <c r="C23" s="2">
-        <f t="shared" ref="C23:E23" si="13">C22*100</f>
-        <v>1670.7143039122652</v>
-      </c>
-      <c r="D23" s="2">
+        <v>19</v>
+      </c>
+      <c r="B23" s="1">
+        <f>B21+B22</f>
+        <v>11.790531082854615</v>
+      </c>
+      <c r="C23" s="1">
+        <f t="shared" ref="C23:E23" si="13">C21+C22</f>
+        <v>16.707143039122652</v>
+      </c>
+      <c r="D23" s="1">
         <f t="shared" si="13"/>
-        <v>2162.3754995390691</v>
-      </c>
-      <c r="E23" s="2">
+        <v>21.623754995390691</v>
+      </c>
+      <c r="E23" s="1">
         <f t="shared" si="13"/>
-        <v>2654.036695165873</v>
+        <v>26.540366951658729</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24">
-        <v>595</v>
-      </c>
-      <c r="C24">
-        <v>595</v>
-      </c>
-      <c r="D24">
-        <v>595</v>
-      </c>
-      <c r="E24">
-        <v>595</v>
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <f>B23*100</f>
+        <v>1179.0531082854616</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" ref="C24:E24" si="14">C23*100</f>
+        <v>1670.7143039122652</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="14"/>
+        <v>2162.3754995390691</v>
+      </c>
+      <c r="E24" s="2">
+        <f t="shared" si="14"/>
+        <v>2654.036695165873</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25">
+        <v>595</v>
+      </c>
+      <c r="C25">
+        <v>595</v>
+      </c>
+      <c r="D25">
+        <v>595</v>
+      </c>
+      <c r="E25">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="3">
-        <f>B23/B24-1</f>
+      <c r="B26" s="3">
+        <f>B24/B25-1</f>
         <v>0.98160186266464122</v>
       </c>
-      <c r="C25" s="3">
-        <f t="shared" ref="C25:E25" si="14">C23/C24-1</f>
+      <c r="C26" s="3">
+        <f t="shared" ref="C26:E26" si="15">C24/C25-1</f>
         <v>1.8079231998525467</v>
       </c>
-      <c r="D25" s="3">
-        <f t="shared" si="14"/>
+      <c r="D26" s="3">
+        <f t="shared" si="15"/>
         <v>2.6342445370404524</v>
       </c>
-      <c r="E25" s="3">
-        <f t="shared" si="14"/>
+      <c r="E26" s="3">
+        <f t="shared" si="15"/>
         <v>3.460565874228358</v>
       </c>
     </row>

--- a/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
+++ b/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Value Investing\Zegona Communications Plc - ZEG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8479BE20-CB32-46E0-AFF9-E1305212B8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3740F8-6823-45C8-AB06-9933FCBC982A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15600" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15600" activeTab="2" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
   </bookViews>
   <sheets>
     <sheet name="Dividendo + Preferentes" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="30">
   <si>
     <t>EV/EBITDAaL</t>
   </si>
@@ -232,6 +232,12 @@
   </si>
   <si>
     <t>Covenant financiero (2,25xEBITDAaL)</t>
+  </si>
+  <si>
+    <t>Reducción EBITDA por creación FibreCo Telefónica (-)</t>
+  </si>
+  <si>
+    <t>Reducción EBITDA por creación FibreCo MásOrange (-)</t>
   </si>
 </sst>
 </file>
@@ -631,7 +637,7 @@
   <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -672,44 +678,44 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B3">
-        <f>-47</f>
-        <v>-47</v>
+        <f>47</f>
+        <v>47</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:E3" si="0">-47</f>
-        <v>-47</v>
+        <f>47</f>
+        <v>47</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
-        <v>-47</v>
+        <f>47</f>
+        <v>47</v>
       </c>
       <c r="E3">
-        <f t="shared" si="0"/>
-        <v>-47</v>
+        <f>47</f>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B4">
-        <f>-140</f>
-        <v>-140</v>
+        <f>140</f>
+        <v>140</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:E4" si="1">-140</f>
-        <v>-140</v>
+        <f>140</f>
+        <v>140</v>
       </c>
       <c r="D4">
-        <f t="shared" si="1"/>
-        <v>-140</v>
+        <f>140</f>
+        <v>140</v>
       </c>
       <c r="E4">
-        <f t="shared" si="1"/>
-        <v>-140</v>
+        <f>140</f>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -717,19 +723,19 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <f>SUM(B2:B4)</f>
+        <f>B2-B3-B4</f>
         <v>1049</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:E5" si="2">SUM(C2:C4)</f>
+        <f t="shared" ref="C5:E5" si="0">C2-C3-C4</f>
         <v>1049</v>
       </c>
       <c r="D5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1049</v>
       </c>
       <c r="E5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1049</v>
       </c>
     </row>
@@ -742,15 +748,15 @@
         <v>4196</v>
       </c>
       <c r="C6">
-        <f t="shared" ref="C6:E6" si="3">C5*C1</f>
+        <f t="shared" ref="C6:E6" si="1">C5*C1</f>
         <v>5245</v>
       </c>
       <c r="D6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>6294</v>
       </c>
       <c r="E6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>7343</v>
       </c>
     </row>
@@ -763,15 +769,15 @@
         <v>2360.25</v>
       </c>
       <c r="C7" s="2">
-        <f t="shared" ref="C7:E7" si="4">2.25*C5</f>
+        <f t="shared" ref="C7:E7" si="2">2.25*C5</f>
         <v>2360.25</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2360.25</v>
       </c>
       <c r="E7" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2360.25</v>
       </c>
     </row>
@@ -889,15 +895,15 @@
         <v>2247</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:E13" si="5">C8-C9-C10-C11+C12</f>
+        <f t="shared" ref="C13:E13" si="3">C8-C9-C10-C11+C12</f>
         <v>2247</v>
       </c>
       <c r="D13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2247</v>
       </c>
       <c r="E13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2247</v>
       </c>
     </row>
@@ -910,15 +916,15 @@
         <v>1949</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:E14" si="6">C6-C13</f>
+        <f t="shared" ref="C14:E14" si="4">C6-C13</f>
         <v>2998</v>
       </c>
       <c r="D14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>4047</v>
       </c>
       <c r="E14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5096</v>
       </c>
     </row>
@@ -931,15 +937,15 @@
         <v>759.20990500000005</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" ref="C15:E15" si="7">759209905/1000000</f>
+        <f t="shared" ref="C15:E15" si="5">759209905/1000000</f>
         <v>759.20990500000005</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>759.20990500000005</v>
       </c>
       <c r="E15" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>759.20990500000005</v>
       </c>
     </row>
@@ -952,15 +958,15 @@
         <v>523.24060299999996</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" ref="C16:E16" si="8">523240603/1000000</f>
+        <f t="shared" ref="C16:E16" si="6">523240603/1000000</f>
         <v>523.24060299999996</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>523.24060299999996</v>
       </c>
       <c r="E16" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>523.24060299999996</v>
       </c>
     </row>
@@ -973,15 +979,15 @@
         <v>235.96930200000008</v>
       </c>
       <c r="C17" s="2">
-        <f t="shared" ref="C17:E17" si="9">C15-C16</f>
+        <f t="shared" ref="C17:E17" si="7">C15-C16</f>
         <v>235.96930200000008</v>
       </c>
       <c r="D17" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>235.96930200000008</v>
       </c>
       <c r="E17" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>235.96930200000008</v>
       </c>
     </row>
@@ -994,15 +1000,15 @@
         <v>8.2595489475999688</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" ref="C18:E18" si="10">C14/C17</f>
+        <f t="shared" ref="C18:E18" si="8">C14/C17</f>
         <v>12.705042455056288</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>17.15053596251261</v>
       </c>
       <c r="E18" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>21.596029469968929</v>
       </c>
     </row>
@@ -1015,15 +1021,15 @@
         <v>1.18</v>
       </c>
       <c r="C19">
-        <f t="shared" ref="C19:E19" si="11">1.18</f>
+        <f t="shared" ref="C19:E19" si="9">1.18</f>
         <v>1.18</v>
       </c>
       <c r="D19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.18</v>
       </c>
       <c r="E19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.18</v>
       </c>
     </row>
@@ -1036,15 +1042,15 @@
         <v>6.9996177522033634</v>
       </c>
       <c r="C20" s="1">
-        <f t="shared" ref="C20:E20" si="12">C18/C19</f>
+        <f t="shared" ref="C20:E20" si="10">C18/C19</f>
         <v>10.766985131403635</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>14.534352510603908</v>
       </c>
       <c r="E20" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>18.301719889804179</v>
       </c>
     </row>
@@ -1057,15 +1063,15 @@
         <v>1.57</v>
       </c>
       <c r="C21">
-        <f t="shared" ref="C21:E21" si="13">1.57</f>
+        <f t="shared" ref="C21:E21" si="11">1.57</f>
         <v>1.57</v>
       </c>
       <c r="D21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1.57</v>
       </c>
       <c r="E21">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>1.57</v>
       </c>
     </row>
@@ -1078,15 +1084,15 @@
         <v>8.5696177522033636</v>
       </c>
       <c r="C22" s="1">
-        <f t="shared" ref="C22:E22" si="14">C20+C21</f>
+        <f t="shared" ref="C22:E22" si="12">C20+C21</f>
         <v>12.336985131403635</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>16.104352510603906</v>
       </c>
       <c r="E22" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>19.871719889804179</v>
       </c>
     </row>
@@ -1099,15 +1105,15 @@
         <v>856.96177522033634</v>
       </c>
       <c r="C23" s="2">
-        <f t="shared" ref="C23:E23" si="15">C22*100</f>
+        <f t="shared" ref="C23:E23" si="13">C22*100</f>
         <v>1233.6985131403635</v>
       </c>
       <c r="D23" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1610.4352510603906</v>
       </c>
       <c r="E23" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1987.1719889804178</v>
       </c>
     </row>
@@ -1137,15 +1143,15 @@
         <v>0.44027189112661569</v>
       </c>
       <c r="C25" s="3">
-        <f t="shared" ref="C25:E25" si="16">C23/C24-1</f>
+        <f t="shared" ref="C25:E25" si="14">C23/C24-1</f>
         <v>1.0734428792275015</v>
       </c>
       <c r="D25" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>1.7066138673283873</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>2.3397848554292735</v>
       </c>
     </row>
@@ -1201,44 +1207,44 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B3">
-        <f>-47</f>
-        <v>-47</v>
+        <f>47</f>
+        <v>47</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:E3" si="0">-47</f>
-        <v>-47</v>
+        <f>47</f>
+        <v>47</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
-        <v>-47</v>
+        <f>47</f>
+        <v>47</v>
       </c>
       <c r="E3">
-        <f t="shared" si="0"/>
-        <v>-47</v>
+        <f>47</f>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B4">
-        <f>-140</f>
-        <v>-140</v>
+        <f>140</f>
+        <v>140</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:E4" si="1">-140</f>
-        <v>-140</v>
+        <f>140</f>
+        <v>140</v>
       </c>
       <c r="D4">
-        <f t="shared" si="1"/>
-        <v>-140</v>
+        <f>140</f>
+        <v>140</v>
       </c>
       <c r="E4">
-        <f t="shared" si="1"/>
-        <v>-140</v>
+        <f>140</f>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1246,19 +1252,19 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <f>SUM(B2:B4)</f>
+        <f>B2-B3-B4</f>
         <v>1049</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:E5" si="2">SUM(C2:C4)</f>
+        <f t="shared" ref="C5:E5" si="0">C2-C3-C4</f>
         <v>1049</v>
       </c>
       <c r="D5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1049</v>
       </c>
       <c r="E5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1049</v>
       </c>
     </row>
@@ -1271,15 +1277,15 @@
         <v>4196</v>
       </c>
       <c r="C6">
-        <f t="shared" ref="C6:E6" si="3">C5*C1</f>
+        <f t="shared" ref="C6:E6" si="1">C5*C1</f>
         <v>5245</v>
       </c>
       <c r="D6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>6294</v>
       </c>
       <c r="E6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>7343</v>
       </c>
     </row>
@@ -1292,15 +1298,15 @@
         <v>2360.25</v>
       </c>
       <c r="C7" s="2">
-        <f t="shared" ref="C7:E7" si="4">2.25*C5</f>
+        <f t="shared" ref="C7:E7" si="2">2.25*C5</f>
         <v>2360.25</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2360.25</v>
       </c>
       <c r="E7" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2360.25</v>
       </c>
     </row>
@@ -1418,15 +1424,15 @@
         <v>2193</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:E13" si="5">C8-C9-C10-C11+C12</f>
+        <f t="shared" ref="C13:E13" si="3">C8-C9-C10-C11+C12</f>
         <v>2193</v>
       </c>
       <c r="D13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2193</v>
       </c>
       <c r="E13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2193</v>
       </c>
     </row>
@@ -1439,15 +1445,15 @@
         <v>2003</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:E14" si="6">C6-C13</f>
+        <f t="shared" ref="C14:E14" si="4">C6-C13</f>
         <v>3052</v>
       </c>
       <c r="D14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>4101</v>
       </c>
       <c r="E14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5150</v>
       </c>
     </row>
@@ -1460,15 +1466,15 @@
         <v>759.20990500000005</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" ref="C15:E15" si="7">759209905/1000000</f>
+        <f t="shared" ref="C15:E15" si="5">759209905/1000000</f>
         <v>759.20990500000005</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>759.20990500000005</v>
       </c>
       <c r="E15" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>759.20990500000005</v>
       </c>
     </row>
@@ -1481,15 +1487,15 @@
         <v>523.24060299999996</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" ref="C16:E16" si="8">523240603/1000000</f>
+        <f t="shared" ref="C16:E16" si="6">523240603/1000000</f>
         <v>523.24060299999996</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>523.24060299999996</v>
       </c>
       <c r="E16" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>523.24060299999996</v>
       </c>
     </row>
@@ -1502,15 +1508,15 @@
         <v>235.96930200000008</v>
       </c>
       <c r="C17" s="2">
-        <f t="shared" ref="C17:E17" si="9">C15-C16</f>
+        <f t="shared" ref="C17:E17" si="7">C15-C16</f>
         <v>235.96930200000008</v>
       </c>
       <c r="D17" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>235.96930200000008</v>
       </c>
       <c r="E17" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>235.96930200000008</v>
       </c>
     </row>
@@ -1523,15 +1529,15 @@
         <v>8.4883922740085875</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" ref="C18:E18" si="10">C14/C17</f>
+        <f t="shared" ref="C18:E18" si="8">C14/C17</f>
         <v>12.933885781464909</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>17.379379288921228</v>
       </c>
       <c r="E18" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>21.824872796377548</v>
       </c>
     </row>
@@ -1544,15 +1550,15 @@
         <v>1.18</v>
       </c>
       <c r="C19">
-        <f t="shared" ref="C19:E19" si="11">1.18</f>
+        <f t="shared" ref="C19:E19" si="9">1.18</f>
         <v>1.18</v>
       </c>
       <c r="D19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.18</v>
       </c>
       <c r="E19">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.18</v>
       </c>
     </row>
@@ -1565,15 +1571,15 @@
         <v>7.1935527745835488</v>
       </c>
       <c r="C20" s="1">
-        <f t="shared" ref="C20:E20" si="12">C18/C19</f>
+        <f t="shared" ref="C20:E20" si="10">C18/C19</f>
         <v>10.960920153783821</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>14.728287532984092</v>
       </c>
       <c r="E20" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>18.495654912184364</v>
       </c>
     </row>
@@ -1603,15 +1609,15 @@
         <v>7.1935527745835488</v>
       </c>
       <c r="C22" s="1">
-        <f t="shared" ref="C22:E22" si="13">C20+C21</f>
+        <f t="shared" ref="C22:E22" si="11">C20+C21</f>
         <v>10.960920153783821</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>14.728287532984092</v>
       </c>
       <c r="E22" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>18.495654912184364</v>
       </c>
     </row>
@@ -1624,15 +1630,15 @@
         <v>719.35527745835486</v>
       </c>
       <c r="C23" s="2">
-        <f t="shared" ref="C23:E23" si="14">C22*100</f>
+        <f t="shared" ref="C23:E23" si="12">C22*100</f>
         <v>1096.092015378382</v>
       </c>
       <c r="D23" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1472.8287532984093</v>
       </c>
       <c r="E23" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>1849.5654912184364</v>
       </c>
     </row>
@@ -1662,15 +1668,15 @@
         <v>0.20900046631656277</v>
       </c>
       <c r="C25" s="3">
-        <f t="shared" ref="C25:E25" si="15">C23/C24-1</f>
+        <f t="shared" ref="C25:E25" si="13">C23/C24-1</f>
         <v>0.84217145441744878</v>
       </c>
       <c r="D25" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1.4753424425183348</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>2.1085134306192206</v>
       </c>
     </row>
@@ -1747,44 +1753,44 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <f>-47</f>
-        <v>-47</v>
+        <f>47</f>
+        <v>47</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:E4" si="0">-47</f>
-        <v>-47</v>
+        <f>47</f>
+        <v>47</v>
       </c>
       <c r="D4">
-        <f t="shared" si="0"/>
-        <v>-47</v>
+        <f>47</f>
+        <v>47</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
-        <v>-47</v>
+        <f>47</f>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B5">
-        <f>-140</f>
-        <v>-140</v>
+        <f>140</f>
+        <v>140</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:E5" si="1">-140</f>
-        <v>-140</v>
+        <f>140</f>
+        <v>140</v>
       </c>
       <c r="D5">
-        <f t="shared" si="1"/>
-        <v>-140</v>
+        <f>140</f>
+        <v>140</v>
       </c>
       <c r="E5">
-        <f t="shared" si="1"/>
-        <v>-140</v>
+        <f>140</f>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1792,19 +1798,19 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <f>SUM(B2:B5)</f>
+        <f>B2+B3-B4-B5</f>
         <v>1369</v>
       </c>
       <c r="C6">
-        <f t="shared" ref="C6:E6" si="2">SUM(C2:C5)</f>
+        <f t="shared" ref="C6:E6" si="0">C2+C3-C4-C5</f>
         <v>1369</v>
       </c>
       <c r="D6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1369</v>
       </c>
       <c r="E6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1369</v>
       </c>
     </row>
@@ -1817,15 +1823,15 @@
         <v>5476</v>
       </c>
       <c r="C7">
-        <f t="shared" ref="C7:E7" si="3">C6*C1</f>
+        <f t="shared" ref="C7:E7" si="1">C6*C1</f>
         <v>6845</v>
       </c>
       <c r="D7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>8214</v>
       </c>
       <c r="E7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>9583</v>
       </c>
     </row>
@@ -1838,15 +1844,15 @@
         <v>3080.25</v>
       </c>
       <c r="C8" s="2">
-        <f t="shared" ref="C8:E8" si="4">2.25*C6</f>
+        <f t="shared" ref="C8:E8" si="2">2.25*C6</f>
         <v>3080.25</v>
       </c>
       <c r="D8" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>3080.25</v>
       </c>
       <c r="E8" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>3080.25</v>
       </c>
     </row>
@@ -1964,15 +1970,15 @@
         <v>2193</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:E14" si="5">C9-C10-C11-C12+C13</f>
+        <f t="shared" ref="C14:E14" si="3">C9-C10-C11-C12+C13</f>
         <v>2193</v>
       </c>
       <c r="D14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2193</v>
       </c>
       <c r="E14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2193</v>
       </c>
     </row>
@@ -1985,15 +1991,15 @@
         <v>3283</v>
       </c>
       <c r="C15">
-        <f t="shared" ref="C15:E15" si="6">C7-C14</f>
+        <f t="shared" ref="C15:E15" si="4">C7-C14</f>
         <v>4652</v>
       </c>
       <c r="D15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>6021</v>
       </c>
       <c r="E15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>7390</v>
       </c>
     </row>
@@ -2006,15 +2012,15 @@
         <v>759.20990500000005</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" ref="C16:E16" si="7">759209905/1000000</f>
+        <f t="shared" ref="C16:E16" si="5">759209905/1000000</f>
         <v>759.20990500000005</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>759.20990500000005</v>
       </c>
       <c r="E16" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>759.20990500000005</v>
       </c>
     </row>
@@ -2027,15 +2033,15 @@
         <v>523.24060299999996</v>
       </c>
       <c r="C17" s="2">
-        <f t="shared" ref="C17:E17" si="8">523240603/1000000</f>
+        <f t="shared" ref="C17:E17" si="6">523240603/1000000</f>
         <v>523.24060299999996</v>
       </c>
       <c r="D17" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>523.24060299999996</v>
       </c>
       <c r="E17" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>523.24060299999996</v>
       </c>
     </row>
@@ -2048,15 +2054,15 @@
         <v>235.96930200000008</v>
       </c>
       <c r="C18" s="2">
-        <f t="shared" ref="C18:E18" si="9">C16-C17</f>
+        <f t="shared" ref="C18:E18" si="7">C16-C17</f>
         <v>235.96930200000008</v>
       </c>
       <c r="D18" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>235.96930200000008</v>
       </c>
       <c r="E18" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>235.96930200000008</v>
       </c>
     </row>
@@ -2069,15 +2075,15 @@
         <v>13.912826677768445</v>
       </c>
       <c r="C19" s="1">
-        <f t="shared" ref="C19:E19" si="10">C15/C18</f>
+        <f t="shared" ref="C19:E19" si="8">C15/C18</f>
         <v>19.714428786164728</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>25.516030894561013</v>
       </c>
       <c r="E19" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>31.317633002957297</v>
       </c>
     </row>
@@ -2090,15 +2096,15 @@
         <v>1.18</v>
       </c>
       <c r="C20">
-        <f t="shared" ref="C20:E20" si="11">1.18</f>
+        <f t="shared" ref="C20:E20" si="9">1.18</f>
         <v>1.18</v>
       </c>
       <c r="D20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.18</v>
       </c>
       <c r="E20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1.18</v>
       </c>
     </row>
@@ -2111,15 +2117,15 @@
         <v>11.790531082854615</v>
       </c>
       <c r="C21" s="1">
-        <f t="shared" ref="C21:E21" si="12">C19/C20</f>
+        <f t="shared" ref="C21:E21" si="10">C19/C20</f>
         <v>16.707143039122652</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>21.623754995390691</v>
       </c>
       <c r="E21" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>26.540366951658729</v>
       </c>
     </row>
@@ -2149,15 +2155,15 @@
         <v>11.790531082854615</v>
       </c>
       <c r="C23" s="1">
-        <f t="shared" ref="C23:E23" si="13">C21+C22</f>
+        <f t="shared" ref="C23:E23" si="11">C21+C22</f>
         <v>16.707143039122652</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>21.623754995390691</v>
       </c>
       <c r="E23" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>26.540366951658729</v>
       </c>
     </row>
@@ -2170,15 +2176,15 @@
         <v>1179.0531082854616</v>
       </c>
       <c r="C24" s="2">
-        <f t="shared" ref="C24:E24" si="14">C23*100</f>
+        <f t="shared" ref="C24:E24" si="12">C23*100</f>
         <v>1670.7143039122652</v>
       </c>
       <c r="D24" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>2162.3754995390691</v>
       </c>
       <c r="E24" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>2654.036695165873</v>
       </c>
     </row>
@@ -2208,15 +2214,15 @@
         <v>0.98160186266464122</v>
       </c>
       <c r="C26" s="3">
-        <f t="shared" ref="C26:E26" si="15">C24/C25-1</f>
+        <f t="shared" ref="C26:E26" si="13">C24/C25-1</f>
         <v>1.8079231998525467</v>
       </c>
       <c r="D26" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>2.6342445370404524</v>
       </c>
       <c r="E26" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>3.460565874228358</v>
       </c>
     </row>

--- a/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
+++ b/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Value Investing\Zegona Communications Plc - ZEG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3740F8-6823-45C8-AB06-9933FCBC982A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE8EB8A-6EFF-4E1B-B56A-B22F6AE9E84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15600" activeTab="2" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
   </bookViews>
   <sheets>
     <sheet name="Dividendo + Preferentes" sheetId="1" r:id="rId1"/>
@@ -1735,20 +1735,16 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <f>320</f>
-        <v>320</v>
+        <v>230</v>
       </c>
       <c r="C3">
-        <f>320</f>
-        <v>320</v>
+        <v>230</v>
       </c>
       <c r="D3">
-        <f>320</f>
-        <v>320</v>
+        <v>230</v>
       </c>
       <c r="E3">
-        <f>320</f>
-        <v>320</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1799,19 +1795,19 @@
       </c>
       <c r="B6">
         <f>B2+B3-B4-B5</f>
-        <v>1369</v>
+        <v>1279</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:E6" si="0">C2+C3-C4-C5</f>
-        <v>1369</v>
+        <v>1279</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>1369</v>
+        <v>1279</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>1369</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1820,19 +1816,19 @@
       </c>
       <c r="B7">
         <f>B6*B1</f>
-        <v>5476</v>
+        <v>5116</v>
       </c>
       <c r="C7">
         <f t="shared" ref="C7:E7" si="1">C6*C1</f>
-        <v>6845</v>
+        <v>6395</v>
       </c>
       <c r="D7">
         <f t="shared" si="1"/>
-        <v>8214</v>
+        <v>7674</v>
       </c>
       <c r="E7">
         <f t="shared" si="1"/>
-        <v>9583</v>
+        <v>8953</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1841,19 +1837,19 @@
       </c>
       <c r="B8" s="2">
         <f>2.25*B6</f>
-        <v>3080.25</v>
+        <v>2877.75</v>
       </c>
       <c r="C8" s="2">
         <f t="shared" ref="C8:E8" si="2">2.25*C6</f>
-        <v>3080.25</v>
+        <v>2877.75</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="2"/>
-        <v>3080.25</v>
+        <v>2877.75</v>
       </c>
       <c r="E8" s="2">
         <f t="shared" si="2"/>
-        <v>3080.25</v>
+        <v>2877.75</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1988,19 +1984,19 @@
       </c>
       <c r="B15">
         <f>B7-B14</f>
-        <v>3283</v>
+        <v>2923</v>
       </c>
       <c r="C15">
         <f t="shared" ref="C15:E15" si="4">C7-C14</f>
-        <v>4652</v>
+        <v>4202</v>
       </c>
       <c r="D15">
         <f t="shared" si="4"/>
-        <v>6021</v>
+        <v>5481</v>
       </c>
       <c r="E15">
         <f t="shared" si="4"/>
-        <v>7390</v>
+        <v>6760</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2072,19 +2068,19 @@
       </c>
       <c r="B19" s="1">
         <f>B15/B18</f>
-        <v>13.912826677768445</v>
+        <v>12.387204501710984</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" ref="C19:E19" si="8">C15/C18</f>
-        <v>19.714428786164728</v>
+        <v>17.807401066092904</v>
       </c>
       <c r="D19" s="1">
         <f t="shared" si="8"/>
-        <v>25.516030894561013</v>
+        <v>23.227597630474822</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="8"/>
-        <v>31.317633002957297</v>
+        <v>28.647794194856743</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2114,19 +2110,19 @@
       </c>
       <c r="B21" s="1">
         <f>B19/B20</f>
-        <v>11.790531082854615</v>
+        <v>10.497630933653378</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" ref="C21:E21" si="10">C19/C20</f>
-        <v>16.707143039122652</v>
+        <v>15.091017852621105</v>
       </c>
       <c r="D21" s="1">
         <f t="shared" si="10"/>
-        <v>21.623754995390691</v>
+        <v>19.684404771588834</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" si="10"/>
-        <v>26.540366951658729</v>
+        <v>24.277791690556562</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2152,19 +2148,19 @@
       </c>
       <c r="B23" s="1">
         <f>B21+B22</f>
-        <v>11.790531082854615</v>
+        <v>10.497630933653378</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" ref="C23:E23" si="11">C21+C22</f>
-        <v>16.707143039122652</v>
+        <v>15.091017852621105</v>
       </c>
       <c r="D23" s="1">
         <f t="shared" si="11"/>
-        <v>21.623754995390691</v>
+        <v>19.684404771588834</v>
       </c>
       <c r="E23" s="1">
         <f t="shared" si="11"/>
-        <v>26.540366951658729</v>
+        <v>24.277791690556562</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2173,19 +2169,19 @@
       </c>
       <c r="B24" s="2">
         <f>B23*100</f>
-        <v>1179.0531082854616</v>
+        <v>1049.7630933653377</v>
       </c>
       <c r="C24" s="2">
         <f t="shared" ref="C24:E24" si="12">C23*100</f>
-        <v>1670.7143039122652</v>
+        <v>1509.1017852621105</v>
       </c>
       <c r="D24" s="2">
         <f t="shared" si="12"/>
-        <v>2162.3754995390691</v>
+        <v>1968.4404771588834</v>
       </c>
       <c r="E24" s="2">
         <f t="shared" si="12"/>
-        <v>2654.036695165873</v>
+        <v>2427.779169055656</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2211,19 +2207,19 @@
       </c>
       <c r="B26" s="3">
         <f>B24/B25-1</f>
-        <v>0.98160186266464122</v>
+        <v>0.76430771994174407</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" ref="C26:E26" si="13">C24/C25-1</f>
-        <v>1.8079231998525467</v>
+        <v>1.5363055214489254</v>
       </c>
       <c r="D26" s="3">
         <f t="shared" si="13"/>
-        <v>2.6342445370404524</v>
+        <v>2.3083033229561063</v>
       </c>
       <c r="E26" s="3">
         <f t="shared" si="13"/>
-        <v>3.460565874228358</v>
+        <v>3.0803011244632872</v>
       </c>
     </row>
   </sheetData>

--- a/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
+++ b/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Value Investing\Zegona Communications Plc - ZEG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE8EB8A-6EFF-4E1B-B56A-B22F6AE9E84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35117D84-D4D4-4E58-B73B-A406250CA811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
   </bookViews>
@@ -1941,20 +1941,20 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <f>967</f>
-        <v>967</v>
+        <f>1405</f>
+        <v>1405</v>
       </c>
       <c r="C13">
-        <f>967</f>
-        <v>967</v>
+        <f>1405</f>
+        <v>1405</v>
       </c>
       <c r="D13">
-        <f>967</f>
-        <v>967</v>
+        <f>1405</f>
+        <v>1405</v>
       </c>
       <c r="E13">
-        <f>967</f>
-        <v>967</v>
+        <f>1405</f>
+        <v>1405</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1963,19 +1963,19 @@
       </c>
       <c r="B14">
         <f>B9-B10-B11-B12+B13</f>
-        <v>2193</v>
+        <v>2631</v>
       </c>
       <c r="C14">
         <f t="shared" ref="C14:E14" si="3">C9-C10-C11-C12+C13</f>
-        <v>2193</v>
+        <v>2631</v>
       </c>
       <c r="D14">
         <f t="shared" si="3"/>
-        <v>2193</v>
+        <v>2631</v>
       </c>
       <c r="E14">
         <f t="shared" si="3"/>
-        <v>2193</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1984,19 +1984,19 @@
       </c>
       <c r="B15">
         <f>B7-B14</f>
-        <v>2923</v>
+        <v>2485</v>
       </c>
       <c r="C15">
         <f t="shared" ref="C15:E15" si="4">C7-C14</f>
-        <v>4202</v>
+        <v>3764</v>
       </c>
       <c r="D15">
         <f t="shared" si="4"/>
-        <v>5481</v>
+        <v>5043</v>
       </c>
       <c r="E15">
         <f t="shared" si="4"/>
-        <v>6760</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2068,19 +2068,19 @@
       </c>
       <c r="B19" s="1">
         <f>B15/B18</f>
-        <v>12.387204501710984</v>
+        <v>10.531030854174409</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" ref="C19:E19" si="8">C15/C18</f>
-        <v>17.807401066092904</v>
+        <v>15.951227418556329</v>
       </c>
       <c r="D19" s="1">
         <f t="shared" si="8"/>
-        <v>23.227597630474822</v>
+        <v>21.371423982938246</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="8"/>
-        <v>28.647794194856743</v>
+        <v>26.791620547320168</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2110,19 +2110,19 @@
       </c>
       <c r="B21" s="1">
         <f>B19/B20</f>
-        <v>10.497630933653378</v>
+        <v>8.9246024187918724</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" ref="C21:E21" si="10">C19/C20</f>
-        <v>15.091017852621105</v>
+        <v>13.517989337759602</v>
       </c>
       <c r="D21" s="1">
         <f t="shared" si="10"/>
-        <v>19.684404771588834</v>
+        <v>18.111376256727329</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" si="10"/>
-        <v>24.277791690556562</v>
+        <v>22.70476317569506</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2130,16 +2130,20 @@
         <v>11</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <f>1.57</f>
+        <v>1.57</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <f t="shared" ref="C22:E22" si="11">1.57</f>
+        <v>1.57</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1.57</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1.57</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2148,19 +2152,19 @@
       </c>
       <c r="B23" s="1">
         <f>B21+B22</f>
-        <v>10.497630933653378</v>
+        <v>10.494602418791873</v>
       </c>
       <c r="C23" s="1">
-        <f t="shared" ref="C23:E23" si="11">C21+C22</f>
-        <v>15.091017852621105</v>
+        <f t="shared" ref="C23:E23" si="12">C21+C22</f>
+        <v>15.087989337759602</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="11"/>
-        <v>19.684404771588834</v>
+        <f t="shared" si="12"/>
+        <v>19.681376256727329</v>
       </c>
       <c r="E23" s="1">
-        <f t="shared" si="11"/>
-        <v>24.277791690556562</v>
+        <f t="shared" si="12"/>
+        <v>24.27476317569506</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2169,19 +2173,19 @@
       </c>
       <c r="B24" s="2">
         <f>B23*100</f>
-        <v>1049.7630933653377</v>
+        <v>1049.4602418791874</v>
       </c>
       <c r="C24" s="2">
-        <f t="shared" ref="C24:E24" si="12">C23*100</f>
-        <v>1509.1017852621105</v>
+        <f t="shared" ref="C24:E24" si="13">C23*100</f>
+        <v>1508.7989337759602</v>
       </c>
       <c r="D24" s="2">
-        <f t="shared" si="12"/>
-        <v>1968.4404771588834</v>
+        <f t="shared" si="13"/>
+        <v>1968.1376256727328</v>
       </c>
       <c r="E24" s="2">
-        <f t="shared" si="12"/>
-        <v>2427.779169055656</v>
+        <f t="shared" si="13"/>
+        <v>2427.4763175695061</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2207,19 +2211,19 @@
       </c>
       <c r="B26" s="3">
         <f>B24/B25-1</f>
-        <v>0.76430771994174407</v>
+        <v>0.76379872584737374</v>
       </c>
       <c r="C26" s="3">
-        <f t="shared" ref="C26:E26" si="13">C24/C25-1</f>
-        <v>1.5363055214489254</v>
+        <f t="shared" ref="C26:E26" si="14">C24/C25-1</f>
+        <v>1.5357965273545551</v>
       </c>
       <c r="D26" s="3">
-        <f t="shared" si="13"/>
-        <v>2.3083033229561063</v>
+        <f t="shared" si="14"/>
+        <v>2.307794328861736</v>
       </c>
       <c r="E26" s="3">
-        <f t="shared" si="13"/>
-        <v>3.0803011244632872</v>
+        <f t="shared" si="14"/>
+        <v>3.0797921303689177</v>
       </c>
     </row>
   </sheetData>

--- a/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
+++ b/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Value Investing\Zegona Communications Plc - ZEG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35117D84-D4D4-4E58-B73B-A406250CA811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1227265B-E907-428E-BB72-410B34208204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dividendo + Preferentes" sheetId="1" r:id="rId1"/>
-    <sheet name="Dividendo parcial + Preferentes" sheetId="2" r:id="rId2"/>
+    <sheet name="Dividendo parcial + Preferentes" sheetId="2" r:id="rId1"/>
+    <sheet name="Dividendo + Preferentes" sheetId="1" r:id="rId2"/>
     <sheet name="Reestructuracion (+Div+Pre)" sheetId="4" r:id="rId3"/>
     <sheet name="Gabriel Castro" sheetId="7" r:id="rId4"/>
   </sheets>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="41">
   <si>
     <t>EV/EBITDAaL</t>
   </si>
@@ -239,12 +239,117 @@
   <si>
     <t>Reducción EBITDA por creación FibreCo MásOrange (-)</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Equity </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>core business</t>
+    </r>
+  </si>
+  <si>
+    <t>EV/EBITDA</t>
+  </si>
+  <si>
+    <t>EBITDA</t>
+  </si>
+  <si>
+    <t>Equity participación Vodafone España</t>
+  </si>
+  <si>
+    <r>
+      <t>Negocio principal (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>core business)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FibreCo</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Telefónica</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FibreCo</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> MásOrange</t>
+    </r>
+  </si>
+  <si>
+    <t>Participación Vodafone España</t>
+  </si>
+  <si>
+    <t>Deuda (leverage recap)</t>
+  </si>
+  <si>
+    <t>Apalancamiento Deuda/EBITDA</t>
+  </si>
+  <si>
+    <t>Equity Total (SOTP)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,6 +378,15 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -294,12 +408,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -633,8 +765,906 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{740D45DC-A80B-4615-953A-F453DF4F4E26}">
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="49.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1236</v>
+      </c>
+      <c r="C3">
+        <v>1236</v>
+      </c>
+      <c r="D3">
+        <v>1236</v>
+      </c>
+      <c r="E3">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="C4">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="D4">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="E4">
+        <f>47</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="C5">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="D5">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="E5">
+        <f>140</f>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <f>B3-B4-B5</f>
+        <v>1049</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:E6" si="0">C3-C4-C5</f>
+        <v>1049</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>1049</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>B6*B2</f>
+        <v>4196</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:E7" si="1">C6*C2</f>
+        <v>5245</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>6294</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>7343</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="2">
+        <f>2.25*B6</f>
+        <v>2360.25</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" ref="C8:E8" si="2">2.25*C6</f>
+        <v>2360.25</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="2"/>
+        <v>2360.25</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="2"/>
+        <v>2360.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="C9">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="D9">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="E9">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="C10">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="D10">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="E10">
+        <f>260</f>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="C11">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="D11">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="E11">
+        <f>538</f>
+        <v>538</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12">
+        <f>1776</f>
+        <v>1776</v>
+      </c>
+      <c r="C12">
+        <f>1776</f>
+        <v>1776</v>
+      </c>
+      <c r="D12">
+        <f>1776</f>
+        <v>1776</v>
+      </c>
+      <c r="E12">
+        <f>1776</f>
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <f>967</f>
+        <v>967</v>
+      </c>
+      <c r="C13">
+        <f>967</f>
+        <v>967</v>
+      </c>
+      <c r="D13">
+        <f>967</f>
+        <v>967</v>
+      </c>
+      <c r="E13">
+        <f>967</f>
+        <v>967</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <f>B9-B10-B11-B12+B13</f>
+        <v>2193</v>
+      </c>
+      <c r="C14">
+        <f t="shared" ref="C14:E14" si="3">C9-C10-C11-C12+C13</f>
+        <v>2193</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="3"/>
+        <v>2193</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="3"/>
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <f>B7-B14</f>
+        <v>2003</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:E15" si="4">C7-C14</f>
+        <v>3052</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="4"/>
+        <v>4101</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="4"/>
+        <v>5150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="8">
+        <v>15</v>
+      </c>
+      <c r="C17" s="8">
+        <v>15</v>
+      </c>
+      <c r="D17" s="8">
+        <v>15</v>
+      </c>
+      <c r="E17" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="8">
+        <v>125</v>
+      </c>
+      <c r="C18" s="8">
+        <v>125</v>
+      </c>
+      <c r="D18" s="8">
+        <v>125</v>
+      </c>
+      <c r="E18" s="8">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="8">
+        <f>B17*B18</f>
+        <v>1875</v>
+      </c>
+      <c r="C19" s="8">
+        <f t="shared" ref="C19:E19" si="5">C17*C18</f>
+        <v>1875</v>
+      </c>
+      <c r="D19" s="8">
+        <f t="shared" si="5"/>
+        <v>1875</v>
+      </c>
+      <c r="E19" s="8">
+        <f t="shared" si="5"/>
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="8">
+        <f>2.5</f>
+        <v>2.5</v>
+      </c>
+      <c r="C20" s="8">
+        <f t="shared" ref="C20:E20" si="6">2.5</f>
+        <v>2.5</v>
+      </c>
+      <c r="D20" s="8">
+        <f t="shared" si="6"/>
+        <v>2.5</v>
+      </c>
+      <c r="E20" s="8">
+        <f t="shared" si="6"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="10">
+        <f>B18*B20</f>
+        <v>312.5</v>
+      </c>
+      <c r="C21" s="10">
+        <f t="shared" ref="C21:E21" si="7">C18*C20</f>
+        <v>312.5</v>
+      </c>
+      <c r="D21" s="10">
+        <f t="shared" si="7"/>
+        <v>312.5</v>
+      </c>
+      <c r="E21" s="10">
+        <f t="shared" si="7"/>
+        <v>312.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="10">
+        <f>B19-B21</f>
+        <v>1562.5</v>
+      </c>
+      <c r="C22" s="10">
+        <f t="shared" ref="C22:E22" si="8">C19-C21</f>
+        <v>1562.5</v>
+      </c>
+      <c r="D22" s="10">
+        <f t="shared" si="8"/>
+        <v>1562.5</v>
+      </c>
+      <c r="E22" s="10">
+        <f t="shared" si="8"/>
+        <v>1562.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="C23" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="D23" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="E23" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="2">
+        <f>B23*B22</f>
+        <v>156.25</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" ref="C24:E24" si="9">C23*C22</f>
+        <v>156.25</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="9"/>
+        <v>156.25</v>
+      </c>
+      <c r="E24" s="2">
+        <f t="shared" si="9"/>
+        <v>156.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="8">
+        <v>15</v>
+      </c>
+      <c r="C26" s="8">
+        <v>15</v>
+      </c>
+      <c r="D26" s="8">
+        <v>15</v>
+      </c>
+      <c r="E26" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="8">
+        <v>480</v>
+      </c>
+      <c r="C27" s="8">
+        <v>480</v>
+      </c>
+      <c r="D27" s="8">
+        <v>480</v>
+      </c>
+      <c r="E27" s="8">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="8">
+        <f>B26*B27</f>
+        <v>7200</v>
+      </c>
+      <c r="C28" s="8">
+        <f t="shared" ref="C28:E28" si="10">C26*C27</f>
+        <v>7200</v>
+      </c>
+      <c r="D28" s="8">
+        <f t="shared" si="10"/>
+        <v>7200</v>
+      </c>
+      <c r="E28" s="8">
+        <f t="shared" si="10"/>
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="C29" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="D29" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="E29" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="10">
+        <f>B27*B29</f>
+        <v>3360</v>
+      </c>
+      <c r="C30" s="10">
+        <f t="shared" ref="C30:E30" si="11">C27*C29</f>
+        <v>3360</v>
+      </c>
+      <c r="D30" s="10">
+        <f t="shared" si="11"/>
+        <v>3360</v>
+      </c>
+      <c r="E30" s="10">
+        <f t="shared" si="11"/>
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="10">
+        <f>B28-B30</f>
+        <v>3840</v>
+      </c>
+      <c r="C31" s="10">
+        <f t="shared" ref="C31:E31" si="12">C28-C30</f>
+        <v>3840</v>
+      </c>
+      <c r="D31" s="10">
+        <f t="shared" si="12"/>
+        <v>3840</v>
+      </c>
+      <c r="E31" s="10">
+        <f t="shared" si="12"/>
+        <v>3840</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="C32" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="D32" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="E32" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <f>B32*B31</f>
+        <v>384</v>
+      </c>
+      <c r="C33">
+        <f t="shared" ref="C33:E33" si="13">C32*C31</f>
+        <v>384</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="13"/>
+        <v>384</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="13"/>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="2">
+        <f>B15+B24+B33</f>
+        <v>2543.25</v>
+      </c>
+      <c r="C34" s="2">
+        <f>C15+C24+C33</f>
+        <v>3592.25</v>
+      </c>
+      <c r="D34" s="2">
+        <f>D15+D24+D33</f>
+        <v>4641.25</v>
+      </c>
+      <c r="E34" s="2">
+        <f>E15+E24+E33</f>
+        <v>5690.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="2">
+        <f>759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="C35" s="2">
+        <f t="shared" ref="C35:E35" si="14">759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="D35" s="2">
+        <f t="shared" si="14"/>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="E35" s="2">
+        <f t="shared" si="14"/>
+        <v>759.20990500000005</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="2">
+        <f>523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="C36" s="2">
+        <f t="shared" ref="C36:E36" si="15">523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="D36" s="2">
+        <f t="shared" si="15"/>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="E36" s="2">
+        <f t="shared" si="15"/>
+        <v>523.24060299999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="2">
+        <f>B35-B36</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="C37" s="2">
+        <f t="shared" ref="C37:E37" si="16">C35-C36</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" si="16"/>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="E37" s="2">
+        <f t="shared" si="16"/>
+        <v>235.96930200000008</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="1">
+        <f>B34/B37</f>
+        <v>10.777884997939262</v>
+      </c>
+      <c r="C38" s="1">
+        <f t="shared" ref="C38:E38" si="17">C34/C37</f>
+        <v>15.223378505395582</v>
+      </c>
+      <c r="D38" s="1">
+        <f t="shared" si="17"/>
+        <v>19.668872012851903</v>
+      </c>
+      <c r="E38" s="1">
+        <f t="shared" si="17"/>
+        <v>24.114365520308223</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39">
+        <f>1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="C39">
+        <f t="shared" ref="C39:E39" si="18">1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="18"/>
+        <v>1.18</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="18"/>
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="1">
+        <f>B38/B39</f>
+        <v>9.1338008457112387</v>
+      </c>
+      <c r="C40" s="1">
+        <f t="shared" ref="C40:E40" si="19">C38/C39</f>
+        <v>12.90116822491151</v>
+      </c>
+      <c r="D40" s="1">
+        <f t="shared" si="19"/>
+        <v>16.668535604111781</v>
+      </c>
+      <c r="E40" s="1">
+        <f t="shared" si="19"/>
+        <v>20.435902983312054</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="1">
+        <f>B40+B41</f>
+        <v>9.1338008457112387</v>
+      </c>
+      <c r="C42" s="1">
+        <f t="shared" ref="C42:E42" si="20">C40+C41</f>
+        <v>12.90116822491151</v>
+      </c>
+      <c r="D42" s="1">
+        <f t="shared" si="20"/>
+        <v>16.668535604111781</v>
+      </c>
+      <c r="E42" s="1">
+        <f t="shared" si="20"/>
+        <v>20.435902983312054</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" s="2">
+        <f>B42*100</f>
+        <v>913.38008457112392</v>
+      </c>
+      <c r="C43" s="2">
+        <f t="shared" ref="C43:E43" si="21">C42*100</f>
+        <v>1290.116822491151</v>
+      </c>
+      <c r="D43" s="2">
+        <f t="shared" si="21"/>
+        <v>1666.853560411178</v>
+      </c>
+      <c r="E43" s="2">
+        <f t="shared" si="21"/>
+        <v>2043.5902983312055</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44">
+        <v>595</v>
+      </c>
+      <c r="C44">
+        <v>595</v>
+      </c>
+      <c r="D44">
+        <v>595</v>
+      </c>
+      <c r="E44">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="3">
+        <f>B43/B44-1</f>
+        <v>0.53509257911113273</v>
+      </c>
+      <c r="C45" s="3">
+        <f t="shared" ref="C45:E45" si="22">C43/C44-1</f>
+        <v>1.1682635672120183</v>
+      </c>
+      <c r="D45" s="3">
+        <f t="shared" si="22"/>
+        <v>1.8014345553129041</v>
+      </c>
+      <c r="E45" s="3">
+        <f t="shared" si="22"/>
+        <v>2.4346055434137908</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A25:E25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FC67936-1270-4D10-AE0F-8072EC119D20}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.7109375" bestFit="1" customWidth="1"/>
@@ -643,1044 +1673,892 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
+      <c r="B2">
         <v>4</v>
       </c>
-      <c r="C1">
+      <c r="C2">
         <v>5</v>
       </c>
-      <c r="D1">
+      <c r="D2">
         <v>6</v>
       </c>
-      <c r="E1">
+      <c r="E2">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1236</v>
-      </c>
-      <c r="C2">
-        <v>1236</v>
-      </c>
-      <c r="D2">
-        <v>1236</v>
-      </c>
-      <c r="E2">
-        <v>1236</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1236</v>
+      </c>
+      <c r="C3">
+        <v>1236</v>
+      </c>
+      <c r="D3">
+        <v>1236</v>
+      </c>
+      <c r="E3">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>28</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <f>47</f>
         <v>47</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <f>47</f>
         <v>47</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <f>47</f>
         <v>47</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <f>47</f>
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>29</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <f>140</f>
         <v>140</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <f>140</f>
         <v>140</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <f>140</f>
         <v>140</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <f>140</f>
         <v>140</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B5">
-        <f>B2-B3-B4</f>
+      <c r="B6">
+        <f>B3-B4-B5</f>
         <v>1049</v>
       </c>
-      <c r="C5">
-        <f t="shared" ref="C5:E5" si="0">C2-C3-C4</f>
+      <c r="C6">
+        <f t="shared" ref="C6:E6" si="0">C3-C4-C5</f>
         <v>1049</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <f t="shared" si="0"/>
         <v>1049</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <f t="shared" si="0"/>
         <v>1049</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B6">
-        <f>B5*B1</f>
+      <c r="B7">
+        <f>B6*B2</f>
         <v>4196</v>
       </c>
-      <c r="C6">
-        <f t="shared" ref="C6:E6" si="1">C5*C1</f>
+      <c r="C7">
+        <f t="shared" ref="C7:E7" si="1">C6*C2</f>
         <v>5245</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <f t="shared" si="1"/>
         <v>6294</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <f t="shared" si="1"/>
         <v>7343</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="2">
-        <f>2.25*B5</f>
+      <c r="B8" s="2">
+        <f>2.25*B6</f>
         <v>2360.25</v>
       </c>
-      <c r="C7" s="2">
-        <f t="shared" ref="C7:E7" si="2">2.25*C5</f>
+      <c r="C8" s="2">
+        <f t="shared" ref="C8:E8" si="2">2.25*C6</f>
         <v>2360.25</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D8" s="2">
         <f t="shared" si="2"/>
         <v>2360.25</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E8" s="2">
         <f t="shared" si="2"/>
         <v>2360.25</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <f>3800</f>
         <v>3800</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <f>3800</f>
         <v>3800</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <f>3800</f>
         <v>3800</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <f>3800</f>
         <v>3800</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>24</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <f>260</f>
         <v>260</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <f>260</f>
         <v>260</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <f>260</f>
         <v>260</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <f>260</f>
         <v>260</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>25</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <f>538</f>
         <v>538</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <f>538</f>
         <v>538</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <f>538</f>
         <v>538</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <f>538</f>
         <v>538</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>26</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <f>2160</f>
         <v>2160</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <f>2160</f>
         <v>2160</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <f>2160</f>
         <v>2160</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <f>2160</f>
         <v>2160</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <f>1405</f>
         <v>1405</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <f>1405</f>
         <v>1405</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <f>1405</f>
         <v>1405</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <f>1405</f>
         <v>1405</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="14" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B13">
-        <f>B8-B9-B10-B11+B12</f>
+      <c r="B14">
+        <f>B9-B10-B11-B12+B13</f>
         <v>2247</v>
       </c>
-      <c r="C13">
-        <f t="shared" ref="C13:E13" si="3">C8-C9-C10-C11+C12</f>
+      <c r="C14">
+        <f t="shared" ref="C14:E14" si="3">C9-C10-C11-C12+C13</f>
         <v>2247</v>
       </c>
-      <c r="D13">
+      <c r="D14">
         <f t="shared" si="3"/>
         <v>2247</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <f t="shared" si="3"/>
         <v>2247</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14">
-        <f>B6-B13</f>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <f>B7-B14</f>
         <v>1949</v>
       </c>
-      <c r="C14">
-        <f t="shared" ref="C14:E14" si="4">C6-C13</f>
+      <c r="C15">
+        <f t="shared" ref="C15:E15" si="4">C7-C14</f>
         <v>2998</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <f t="shared" si="4"/>
         <v>4047</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <f t="shared" si="4"/>
         <v>5096</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="16" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="8">
+        <v>15</v>
+      </c>
+      <c r="C17" s="8">
+        <v>15</v>
+      </c>
+      <c r="D17" s="8">
+        <v>15</v>
+      </c>
+      <c r="E17" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="8">
+        <v>125</v>
+      </c>
+      <c r="C18" s="8">
+        <v>125</v>
+      </c>
+      <c r="D18" s="8">
+        <v>125</v>
+      </c>
+      <c r="E18" s="8">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="8">
+        <f>B17*B18</f>
+        <v>1875</v>
+      </c>
+      <c r="C19" s="8">
+        <f t="shared" ref="C19:E19" si="5">C17*C18</f>
+        <v>1875</v>
+      </c>
+      <c r="D19" s="8">
+        <f t="shared" si="5"/>
+        <v>1875</v>
+      </c>
+      <c r="E19" s="8">
+        <f t="shared" si="5"/>
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="8">
+        <f>2.5</f>
+        <v>2.5</v>
+      </c>
+      <c r="C20" s="8">
+        <f t="shared" ref="C20:E20" si="6">2.5</f>
+        <v>2.5</v>
+      </c>
+      <c r="D20" s="8">
+        <f t="shared" si="6"/>
+        <v>2.5</v>
+      </c>
+      <c r="E20" s="8">
+        <f t="shared" si="6"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="10">
+        <f>B18*B20</f>
+        <v>312.5</v>
+      </c>
+      <c r="C21" s="10">
+        <f t="shared" ref="C21:E21" si="7">C18*C20</f>
+        <v>312.5</v>
+      </c>
+      <c r="D21" s="10">
+        <f t="shared" si="7"/>
+        <v>312.5</v>
+      </c>
+      <c r="E21" s="10">
+        <f t="shared" si="7"/>
+        <v>312.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="10">
+        <f>B19-B21</f>
+        <v>1562.5</v>
+      </c>
+      <c r="C22" s="10">
+        <f t="shared" ref="C22:E22" si="8">C19-C21</f>
+        <v>1562.5</v>
+      </c>
+      <c r="D22" s="10">
+        <f t="shared" si="8"/>
+        <v>1562.5</v>
+      </c>
+      <c r="E22" s="10">
+        <f t="shared" si="8"/>
+        <v>1562.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="C23" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="D23" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="E23" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="2">
+        <f>B23*B22</f>
+        <v>156.25</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" ref="C24:E24" si="9">C23*C22</f>
+        <v>156.25</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="9"/>
+        <v>156.25</v>
+      </c>
+      <c r="E24" s="2">
+        <f t="shared" si="9"/>
+        <v>156.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="8">
+        <v>19</v>
+      </c>
+      <c r="C26" s="8">
+        <v>19</v>
+      </c>
+      <c r="D26" s="8">
+        <v>19</v>
+      </c>
+      <c r="E26" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="8">
+        <v>480</v>
+      </c>
+      <c r="C27" s="8">
+        <v>480</v>
+      </c>
+      <c r="D27" s="8">
+        <v>480</v>
+      </c>
+      <c r="E27" s="8">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="8">
+        <f>B26*B27</f>
+        <v>9120</v>
+      </c>
+      <c r="C28" s="8">
+        <f t="shared" ref="C28" si="10">C26*C27</f>
+        <v>9120</v>
+      </c>
+      <c r="D28" s="8">
+        <f t="shared" ref="D28" si="11">D26*D27</f>
+        <v>9120</v>
+      </c>
+      <c r="E28" s="8">
+        <f t="shared" ref="E28" si="12">E26*E27</f>
+        <v>9120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="C29" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="D29" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="E29" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="10">
+        <f>B27*B29</f>
+        <v>3360</v>
+      </c>
+      <c r="C30" s="10">
+        <f t="shared" ref="C30" si="13">C27*C29</f>
+        <v>3360</v>
+      </c>
+      <c r="D30" s="10">
+        <f t="shared" ref="D30" si="14">D27*D29</f>
+        <v>3360</v>
+      </c>
+      <c r="E30" s="10">
+        <f t="shared" ref="E30" si="15">E27*E29</f>
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="10">
+        <f>B28-B30</f>
+        <v>5760</v>
+      </c>
+      <c r="C31" s="10">
+        <f t="shared" ref="C31" si="16">C28-C30</f>
+        <v>5760</v>
+      </c>
+      <c r="D31" s="10">
+        <f t="shared" ref="D31" si="17">D28-D30</f>
+        <v>5760</v>
+      </c>
+      <c r="E31" s="10">
+        <f t="shared" ref="E31" si="18">E28-E30</f>
+        <v>5760</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="C32" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="D32" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="E32" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <f>B32*B31</f>
+        <v>576</v>
+      </c>
+      <c r="C33">
+        <f t="shared" ref="C33:E33" si="19">C32*C31</f>
+        <v>576</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="19"/>
+        <v>576</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="19"/>
+        <v>576</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="2">
+        <f>B15+B24+B33</f>
+        <v>2681.25</v>
+      </c>
+      <c r="C34" s="2">
+        <f t="shared" ref="C34:E34" si="20">C15+C24+C33</f>
+        <v>3730.25</v>
+      </c>
+      <c r="D34" s="2">
+        <f t="shared" si="20"/>
+        <v>4779.25</v>
+      </c>
+      <c r="E34" s="2">
+        <f t="shared" si="20"/>
+        <v>5828.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B35" s="2">
         <f>759209905/1000000</f>
         <v>759.20990500000005</v>
       </c>
-      <c r="C15" s="2">
-        <f t="shared" ref="C15:E15" si="5">759209905/1000000</f>
+      <c r="C35" s="2">
+        <f t="shared" ref="C35:E35" si="21">759209905/1000000</f>
         <v>759.20990500000005</v>
       </c>
-      <c r="D15" s="2">
-        <f t="shared" si="5"/>
+      <c r="D35" s="2">
+        <f t="shared" si="21"/>
         <v>759.20990500000005</v>
       </c>
-      <c r="E15" s="2">
-        <f t="shared" si="5"/>
+      <c r="E35" s="2">
+        <f t="shared" si="21"/>
         <v>759.20990500000005</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B36" s="2">
         <f>523240603/1000000</f>
         <v>523.24060299999996</v>
       </c>
-      <c r="C16" s="2">
-        <f t="shared" ref="C16:E16" si="6">523240603/1000000</f>
+      <c r="C36" s="2">
+        <f t="shared" ref="C36:E36" si="22">523240603/1000000</f>
         <v>523.24060299999996</v>
       </c>
-      <c r="D16" s="2">
-        <f t="shared" si="6"/>
+      <c r="D36" s="2">
+        <f t="shared" si="22"/>
         <v>523.24060299999996</v>
       </c>
-      <c r="E16" s="2">
-        <f t="shared" si="6"/>
+      <c r="E36" s="2">
+        <f t="shared" si="22"/>
         <v>523.24060299999996</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="2">
-        <f>B15-B16</f>
+      <c r="B37" s="2">
+        <f>B35-B36</f>
         <v>235.96930200000008</v>
       </c>
-      <c r="C17" s="2">
-        <f t="shared" ref="C17:E17" si="7">C15-C16</f>
+      <c r="C37" s="2">
+        <f t="shared" ref="C37:E37" si="23">C35-C36</f>
         <v>235.96930200000008</v>
       </c>
-      <c r="D17" s="2">
-        <f t="shared" si="7"/>
+      <c r="D37" s="2">
+        <f t="shared" si="23"/>
         <v>235.96930200000008</v>
       </c>
-      <c r="E17" s="2">
-        <f t="shared" si="7"/>
+      <c r="E37" s="2">
+        <f t="shared" si="23"/>
         <v>235.96930200000008</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="1">
-        <f>B14/B17</f>
-        <v>8.2595489475999688</v>
-      </c>
-      <c r="C18" s="1">
-        <f t="shared" ref="C18:E18" si="8">C14/C17</f>
-        <v>12.705042455056288</v>
-      </c>
-      <c r="D18" s="1">
-        <f t="shared" si="8"/>
-        <v>17.15053596251261</v>
-      </c>
-      <c r="E18" s="1">
-        <f t="shared" si="8"/>
-        <v>21.596029469968929</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="B38" s="1">
+        <f>B34/B37</f>
+        <v>11.362706832094622</v>
+      </c>
+      <c r="C38" s="1">
+        <f t="shared" ref="C38:E38" si="24">C34/C37</f>
+        <v>15.808200339550941</v>
+      </c>
+      <c r="D38" s="1">
+        <f t="shared" si="24"/>
+        <v>20.253693847007263</v>
+      </c>
+      <c r="E38" s="1">
+        <f t="shared" si="24"/>
+        <v>24.699187354463582</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B19">
+      <c r="B39">
         <f>1.18</f>
         <v>1.18</v>
       </c>
-      <c r="C19">
-        <f t="shared" ref="C19:E19" si="9">1.18</f>
+      <c r="C39">
+        <f t="shared" ref="C39:E39" si="25">1.18</f>
         <v>1.18</v>
       </c>
-      <c r="D19">
-        <f t="shared" si="9"/>
+      <c r="D39">
+        <f t="shared" si="25"/>
         <v>1.18</v>
       </c>
-      <c r="E19">
-        <f t="shared" si="9"/>
+      <c r="E39">
+        <f t="shared" si="25"/>
         <v>1.18</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="1">
-        <f>B18/B19</f>
-        <v>6.9996177522033634</v>
-      </c>
-      <c r="C20" s="1">
-        <f t="shared" ref="C20:E20" si="10">C18/C19</f>
-        <v>10.766985131403635</v>
-      </c>
-      <c r="D20" s="1">
-        <f t="shared" si="10"/>
-        <v>14.534352510603908</v>
-      </c>
-      <c r="E20" s="1">
-        <f t="shared" si="10"/>
-        <v>18.301719889804179</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B40" s="1">
+        <f>B38/B39</f>
+        <v>9.6294125695717145</v>
+      </c>
+      <c r="C40" s="1">
+        <f t="shared" ref="C40:E40" si="26">C38/C39</f>
+        <v>13.396779948771984</v>
+      </c>
+      <c r="D40" s="1">
+        <f t="shared" si="26"/>
+        <v>17.164147327972259</v>
+      </c>
+      <c r="E40" s="1">
+        <f t="shared" si="26"/>
+        <v>20.931514707172528</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>11</v>
       </c>
-      <c r="B21">
+      <c r="B41">
         <f>1.57</f>
         <v>1.57</v>
       </c>
-      <c r="C21">
-        <f t="shared" ref="C21:E21" si="11">1.57</f>
+      <c r="C41">
+        <f t="shared" ref="C41:E41" si="27">1.57</f>
         <v>1.57</v>
       </c>
-      <c r="D21">
-        <f t="shared" si="11"/>
+      <c r="D41">
+        <f t="shared" si="27"/>
         <v>1.57</v>
       </c>
-      <c r="E21">
-        <f t="shared" si="11"/>
+      <c r="E41">
+        <f t="shared" si="27"/>
         <v>1.57</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="1">
-        <f>B20+B21</f>
-        <v>8.5696177522033636</v>
-      </c>
-      <c r="C22" s="1">
-        <f t="shared" ref="C22:E22" si="12">C20+C21</f>
-        <v>12.336985131403635</v>
-      </c>
-      <c r="D22" s="1">
-        <f t="shared" si="12"/>
-        <v>16.104352510603906</v>
-      </c>
-      <c r="E22" s="1">
-        <f t="shared" si="12"/>
-        <v>19.871719889804179</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="B42" s="1">
+        <f>B40+B41</f>
+        <v>11.199412569571715</v>
+      </c>
+      <c r="C42" s="1">
+        <f t="shared" ref="C42:E42" si="28">C40+C41</f>
+        <v>14.966779948771984</v>
+      </c>
+      <c r="D42" s="1">
+        <f t="shared" si="28"/>
+        <v>18.734147327972259</v>
+      </c>
+      <c r="E42" s="1">
+        <f t="shared" si="28"/>
+        <v>22.501514707172529</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="2">
-        <f>B22*100</f>
-        <v>856.96177522033634</v>
-      </c>
-      <c r="C23" s="2">
-        <f t="shared" ref="C23:E23" si="13">C22*100</f>
-        <v>1233.6985131403635</v>
-      </c>
-      <c r="D23" s="2">
-        <f t="shared" si="13"/>
-        <v>1610.4352510603906</v>
-      </c>
-      <c r="E23" s="2">
-        <f t="shared" si="13"/>
-        <v>1987.1719889804178</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="B43" s="2">
+        <f>B42*100</f>
+        <v>1119.9412569571714</v>
+      </c>
+      <c r="C43" s="2">
+        <f t="shared" ref="C43:E43" si="29">C42*100</f>
+        <v>1496.6779948771984</v>
+      </c>
+      <c r="D43" s="2">
+        <f t="shared" si="29"/>
+        <v>1873.414732797226</v>
+      </c>
+      <c r="E43" s="2">
+        <f t="shared" si="29"/>
+        <v>2250.1514707172528</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B24">
+      <c r="B44">
         <v>595</v>
       </c>
-      <c r="C24">
+      <c r="C44">
         <v>595</v>
       </c>
-      <c r="D24">
+      <c r="D44">
         <v>595</v>
       </c>
-      <c r="E24">
+      <c r="E44">
         <v>595</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="3">
-        <f>B23/B24-1</f>
-        <v>0.44027189112661569</v>
-      </c>
-      <c r="C25" s="3">
-        <f t="shared" ref="C25:E25" si="14">C23/C24-1</f>
-        <v>1.0734428792275015</v>
-      </c>
-      <c r="D25" s="3">
-        <f t="shared" si="14"/>
-        <v>1.7066138673283873</v>
-      </c>
-      <c r="E25" s="3">
-        <f t="shared" si="14"/>
-        <v>2.3397848554292735</v>
+      <c r="B45" s="3">
+        <f>B43/B44-1</f>
+        <v>0.88225421337339727</v>
+      </c>
+      <c r="C45" s="3">
+        <f t="shared" ref="C45:E45" si="30">C43/C44-1</f>
+        <v>1.5154252014742831</v>
+      </c>
+      <c r="D45" s="3">
+        <f t="shared" si="30"/>
+        <v>2.1485961895751697</v>
+      </c>
+      <c r="E45" s="3">
+        <f t="shared" si="30"/>
+        <v>2.7817671776760551</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{740D45DC-A80B-4615-953A-F453DF4F4E26}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>4</v>
-      </c>
-      <c r="C1">
-        <v>5</v>
-      </c>
-      <c r="D1">
-        <v>6</v>
-      </c>
-      <c r="E1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1236</v>
-      </c>
-      <c r="C2">
-        <v>1236</v>
-      </c>
-      <c r="D2">
-        <v>1236</v>
-      </c>
-      <c r="E2">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3">
-        <f>47</f>
-        <v>47</v>
-      </c>
-      <c r="C3">
-        <f>47</f>
-        <v>47</v>
-      </c>
-      <c r="D3">
-        <f>47</f>
-        <v>47</v>
-      </c>
-      <c r="E3">
-        <f>47</f>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4">
-        <f>140</f>
-        <v>140</v>
-      </c>
-      <c r="C4">
-        <f>140</f>
-        <v>140</v>
-      </c>
-      <c r="D4">
-        <f>140</f>
-        <v>140</v>
-      </c>
-      <c r="E4">
-        <f>140</f>
-        <v>140</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5">
-        <f>B2-B3-B4</f>
-        <v>1049</v>
-      </c>
-      <c r="C5">
-        <f t="shared" ref="C5:E5" si="0">C2-C3-C4</f>
-        <v>1049</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>1049</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="0"/>
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <f>B5*B1</f>
-        <v>4196</v>
-      </c>
-      <c r="C6">
-        <f t="shared" ref="C6:E6" si="1">C5*C1</f>
-        <v>5245</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="1"/>
-        <v>6294</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="1"/>
-        <v>7343</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="2">
-        <f>2.25*B5</f>
-        <v>2360.25</v>
-      </c>
-      <c r="C7" s="2">
-        <f t="shared" ref="C7:E7" si="2">2.25*C5</f>
-        <v>2360.25</v>
-      </c>
-      <c r="D7" s="2">
-        <f t="shared" si="2"/>
-        <v>2360.25</v>
-      </c>
-      <c r="E7" s="2">
-        <f t="shared" si="2"/>
-        <v>2360.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <f>3800</f>
-        <v>3800</v>
-      </c>
-      <c r="C8">
-        <f>3800</f>
-        <v>3800</v>
-      </c>
-      <c r="D8">
-        <f>3800</f>
-        <v>3800</v>
-      </c>
-      <c r="E8">
-        <f>3800</f>
-        <v>3800</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
-        <f>260</f>
-        <v>260</v>
-      </c>
-      <c r="C9">
-        <f>260</f>
-        <v>260</v>
-      </c>
-      <c r="D9">
-        <f>260</f>
-        <v>260</v>
-      </c>
-      <c r="E9">
-        <f>260</f>
-        <v>260</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10">
-        <f>538</f>
-        <v>538</v>
-      </c>
-      <c r="C10">
-        <f>538</f>
-        <v>538</v>
-      </c>
-      <c r="D10">
-        <f>538</f>
-        <v>538</v>
-      </c>
-      <c r="E10">
-        <f>538</f>
-        <v>538</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-      <c r="C11">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-      <c r="D11">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-      <c r="E11">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12">
-        <f>967</f>
-        <v>967</v>
-      </c>
-      <c r="C12">
-        <f>967</f>
-        <v>967</v>
-      </c>
-      <c r="D12">
-        <f>967</f>
-        <v>967</v>
-      </c>
-      <c r="E12">
-        <f>967</f>
-        <v>967</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13">
-        <f>B8-B9-B10-B11+B12</f>
-        <v>2193</v>
-      </c>
-      <c r="C13">
-        <f t="shared" ref="C13:E13" si="3">C8-C9-C10-C11+C12</f>
-        <v>2193</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="3"/>
-        <v>2193</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="3"/>
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14">
-        <f>B6-B13</f>
-        <v>2003</v>
-      </c>
-      <c r="C14">
-        <f t="shared" ref="C14:E14" si="4">C6-C13</f>
-        <v>3052</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="4"/>
-        <v>4101</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="4"/>
-        <v>5150</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="2">
-        <f>759209905/1000000</f>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="C15" s="2">
-        <f t="shared" ref="C15:E15" si="5">759209905/1000000</f>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="D15" s="2">
-        <f t="shared" si="5"/>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="E15" s="2">
-        <f t="shared" si="5"/>
-        <v>759.20990500000005</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="2">
-        <f>523240603/1000000</f>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="C16" s="2">
-        <f t="shared" ref="C16:E16" si="6">523240603/1000000</f>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="D16" s="2">
-        <f t="shared" si="6"/>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="E16" s="2">
-        <f t="shared" si="6"/>
-        <v>523.24060299999996</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="2">
-        <f>B15-B16</f>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="C17" s="2">
-        <f t="shared" ref="C17:E17" si="7">C15-C16</f>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="D17" s="2">
-        <f t="shared" si="7"/>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="E17" s="2">
-        <f t="shared" si="7"/>
-        <v>235.96930200000008</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="1">
-        <f>B14/B17</f>
-        <v>8.4883922740085875</v>
-      </c>
-      <c r="C18" s="1">
-        <f t="shared" ref="C18:E18" si="8">C14/C17</f>
-        <v>12.933885781464909</v>
-      </c>
-      <c r="D18" s="1">
-        <f t="shared" si="8"/>
-        <v>17.379379288921228</v>
-      </c>
-      <c r="E18" s="1">
-        <f t="shared" si="8"/>
-        <v>21.824872796377548</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19">
-        <f>1.18</f>
-        <v>1.18</v>
-      </c>
-      <c r="C19">
-        <f t="shared" ref="C19:E19" si="9">1.18</f>
-        <v>1.18</v>
-      </c>
-      <c r="D19">
-        <f t="shared" si="9"/>
-        <v>1.18</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="9"/>
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="1">
-        <f>B18/B19</f>
-        <v>7.1935527745835488</v>
-      </c>
-      <c r="C20" s="1">
-        <f t="shared" ref="C20:E20" si="10">C18/C19</f>
-        <v>10.960920153783821</v>
-      </c>
-      <c r="D20" s="1">
-        <f t="shared" si="10"/>
-        <v>14.728287532984092</v>
-      </c>
-      <c r="E20" s="1">
-        <f t="shared" si="10"/>
-        <v>18.495654912184364</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="1">
-        <f>B20+B21</f>
-        <v>7.1935527745835488</v>
-      </c>
-      <c r="C22" s="1">
-        <f t="shared" ref="C22:E22" si="11">C20+C21</f>
-        <v>10.960920153783821</v>
-      </c>
-      <c r="D22" s="1">
-        <f t="shared" si="11"/>
-        <v>14.728287532984092</v>
-      </c>
-      <c r="E22" s="1">
-        <f t="shared" si="11"/>
-        <v>18.495654912184364</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="2">
-        <f>B22*100</f>
-        <v>719.35527745835486</v>
-      </c>
-      <c r="C23" s="2">
-        <f t="shared" ref="C23:E23" si="12">C22*100</f>
-        <v>1096.092015378382</v>
-      </c>
-      <c r="D23" s="2">
-        <f t="shared" si="12"/>
-        <v>1472.8287532984093</v>
-      </c>
-      <c r="E23" s="2">
-        <f t="shared" si="12"/>
-        <v>1849.5654912184364</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24">
-        <v>595</v>
-      </c>
-      <c r="C24">
-        <v>595</v>
-      </c>
-      <c r="D24">
-        <v>595</v>
-      </c>
-      <c r="E24">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="3">
-        <f>B23/B24-1</f>
-        <v>0.20900046631656277</v>
-      </c>
-      <c r="C25" s="3">
-        <f t="shared" ref="C25:E25" si="13">C23/C24-1</f>
-        <v>0.84217145441744878</v>
-      </c>
-      <c r="D25" s="3">
-        <f t="shared" si="13"/>
-        <v>1.4753424425183348</v>
-      </c>
-      <c r="E25" s="3">
-        <f t="shared" si="13"/>
-        <v>2.1085134306192206</v>
-      </c>
-    </row>
-  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A25:E25"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1688,545 +2566,918 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE8E3C78-B090-4354-8285-FB4151D5E6FA}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.7109375" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
+      <c r="B2">
         <v>4</v>
       </c>
-      <c r="C1">
+      <c r="C2">
         <v>5</v>
       </c>
-      <c r="D1">
+      <c r="D2">
         <v>6</v>
       </c>
-      <c r="E1">
+      <c r="E2">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1236</v>
-      </c>
-      <c r="C2">
-        <v>1236</v>
-      </c>
-      <c r="D2">
-        <v>1236</v>
-      </c>
-      <c r="E2">
-        <v>1236</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>230</v>
+        <v>1236</v>
       </c>
       <c r="C3">
-        <v>230</v>
+        <v>1236</v>
       </c>
       <c r="D3">
-        <v>230</v>
+        <v>1236</v>
       </c>
       <c r="E3">
-        <v>230</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>230</v>
+      </c>
+      <c r="C4">
+        <v>230</v>
+      </c>
+      <c r="D4">
+        <v>230</v>
+      </c>
+      <c r="E4">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <f>47</f>
         <v>47</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <f>47</f>
         <v>47</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <f>47</f>
         <v>47</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <f>47</f>
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <f>140</f>
         <v>140</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <f>140</f>
         <v>140</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <f>140</f>
         <v>140</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <f>140</f>
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6">
-        <f>B2+B3-B4-B5</f>
+      <c r="B7">
+        <f>B3+B4-B5-B6</f>
         <v>1279</v>
       </c>
-      <c r="C6">
-        <f t="shared" ref="C6:E6" si="0">C2+C3-C4-C5</f>
+      <c r="C7">
+        <f t="shared" ref="C7:E7" si="0">C3+C4-C5-C6</f>
         <v>1279</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <f t="shared" si="0"/>
         <v>1279</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <f t="shared" si="0"/>
         <v>1279</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B7">
-        <f>B6*B1</f>
+      <c r="B8">
+        <f>B7*B2</f>
         <v>5116</v>
       </c>
-      <c r="C7">
-        <f t="shared" ref="C7:E7" si="1">C6*C1</f>
+      <c r="C8">
+        <f t="shared" ref="C8:E8" si="1">C7*C2</f>
         <v>6395</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <f t="shared" si="1"/>
         <v>7674</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <f t="shared" si="1"/>
         <v>8953</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="2">
-        <f>2.25*B6</f>
+      <c r="B9" s="2">
+        <f>2.25*B7</f>
         <v>2877.75</v>
       </c>
-      <c r="C8" s="2">
-        <f t="shared" ref="C8:E8" si="2">2.25*C6</f>
+      <c r="C9" s="2">
+        <f t="shared" ref="C9:E9" si="2">2.25*C7</f>
         <v>2877.75</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D9" s="2">
         <f t="shared" si="2"/>
         <v>2877.75</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E9" s="2">
         <f t="shared" si="2"/>
         <v>2877.75</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>3</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <f>3800</f>
         <v>3800</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <f>3800</f>
         <v>3800</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <f>3800</f>
         <v>3800</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <f>3800</f>
         <v>3800</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>24</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <f>260</f>
         <v>260</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <f>260</f>
         <v>260</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <f>260</f>
         <v>260</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <f>260</f>
         <v>260</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>25</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <f>538</f>
         <v>538</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <f>538</f>
         <v>538</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <f>538</f>
         <v>538</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <f>538</f>
         <v>538</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>26</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <f>1776</f>
         <v>1776</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <f>1776</f>
         <v>1776</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <f>1776</f>
         <v>1776</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <f>1776</f>
         <v>1776</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>9</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <f>1405</f>
         <v>1405</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <f>1405</f>
         <v>1405</v>
       </c>
-      <c r="D13">
+      <c r="D14">
         <f>1405</f>
         <v>1405</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <f>1405</f>
         <v>1405</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B14">
-        <f>B9-B10-B11-B12+B13</f>
+      <c r="B15">
+        <f>B10-B11-B12-B13+B14</f>
         <v>2631</v>
       </c>
-      <c r="C14">
-        <f t="shared" ref="C14:E14" si="3">C9-C10-C11-C12+C13</f>
+      <c r="C15">
+        <f t="shared" ref="C15:E15" si="3">C10-C11-C12-C13+C14</f>
         <v>2631</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <f t="shared" si="3"/>
         <v>2631</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <f t="shared" si="3"/>
         <v>2631</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15">
-        <f>B7-B14</f>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16">
+        <f>B8-B15</f>
         <v>2485</v>
       </c>
-      <c r="C15">
-        <f t="shared" ref="C15:E15" si="4">C7-C14</f>
+      <c r="C16">
+        <f t="shared" ref="C16:E16" si="4">C8-C15</f>
         <v>3764</v>
       </c>
-      <c r="D15">
+      <c r="D16">
         <f t="shared" si="4"/>
         <v>5043</v>
       </c>
-      <c r="E15">
+      <c r="E16">
         <f t="shared" si="4"/>
         <v>6322</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="17" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="8">
+        <v>15</v>
+      </c>
+      <c r="C18" s="8">
+        <v>15</v>
+      </c>
+      <c r="D18" s="8">
+        <v>15</v>
+      </c>
+      <c r="E18" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="8">
+        <v>125</v>
+      </c>
+      <c r="C19" s="8">
+        <v>125</v>
+      </c>
+      <c r="D19" s="8">
+        <v>125</v>
+      </c>
+      <c r="E19" s="8">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="8">
+        <f>B18*B19</f>
+        <v>1875</v>
+      </c>
+      <c r="C20" s="8">
+        <f t="shared" ref="C20:E20" si="5">C18*C19</f>
+        <v>1875</v>
+      </c>
+      <c r="D20" s="8">
+        <f t="shared" si="5"/>
+        <v>1875</v>
+      </c>
+      <c r="E20" s="8">
+        <f t="shared" si="5"/>
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="8">
+        <f>2.5</f>
+        <v>2.5</v>
+      </c>
+      <c r="C21" s="8">
+        <f t="shared" ref="C21:E21" si="6">2.5</f>
+        <v>2.5</v>
+      </c>
+      <c r="D21" s="8">
+        <f t="shared" si="6"/>
+        <v>2.5</v>
+      </c>
+      <c r="E21" s="8">
+        <f t="shared" si="6"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="10">
+        <f>B19*B21</f>
+        <v>312.5</v>
+      </c>
+      <c r="C22" s="10">
+        <f t="shared" ref="C22:E22" si="7">C19*C21</f>
+        <v>312.5</v>
+      </c>
+      <c r="D22" s="10">
+        <f t="shared" si="7"/>
+        <v>312.5</v>
+      </c>
+      <c r="E22" s="10">
+        <f t="shared" si="7"/>
+        <v>312.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="10">
+        <f>B20-B22</f>
+        <v>1562.5</v>
+      </c>
+      <c r="C23" s="10">
+        <f t="shared" ref="C23:E23" si="8">C20-C22</f>
+        <v>1562.5</v>
+      </c>
+      <c r="D23" s="10">
+        <f t="shared" si="8"/>
+        <v>1562.5</v>
+      </c>
+      <c r="E23" s="10">
+        <f t="shared" si="8"/>
+        <v>1562.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="C24" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="D24" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="E24" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="2">
+        <f>0.1*(15*125-2.5*125)</f>
+        <v>156.25</v>
+      </c>
+      <c r="C25" s="2">
+        <f t="shared" ref="C25:E25" si="9">0.1*(15*125-2.5*125)</f>
+        <v>156.25</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="9"/>
+        <v>156.25</v>
+      </c>
+      <c r="E25" s="2">
+        <f t="shared" si="9"/>
+        <v>156.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="8">
+        <v>15</v>
+      </c>
+      <c r="C27" s="8">
+        <v>15</v>
+      </c>
+      <c r="D27" s="8">
+        <v>15</v>
+      </c>
+      <c r="E27" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="8">
+        <v>480</v>
+      </c>
+      <c r="C28" s="8">
+        <v>480</v>
+      </c>
+      <c r="D28" s="8">
+        <v>480</v>
+      </c>
+      <c r="E28" s="8">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="8">
+        <f>B27*B28</f>
+        <v>7200</v>
+      </c>
+      <c r="C29" s="8">
+        <f t="shared" ref="C29:E29" si="10">C27*C28</f>
+        <v>7200</v>
+      </c>
+      <c r="D29" s="8">
+        <f t="shared" si="10"/>
+        <v>7200</v>
+      </c>
+      <c r="E29" s="8">
+        <f t="shared" si="10"/>
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="C30" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="D30" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="E30" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="10">
+        <f>B28*B30</f>
+        <v>3360</v>
+      </c>
+      <c r="C31" s="10">
+        <f t="shared" ref="C31:E31" si="11">C28*C30</f>
+        <v>3360</v>
+      </c>
+      <c r="D31" s="10">
+        <f t="shared" si="11"/>
+        <v>3360</v>
+      </c>
+      <c r="E31" s="10">
+        <f t="shared" si="11"/>
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="10">
+        <f>B29-B31</f>
+        <v>3840</v>
+      </c>
+      <c r="C32" s="10">
+        <f t="shared" ref="C32:E32" si="12">C29-C31</f>
+        <v>3840</v>
+      </c>
+      <c r="D32" s="10">
+        <f t="shared" si="12"/>
+        <v>3840</v>
+      </c>
+      <c r="E32" s="10">
+        <f t="shared" si="12"/>
+        <v>3840</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="C33" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="E33" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <f>B33*B32</f>
+        <v>384</v>
+      </c>
+      <c r="C34">
+        <f t="shared" ref="C34:E34" si="13">C33*C32</f>
+        <v>384</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="13"/>
+        <v>384</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="13"/>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="2">
+        <f>B16+B25+B34</f>
+        <v>3025.25</v>
+      </c>
+      <c r="C35" s="2">
+        <f>C16+C25+C34</f>
+        <v>4304.25</v>
+      </c>
+      <c r="D35" s="2">
+        <f>D16+D25+D34</f>
+        <v>5583.25</v>
+      </c>
+      <c r="E35" s="2">
+        <f>E16+E25+E34</f>
+        <v>6862.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B36" s="2">
         <f>759209905/1000000</f>
         <v>759.20990500000005</v>
       </c>
-      <c r="C16" s="2">
-        <f t="shared" ref="C16:E16" si="5">759209905/1000000</f>
+      <c r="C36" s="2">
+        <f t="shared" ref="C36:E36" si="14">759209905/1000000</f>
         <v>759.20990500000005</v>
       </c>
-      <c r="D16" s="2">
-        <f t="shared" si="5"/>
+      <c r="D36" s="2">
+        <f t="shared" si="14"/>
         <v>759.20990500000005</v>
       </c>
-      <c r="E16" s="2">
-        <f t="shared" si="5"/>
+      <c r="E36" s="2">
+        <f t="shared" si="14"/>
         <v>759.20990500000005</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B37" s="2">
         <f>523240603/1000000</f>
         <v>523.24060299999996</v>
       </c>
-      <c r="C17" s="2">
-        <f t="shared" ref="C17:E17" si="6">523240603/1000000</f>
+      <c r="C37" s="2">
+        <f t="shared" ref="C37:E37" si="15">523240603/1000000</f>
         <v>523.24060299999996</v>
       </c>
-      <c r="D17" s="2">
-        <f t="shared" si="6"/>
+      <c r="D37" s="2">
+        <f t="shared" si="15"/>
         <v>523.24060299999996</v>
       </c>
-      <c r="E17" s="2">
-        <f t="shared" si="6"/>
+      <c r="E37" s="2">
+        <f t="shared" si="15"/>
         <v>523.24060299999996</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="2">
-        <f>B16-B17</f>
+      <c r="B38" s="2">
+        <f>B36-B37</f>
         <v>235.96930200000008</v>
       </c>
-      <c r="C18" s="2">
-        <f t="shared" ref="C18:E18" si="7">C16-C17</f>
+      <c r="C38" s="2">
+        <f t="shared" ref="C38:E38" si="16">C36-C37</f>
         <v>235.96930200000008</v>
       </c>
-      <c r="D18" s="2">
-        <f t="shared" si="7"/>
+      <c r="D38" s="2">
+        <f t="shared" si="16"/>
         <v>235.96930200000008</v>
       </c>
-      <c r="E18" s="2">
-        <f t="shared" si="7"/>
+      <c r="E38" s="2">
+        <f t="shared" si="16"/>
         <v>235.96930200000008</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="1">
-        <f>B15/B18</f>
-        <v>10.531030854174409</v>
-      </c>
-      <c r="C19" s="1">
-        <f t="shared" ref="C19:E19" si="8">C15/C18</f>
-        <v>15.951227418556329</v>
-      </c>
-      <c r="D19" s="1">
-        <f t="shared" si="8"/>
-        <v>21.371423982938246</v>
-      </c>
-      <c r="E19" s="1">
-        <f t="shared" si="8"/>
-        <v>26.791620547320168</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="B39" s="1">
+        <f>B35/B38</f>
+        <v>12.820523578105083</v>
+      </c>
+      <c r="C39" s="1">
+        <f t="shared" ref="C39:E39" si="17">C35/C38</f>
+        <v>18.240720142487003</v>
+      </c>
+      <c r="D39" s="1">
+        <f t="shared" si="17"/>
+        <v>23.660916706868921</v>
+      </c>
+      <c r="E39" s="1">
+        <f t="shared" si="17"/>
+        <v>29.081113271250842</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B20">
+      <c r="B40">
         <f>1.18</f>
         <v>1.18</v>
       </c>
-      <c r="C20">
-        <f t="shared" ref="C20:E20" si="9">1.18</f>
+      <c r="C40">
+        <f t="shared" ref="C40:E40" si="18">1.18</f>
         <v>1.18</v>
       </c>
-      <c r="D20">
-        <f t="shared" si="9"/>
+      <c r="D40">
+        <f t="shared" si="18"/>
         <v>1.18</v>
       </c>
-      <c r="E20">
-        <f t="shared" si="9"/>
+      <c r="E40">
+        <f t="shared" si="18"/>
         <v>1.18</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="1">
-        <f>B19/B20</f>
-        <v>8.9246024187918724</v>
-      </c>
-      <c r="C21" s="1">
-        <f t="shared" ref="C21:E21" si="10">C19/C20</f>
-        <v>13.517989337759602</v>
-      </c>
-      <c r="D21" s="1">
-        <f t="shared" si="10"/>
-        <v>18.111376256727329</v>
-      </c>
-      <c r="E21" s="1">
-        <f t="shared" si="10"/>
-        <v>22.70476317569506</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B41" s="1">
+        <f>B39/B40</f>
+        <v>10.864850489919563</v>
+      </c>
+      <c r="C41" s="1">
+        <f t="shared" ref="C41:E41" si="19">C39/C40</f>
+        <v>15.458237408887292</v>
+      </c>
+      <c r="D41" s="1">
+        <f t="shared" si="19"/>
+        <v>20.05162432785502</v>
+      </c>
+      <c r="E41" s="1">
+        <f t="shared" si="19"/>
+        <v>24.645011246822751</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>11</v>
       </c>
-      <c r="B22">
+      <c r="B42">
         <f>1.57</f>
         <v>1.57</v>
       </c>
-      <c r="C22">
-        <f t="shared" ref="C22:E22" si="11">1.57</f>
+      <c r="C42">
+        <f t="shared" ref="C42:E42" si="20">1.57</f>
         <v>1.57</v>
       </c>
-      <c r="D22">
-        <f t="shared" si="11"/>
+      <c r="D42">
+        <f t="shared" si="20"/>
         <v>1.57</v>
       </c>
-      <c r="E22">
-        <f t="shared" si="11"/>
+      <c r="E42">
+        <f t="shared" si="20"/>
         <v>1.57</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="1">
-        <f>B21+B22</f>
-        <v>10.494602418791873</v>
-      </c>
-      <c r="C23" s="1">
-        <f t="shared" ref="C23:E23" si="12">C21+C22</f>
-        <v>15.087989337759602</v>
-      </c>
-      <c r="D23" s="1">
-        <f t="shared" si="12"/>
-        <v>19.681376256727329</v>
-      </c>
-      <c r="E23" s="1">
-        <f t="shared" si="12"/>
-        <v>24.27476317569506</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="B43" s="1">
+        <f>B41+B42</f>
+        <v>12.434850489919564</v>
+      </c>
+      <c r="C43" s="1">
+        <f t="shared" ref="C43:E43" si="21">C41+C42</f>
+        <v>17.028237408887293</v>
+      </c>
+      <c r="D43" s="1">
+        <f t="shared" si="21"/>
+        <v>21.62162432785502</v>
+      </c>
+      <c r="E43" s="1">
+        <f t="shared" si="21"/>
+        <v>26.215011246822751</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="2">
-        <f>B23*100</f>
-        <v>1049.4602418791874</v>
-      </c>
-      <c r="C24" s="2">
-        <f t="shared" ref="C24:E24" si="13">C23*100</f>
-        <v>1508.7989337759602</v>
-      </c>
-      <c r="D24" s="2">
-        <f t="shared" si="13"/>
-        <v>1968.1376256727328</v>
-      </c>
-      <c r="E24" s="2">
-        <f t="shared" si="13"/>
-        <v>2427.4763175695061</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="B44" s="2">
+        <f>B43*100</f>
+        <v>1243.4850489919563</v>
+      </c>
+      <c r="C44" s="2">
+        <f t="shared" ref="C44:E44" si="22">C43*100</f>
+        <v>1702.8237408887294</v>
+      </c>
+      <c r="D44" s="2">
+        <f t="shared" si="22"/>
+        <v>2162.162432785502</v>
+      </c>
+      <c r="E44" s="2">
+        <f t="shared" si="22"/>
+        <v>2621.5011246822751</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B25">
+      <c r="B45">
         <v>595</v>
       </c>
-      <c r="C25">
+      <c r="C45">
         <v>595</v>
       </c>
-      <c r="D25">
+      <c r="D45">
         <v>595</v>
       </c>
-      <c r="E25">
+      <c r="E45">
         <v>595</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="3">
-        <f>B24/B25-1</f>
-        <v>0.76379872584737374</v>
-      </c>
-      <c r="C26" s="3">
-        <f t="shared" ref="C26:E26" si="14">C24/C25-1</f>
-        <v>1.5357965273545551</v>
-      </c>
-      <c r="D26" s="3">
-        <f t="shared" si="14"/>
-        <v>2.307794328861736</v>
-      </c>
-      <c r="E26" s="3">
-        <f t="shared" si="14"/>
-        <v>3.0797921303689177</v>
+      <c r="B46" s="3">
+        <f>B44/B45-1</f>
+        <v>1.0898908386419435</v>
+      </c>
+      <c r="C46" s="3">
+        <f t="shared" ref="C46:E46" si="23">C44/C45-1</f>
+        <v>1.8618886401491248</v>
+      </c>
+      <c r="D46" s="3">
+        <f t="shared" si="23"/>
+        <v>2.6338864416563057</v>
+      </c>
+      <c r="E46" s="3">
+        <f t="shared" si="23"/>
+        <v>3.4058842431634879</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A26:E26"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
+++ b/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Value Investing\Zegona Communications Plc - ZEG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1227265B-E907-428E-BB72-410B34208204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133EEEE5-B1D7-4575-BD78-6C6839AAC8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
   </bookViews>
   <sheets>
     <sheet name="Dividendo parcial + Preferentes" sheetId="2" r:id="rId1"/>
     <sheet name="Dividendo + Preferentes" sheetId="1" r:id="rId2"/>
     <sheet name="Reestructuracion (+Div+Pre)" sheetId="4" r:id="rId3"/>
-    <sheet name="Gabriel Castro" sheetId="7" r:id="rId4"/>
+    <sheet name="Venta FibreCo MasOrange a GIC" sheetId="8" r:id="rId4"/>
+    <sheet name="Gabriel Castro" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="42">
   <si>
     <t>EV/EBITDAaL</t>
   </si>
@@ -344,12 +345,36 @@
   <si>
     <t>Equity Total (SOTP)</t>
   </si>
+  <si>
+    <r>
+      <t>Precio por acción final (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>GBP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -377,6 +402,13 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -408,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -432,6 +464,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1572,8 +1605,8 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>19</v>
+      <c r="A42" s="11" t="s">
+        <v>41</v>
       </c>
       <c r="B42" s="1">
         <f>B40+B41</f>
@@ -3226,7 +3259,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B35" s="2">
         <f>B16+B25+B34</f>
@@ -3393,8 +3426,8 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>19</v>
+      <c r="A43" s="11" t="s">
+        <v>41</v>
       </c>
       <c r="B43" s="1">
         <f>B41+B42</f>
@@ -3484,6 +3517,908 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D67E2F94-95BD-44CD-A4DD-4E84629A5FE7}">
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="49.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1236</v>
+      </c>
+      <c r="C3">
+        <v>1236</v>
+      </c>
+      <c r="D3">
+        <v>1236</v>
+      </c>
+      <c r="E3">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="C4">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="D4">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="E4">
+        <f>47</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="C5">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="D5">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="E5">
+        <f>140</f>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <f>B3-B4-B5</f>
+        <v>1049</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:E6" si="0">C3-C4-C5</f>
+        <v>1049</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>1049</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>B6*B2</f>
+        <v>4196</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:E7" si="1">C6*C2</f>
+        <v>5245</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>6294</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>7343</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="2">
+        <f>2.25*B6</f>
+        <v>2360.25</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" ref="C8:E8" si="2">2.25*C6</f>
+        <v>2360.25</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="2"/>
+        <v>2360.25</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="2"/>
+        <v>2360.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="C9">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="D9">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="E9">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="C10">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="D10">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="E10">
+        <f>260</f>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="C11">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="D11">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="E11">
+        <f>538</f>
+        <v>538</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12">
+        <f>2160</f>
+        <v>2160</v>
+      </c>
+      <c r="C12">
+        <f>2160</f>
+        <v>2160</v>
+      </c>
+      <c r="D12">
+        <f>2160</f>
+        <v>2160</v>
+      </c>
+      <c r="E12">
+        <f>2160</f>
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="C13">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="D13">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="E13">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <f>B9-B10-B11-B12+B13</f>
+        <v>2247</v>
+      </c>
+      <c r="C14">
+        <f t="shared" ref="C14:E14" si="3">C9-C10-C11-C12+C13</f>
+        <v>2247</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="3"/>
+        <v>2247</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="3"/>
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <f>B7-B14</f>
+        <v>1949</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:E15" si="4">C7-C14</f>
+        <v>2998</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="4"/>
+        <v>4047</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="4"/>
+        <v>5096</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="8">
+        <v>15</v>
+      </c>
+      <c r="C17" s="8">
+        <v>15</v>
+      </c>
+      <c r="D17" s="8">
+        <v>15</v>
+      </c>
+      <c r="E17" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="8">
+        <v>125</v>
+      </c>
+      <c r="C18" s="8">
+        <v>125</v>
+      </c>
+      <c r="D18" s="8">
+        <v>125</v>
+      </c>
+      <c r="E18" s="8">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="8">
+        <f>B17*B18</f>
+        <v>1875</v>
+      </c>
+      <c r="C19" s="8">
+        <f t="shared" ref="C19:E19" si="5">C17*C18</f>
+        <v>1875</v>
+      </c>
+      <c r="D19" s="8">
+        <f t="shared" si="5"/>
+        <v>1875</v>
+      </c>
+      <c r="E19" s="8">
+        <f t="shared" si="5"/>
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="8">
+        <f>2.5</f>
+        <v>2.5</v>
+      </c>
+      <c r="C20" s="8">
+        <f t="shared" ref="C20:E20" si="6">2.5</f>
+        <v>2.5</v>
+      </c>
+      <c r="D20" s="8">
+        <f t="shared" si="6"/>
+        <v>2.5</v>
+      </c>
+      <c r="E20" s="8">
+        <f t="shared" si="6"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="10">
+        <f>B18*B20</f>
+        <v>312.5</v>
+      </c>
+      <c r="C21" s="10">
+        <f t="shared" ref="C21:E21" si="7">C18*C20</f>
+        <v>312.5</v>
+      </c>
+      <c r="D21" s="10">
+        <f t="shared" si="7"/>
+        <v>312.5</v>
+      </c>
+      <c r="E21" s="10">
+        <f t="shared" si="7"/>
+        <v>312.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="10">
+        <f>B19-B21</f>
+        <v>1562.5</v>
+      </c>
+      <c r="C22" s="10">
+        <f t="shared" ref="C22:E22" si="8">C19-C21</f>
+        <v>1562.5</v>
+      </c>
+      <c r="D22" s="10">
+        <f t="shared" si="8"/>
+        <v>1562.5</v>
+      </c>
+      <c r="E22" s="10">
+        <f t="shared" si="8"/>
+        <v>1562.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="C23" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="D23" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="E23" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="2">
+        <f>B23*B22</f>
+        <v>156.25</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" ref="C24:E24" si="9">C23*C22</f>
+        <v>156.25</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="9"/>
+        <v>156.25</v>
+      </c>
+      <c r="E24" s="2">
+        <f t="shared" si="9"/>
+        <v>156.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="8">
+        <v>19</v>
+      </c>
+      <c r="C26" s="8">
+        <v>19</v>
+      </c>
+      <c r="D26" s="8">
+        <v>19</v>
+      </c>
+      <c r="E26" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="8">
+        <v>480</v>
+      </c>
+      <c r="C27" s="8">
+        <v>480</v>
+      </c>
+      <c r="D27" s="8">
+        <v>480</v>
+      </c>
+      <c r="E27" s="8">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="8">
+        <f>B26*B27</f>
+        <v>9120</v>
+      </c>
+      <c r="C28" s="8">
+        <f t="shared" ref="C28:E28" si="10">C26*C27</f>
+        <v>9120</v>
+      </c>
+      <c r="D28" s="8">
+        <f t="shared" si="10"/>
+        <v>9120</v>
+      </c>
+      <c r="E28" s="8">
+        <f t="shared" si="10"/>
+        <v>9120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="C29" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="D29" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="E29" s="8">
+        <f>7</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="10">
+        <f>B27*B29</f>
+        <v>3360</v>
+      </c>
+      <c r="C30" s="10">
+        <f t="shared" ref="C30:E30" si="11">C27*C29</f>
+        <v>3360</v>
+      </c>
+      <c r="D30" s="10">
+        <f t="shared" si="11"/>
+        <v>3360</v>
+      </c>
+      <c r="E30" s="10">
+        <f t="shared" si="11"/>
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="10">
+        <f>B28-B30</f>
+        <v>5760</v>
+      </c>
+      <c r="C31" s="10">
+        <f t="shared" ref="C31:E31" si="12">C28-C30</f>
+        <v>5760</v>
+      </c>
+      <c r="D31" s="10">
+        <f t="shared" si="12"/>
+        <v>5760</v>
+      </c>
+      <c r="E31" s="10">
+        <f t="shared" si="12"/>
+        <v>5760</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="C32" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="D32" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="E32" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <f>B32*B31</f>
+        <v>576</v>
+      </c>
+      <c r="C33">
+        <f t="shared" ref="C33:E33" si="13">C32*C31</f>
+        <v>576</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="13"/>
+        <v>576</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="13"/>
+        <v>576</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="2">
+        <f>B15+B24+B33</f>
+        <v>2681.25</v>
+      </c>
+      <c r="C34" s="2">
+        <f t="shared" ref="C34:E34" si="14">C15+C24+C33</f>
+        <v>3730.25</v>
+      </c>
+      <c r="D34" s="2">
+        <f t="shared" si="14"/>
+        <v>4779.25</v>
+      </c>
+      <c r="E34" s="2">
+        <f t="shared" si="14"/>
+        <v>5828.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="2">
+        <f>759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="C35" s="2">
+        <f t="shared" ref="C35:E35" si="15">759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="D35" s="2">
+        <f t="shared" si="15"/>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="E35" s="2">
+        <f t="shared" si="15"/>
+        <v>759.20990500000005</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="2">
+        <f>523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="C36" s="2">
+        <f t="shared" ref="C36:E36" si="16">523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="D36" s="2">
+        <f t="shared" si="16"/>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="E36" s="2">
+        <f t="shared" si="16"/>
+        <v>523.24060299999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="2">
+        <f>B35-B36</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="C37" s="2">
+        <f t="shared" ref="C37:E37" si="17">C35-C36</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" si="17"/>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="E37" s="2">
+        <f t="shared" si="17"/>
+        <v>235.96930200000008</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="1">
+        <f>B34/B37</f>
+        <v>11.362706832094622</v>
+      </c>
+      <c r="C38" s="1">
+        <f t="shared" ref="C38:E38" si="18">C34/C37</f>
+        <v>15.808200339550941</v>
+      </c>
+      <c r="D38" s="1">
+        <f t="shared" si="18"/>
+        <v>20.253693847007263</v>
+      </c>
+      <c r="E38" s="1">
+        <f t="shared" si="18"/>
+        <v>24.699187354463582</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39">
+        <f>1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="C39">
+        <f t="shared" ref="C39:E39" si="19">1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="19"/>
+        <v>1.18</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="19"/>
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="1">
+        <f>B38/B39</f>
+        <v>9.6294125695717145</v>
+      </c>
+      <c r="C40" s="1">
+        <f t="shared" ref="C40:E40" si="20">C38/C39</f>
+        <v>13.396779948771984</v>
+      </c>
+      <c r="D40" s="1">
+        <f t="shared" si="20"/>
+        <v>17.164147327972259</v>
+      </c>
+      <c r="E40" s="1">
+        <f t="shared" si="20"/>
+        <v>20.931514707172528</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41">
+        <f>1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="C41">
+        <f t="shared" ref="C41:E41" si="21">1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="21"/>
+        <v>1.57</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="21"/>
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="1">
+        <f>B40+B41</f>
+        <v>11.199412569571715</v>
+      </c>
+      <c r="C42" s="1">
+        <f t="shared" ref="C42:E42" si="22">C40+C41</f>
+        <v>14.966779948771984</v>
+      </c>
+      <c r="D42" s="1">
+        <f t="shared" si="22"/>
+        <v>18.734147327972259</v>
+      </c>
+      <c r="E42" s="1">
+        <f t="shared" si="22"/>
+        <v>22.501514707172529</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" s="2">
+        <f>B42*100</f>
+        <v>1119.9412569571714</v>
+      </c>
+      <c r="C43" s="2">
+        <f t="shared" ref="C43:E43" si="23">C42*100</f>
+        <v>1496.6779948771984</v>
+      </c>
+      <c r="D43" s="2">
+        <f t="shared" si="23"/>
+        <v>1873.414732797226</v>
+      </c>
+      <c r="E43" s="2">
+        <f t="shared" si="23"/>
+        <v>2250.1514707172528</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44">
+        <v>595</v>
+      </c>
+      <c r="C44">
+        <v>595</v>
+      </c>
+      <c r="D44">
+        <v>595</v>
+      </c>
+      <c r="E44">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="3">
+        <f>B43/B44-1</f>
+        <v>0.88225421337339727</v>
+      </c>
+      <c r="C45" s="3">
+        <f t="shared" ref="C45:E45" si="24">C43/C44-1</f>
+        <v>1.5154252014742831</v>
+      </c>
+      <c r="D45" s="3">
+        <f t="shared" si="24"/>
+        <v>2.1485961895751697</v>
+      </c>
+      <c r="E45" s="3">
+        <f t="shared" si="24"/>
+        <v>2.7817671776760551</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A25:E25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C948590-68A6-476D-B63A-653E4BD7F956}">
   <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
+++ b/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Value Investing\Zegona Communications Plc - ZEG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133EEEE5-B1D7-4575-BD78-6C6839AAC8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF5FFAB-C3A4-4A1A-BA06-35DB25791329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
   </bookViews>
   <sheets>
     <sheet name="Dividendo parcial + Preferentes" sheetId="2" r:id="rId1"/>
     <sheet name="Dividendo + Preferentes" sheetId="1" r:id="rId2"/>
     <sheet name="Reestructuracion (+Div+Pre)" sheetId="4" r:id="rId3"/>
-    <sheet name="Venta FibreCo MasOrange a GIC" sheetId="8" r:id="rId4"/>
-    <sheet name="Gabriel Castro" sheetId="7" r:id="rId5"/>
+    <sheet name="Venta FibreCo MasOrange" sheetId="8" r:id="rId4"/>
+    <sheet name="Venta FibreCo MasOrange + Reest" sheetId="9" r:id="rId5"/>
+    <sheet name="Gabriel Castro" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="43">
   <si>
     <t>EV/EBITDAaL</t>
   </si>
@@ -368,6 +369,9 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>Covenant financiero (3,1xEBITDAaL)</t>
   </si>
 </sst>
 </file>
@@ -3518,7 +3522,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D67E2F94-95BD-44CD-A4DD-4E84629A5FE7}">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.7109375" bestFit="1" customWidth="1"/>
@@ -3655,23 +3659,23 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2">
-        <f>2.25*B6</f>
-        <v>2360.25</v>
+        <f>3.1*B6</f>
+        <v>3251.9</v>
       </c>
       <c r="C8" s="2">
-        <f t="shared" ref="C8:E8" si="2">2.25*C6</f>
-        <v>2360.25</v>
+        <f t="shared" ref="C8:E8" si="2">3.1*C6</f>
+        <v>3251.9</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="2"/>
-        <v>2360.25</v>
+        <v>3251.9</v>
       </c>
       <c r="E8" s="2">
         <f t="shared" si="2"/>
-        <v>2360.25</v>
+        <v>3251.9</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -3679,41 +3683,805 @@
         <v>3</v>
       </c>
       <c r="B9">
-        <f>3800</f>
-        <v>3800</v>
+        <v>3617</v>
       </c>
       <c r="C9">
-        <f>3800</f>
-        <v>3800</v>
+        <v>3617</v>
       </c>
       <c r="D9">
-        <f>3800</f>
-        <v>3800</v>
+        <v>3617</v>
       </c>
       <c r="E9">
-        <f>3800</f>
-        <v>3800</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10">
-        <f>260</f>
-        <v>260</v>
+        <f>538</f>
+        <v>538</v>
       </c>
       <c r="C10">
-        <f>260</f>
-        <v>260</v>
+        <f>538</f>
+        <v>538</v>
       </c>
       <c r="D10">
-        <f>260</f>
-        <v>260</v>
+        <f>538</f>
+        <v>538</v>
       </c>
       <c r="E10">
-        <f>260</f>
-        <v>260</v>
+        <f>538</f>
+        <v>538</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
+        <v>1400</v>
+      </c>
+      <c r="C11">
+        <v>1400</v>
+      </c>
+      <c r="D11">
+        <v>1400</v>
+      </c>
+      <c r="E11">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="C12">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="D12">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="E12">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <f>B9-B10-B11+B12</f>
+        <v>3084</v>
+      </c>
+      <c r="C13">
+        <f t="shared" ref="C13:E13" si="3">C9-C10-C11+C12</f>
+        <v>3084</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="3"/>
+        <v>3084</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="3"/>
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14">
+        <f>B7-B13</f>
+        <v>1112</v>
+      </c>
+      <c r="C14">
+        <f>C7-C13</f>
+        <v>2161</v>
+      </c>
+      <c r="D14">
+        <f>D7-D13</f>
+        <v>3210</v>
+      </c>
+      <c r="E14">
+        <f>E7-E13</f>
+        <v>4259</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="8">
+        <v>15</v>
+      </c>
+      <c r="C16" s="8">
+        <v>15</v>
+      </c>
+      <c r="D16" s="8">
+        <v>15</v>
+      </c>
+      <c r="E16" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="8">
+        <v>125</v>
+      </c>
+      <c r="C17" s="8">
+        <v>125</v>
+      </c>
+      <c r="D17" s="8">
+        <v>125</v>
+      </c>
+      <c r="E17" s="8">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="8">
+        <f>B16*B17</f>
+        <v>1875</v>
+      </c>
+      <c r="C18" s="8">
+        <f t="shared" ref="C18:E18" si="4">C16*C17</f>
+        <v>1875</v>
+      </c>
+      <c r="D18" s="8">
+        <f t="shared" si="4"/>
+        <v>1875</v>
+      </c>
+      <c r="E18" s="8">
+        <f t="shared" si="4"/>
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="8">
+        <f>2.5</f>
+        <v>2.5</v>
+      </c>
+      <c r="C19" s="8">
+        <f t="shared" ref="C19:E19" si="5">2.5</f>
+        <v>2.5</v>
+      </c>
+      <c r="D19" s="8">
+        <f t="shared" si="5"/>
+        <v>2.5</v>
+      </c>
+      <c r="E19" s="8">
+        <f t="shared" si="5"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="10">
+        <f>B17*B19</f>
+        <v>312.5</v>
+      </c>
+      <c r="C20" s="10">
+        <f t="shared" ref="C20:E20" si="6">C17*C19</f>
+        <v>312.5</v>
+      </c>
+      <c r="D20" s="10">
+        <f t="shared" si="6"/>
+        <v>312.5</v>
+      </c>
+      <c r="E20" s="10">
+        <f t="shared" si="6"/>
+        <v>312.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="10">
+        <f>B18-B20</f>
+        <v>1562.5</v>
+      </c>
+      <c r="C21" s="10">
+        <f t="shared" ref="C21:E21" si="7">C18-C20</f>
+        <v>1562.5</v>
+      </c>
+      <c r="D21" s="10">
+        <f t="shared" si="7"/>
+        <v>1562.5</v>
+      </c>
+      <c r="E21" s="10">
+        <f t="shared" si="7"/>
+        <v>1562.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="C22" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="D22" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+      <c r="E22" s="9">
+        <f>10%</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="2">
+        <f>B22*B21</f>
+        <v>156.25</v>
+      </c>
+      <c r="C23" s="2">
+        <f t="shared" ref="C23:E23" si="8">C22*C21</f>
+        <v>156.25</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="8"/>
+        <v>156.25</v>
+      </c>
+      <c r="E23" s="2">
+        <f t="shared" si="8"/>
+        <v>156.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="10">
+        <v>3640</v>
+      </c>
+      <c r="C25" s="10">
+        <v>3640</v>
+      </c>
+      <c r="D25" s="10">
+        <v>3640</v>
+      </c>
+      <c r="E25" s="10">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="9">
+        <f>17.5%</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="C26" s="9">
+        <f t="shared" ref="C26:E26" si="9">17.5%</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="D26" s="9">
+        <f t="shared" si="9"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="E26" s="9">
+        <f t="shared" si="9"/>
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27">
+        <f>B26*B25</f>
+        <v>637</v>
+      </c>
+      <c r="C27">
+        <f t="shared" ref="C27:E27" si="10">C26*C25</f>
+        <v>637</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="10"/>
+        <v>637</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="10"/>
+        <v>637</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="2">
+        <f>B14+B23+B27</f>
+        <v>1905.25</v>
+      </c>
+      <c r="C28" s="2">
+        <f>C14+C23+C27</f>
+        <v>2954.25</v>
+      </c>
+      <c r="D28" s="2">
+        <f>D14+D23+D27</f>
+        <v>4003.25</v>
+      </c>
+      <c r="E28" s="2">
+        <f>E14+E23+E27</f>
+        <v>5052.25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="2">
+        <f>759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="C29" s="2">
+        <f t="shared" ref="C29:E29" si="11">759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="D29" s="2">
+        <f t="shared" si="11"/>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="E29" s="2">
+        <f t="shared" si="11"/>
+        <v>759.20990500000005</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="2">
+        <f>523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="C30" s="2">
+        <f t="shared" ref="C30:E30" si="12">523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" si="12"/>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="E30" s="2">
+        <f t="shared" si="12"/>
+        <v>523.24060299999996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="2">
+        <f>B29-B30</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="C31" s="2">
+        <f t="shared" ref="C31:E31" si="13">C29-C30</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="D31" s="2">
+        <f t="shared" si="13"/>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="E31" s="2">
+        <f t="shared" si="13"/>
+        <v>235.96930200000008</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="1">
+        <f>B28/B31</f>
+        <v>8.0741434748152088</v>
+      </c>
+      <c r="C32" s="1">
+        <f t="shared" ref="C32:E32" si="14">C28/C31</f>
+        <v>12.519636982271528</v>
+      </c>
+      <c r="D32" s="1">
+        <f t="shared" si="14"/>
+        <v>16.965130489727848</v>
+      </c>
+      <c r="E32" s="1">
+        <f t="shared" si="14"/>
+        <v>21.410623997184167</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33">
+        <f>1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="C33">
+        <f t="shared" ref="C33:E33" si="15">1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="15"/>
+        <v>1.18</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="15"/>
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="1">
+        <f>B32/B33</f>
+        <v>6.8424944701823804</v>
+      </c>
+      <c r="C34" s="1">
+        <f t="shared" ref="C34:E34" si="16">C32/C33</f>
+        <v>10.609861849382652</v>
+      </c>
+      <c r="D34" s="1">
+        <f t="shared" si="16"/>
+        <v>14.377229228582923</v>
+      </c>
+      <c r="E34" s="1">
+        <f t="shared" si="16"/>
+        <v>18.144596607783193</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35">
+        <f>1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="C35">
+        <f t="shared" ref="C35:E35" si="17">1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="17"/>
+        <v>1.57</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="17"/>
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="1">
+        <f>B34+B35</f>
+        <v>8.4124944701823807</v>
+      </c>
+      <c r="C36" s="1">
+        <f t="shared" ref="C36:E36" si="18">C34+C35</f>
+        <v>12.179861849382652</v>
+      </c>
+      <c r="D36" s="1">
+        <f t="shared" si="18"/>
+        <v>15.947229228582923</v>
+      </c>
+      <c r="E36" s="1">
+        <f t="shared" si="18"/>
+        <v>19.714596607783193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="2">
+        <f>B36*100</f>
+        <v>841.24944701823802</v>
+      </c>
+      <c r="C37" s="2">
+        <f t="shared" ref="C37:E37" si="19">C36*100</f>
+        <v>1217.9861849382653</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" si="19"/>
+        <v>1594.7229228582923</v>
+      </c>
+      <c r="E37" s="2">
+        <f t="shared" si="19"/>
+        <v>1971.4596607783192</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38">
+        <v>595</v>
+      </c>
+      <c r="C38">
+        <v>595</v>
+      </c>
+      <c r="D38">
+        <v>595</v>
+      </c>
+      <c r="E38">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="3">
+        <f>B37/B38-1</f>
+        <v>0.41386461683737474</v>
+      </c>
+      <c r="C39" s="3">
+        <f t="shared" ref="C39:E39" si="20">C37/C38-1</f>
+        <v>1.047035604938261</v>
+      </c>
+      <c r="D39" s="3">
+        <f t="shared" si="20"/>
+        <v>1.6802065930391468</v>
+      </c>
+      <c r="E39" s="3">
+        <f t="shared" si="20"/>
+        <v>2.3133775811400321</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A24:E24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13C224D3-67F3-44FC-BBD6-2F7B18D9A166}">
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="49.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1236</v>
+      </c>
+      <c r="C3">
+        <v>1236</v>
+      </c>
+      <c r="D3">
+        <v>1236</v>
+      </c>
+      <c r="E3">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>230</v>
+      </c>
+      <c r="C4">
+        <v>230</v>
+      </c>
+      <c r="D4">
+        <v>230</v>
+      </c>
+      <c r="E4">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="C5">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="D5">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="E5">
+        <f>47</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="C6">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="D6">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="E6">
+        <f>140</f>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <f>B3+B4-B5-B6</f>
+        <v>1279</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:E7" si="0">C3+C4-C5-C6</f>
+        <v>1279</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>1279</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <f>B7*B2</f>
+        <v>5116</v>
+      </c>
+      <c r="C8">
+        <f t="shared" ref="C8:E8" si="1">C7*C2</f>
+        <v>6395</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>7674</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>8953</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="2">
+        <f>3.1*B7</f>
+        <v>3964.9</v>
+      </c>
+      <c r="C9" s="2">
+        <f t="shared" ref="C9:E9" si="2">3.1*C7</f>
+        <v>3964.9</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="2"/>
+        <v>3964.9</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="2"/>
+        <v>3964.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>3617</v>
+      </c>
+      <c r="C10">
+        <v>3617</v>
+      </c>
+      <c r="D10">
+        <v>3617</v>
+      </c>
+      <c r="E10">
+        <v>3617</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -3742,20 +4510,16 @@
         <v>26</v>
       </c>
       <c r="B12">
-        <f>2160</f>
-        <v>2160</v>
+        <v>1400</v>
       </c>
       <c r="C12">
-        <f>2160</f>
-        <v>2160</v>
+        <v>1400</v>
       </c>
       <c r="D12">
-        <f>2160</f>
-        <v>2160</v>
+        <v>1400</v>
       </c>
       <c r="E12">
-        <f>2160</f>
-        <v>2160</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -3784,20 +4548,20 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <f>B9-B10-B11-B12+B13</f>
-        <v>2247</v>
+        <f>B10-B11-B12+B13</f>
+        <v>3084</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:E14" si="3">C9-C10-C11-C12+C13</f>
-        <v>2247</v>
+        <f t="shared" ref="C14:E14" si="3">C10-C11-C12+C13</f>
+        <v>3084</v>
       </c>
       <c r="D14">
         <f t="shared" si="3"/>
-        <v>2247</v>
+        <v>3084</v>
       </c>
       <c r="E14">
         <f t="shared" si="3"/>
-        <v>2247</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -3805,20 +4569,20 @@
         <v>30</v>
       </c>
       <c r="B15">
-        <f>B7-B14</f>
-        <v>1949</v>
+        <f>B8-B14</f>
+        <v>2032</v>
       </c>
       <c r="C15">
-        <f t="shared" ref="C15:E15" si="4">C7-C14</f>
-        <v>2998</v>
+        <f>C8-C14</f>
+        <v>3311</v>
       </c>
       <c r="D15">
-        <f t="shared" si="4"/>
-        <v>4047</v>
+        <f>D8-D14</f>
+        <v>4590</v>
       </c>
       <c r="E15">
-        <f t="shared" si="4"/>
-        <v>5096</v>
+        <f>E8-E14</f>
+        <v>5869</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3873,15 +4637,15 @@
         <v>1875</v>
       </c>
       <c r="C19" s="8">
-        <f t="shared" ref="C19:E19" si="5">C17*C18</f>
+        <f t="shared" ref="C19:E19" si="4">C17*C18</f>
         <v>1875</v>
       </c>
       <c r="D19" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1875</v>
       </c>
       <c r="E19" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1875</v>
       </c>
     </row>
@@ -3894,15 +4658,15 @@
         <v>2.5</v>
       </c>
       <c r="C20" s="8">
-        <f t="shared" ref="C20:E20" si="6">2.5</f>
+        <f t="shared" ref="C20:E20" si="5">2.5</f>
         <v>2.5</v>
       </c>
       <c r="D20" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.5</v>
       </c>
       <c r="E20" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.5</v>
       </c>
     </row>
@@ -3915,15 +4679,15 @@
         <v>312.5</v>
       </c>
       <c r="C21" s="10">
-        <f t="shared" ref="C21:E21" si="7">C18*C20</f>
+        <f t="shared" ref="C21:E21" si="6">C18*C20</f>
         <v>312.5</v>
       </c>
       <c r="D21" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>312.5</v>
       </c>
       <c r="E21" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>312.5</v>
       </c>
     </row>
@@ -3936,15 +4700,15 @@
         <v>1562.5</v>
       </c>
       <c r="C22" s="10">
-        <f t="shared" ref="C22:E22" si="8">C19-C21</f>
+        <f t="shared" ref="C22:E22" si="7">C19-C21</f>
         <v>1562.5</v>
       </c>
       <c r="D22" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1562.5</v>
       </c>
       <c r="E22" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1562.5</v>
       </c>
     </row>
@@ -3978,15 +4742,15 @@
         <v>156.25</v>
       </c>
       <c r="C24" s="2">
-        <f t="shared" ref="C24:E24" si="9">C23*C22</f>
+        <f t="shared" ref="C24:E24" si="8">C23*C22</f>
         <v>156.25</v>
       </c>
       <c r="D24" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>156.25</v>
       </c>
       <c r="E24" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>156.25</v>
       </c>
     </row>
@@ -4001,410 +4765,309 @@
     </row>
     <row r="26" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="8">
-        <v>19</v>
-      </c>
-      <c r="C26" s="8">
-        <v>19</v>
-      </c>
-      <c r="D26" s="8">
-        <v>19</v>
-      </c>
-      <c r="E26" s="8">
-        <v>19</v>
+        <v>4</v>
+      </c>
+      <c r="B26" s="10">
+        <v>3640</v>
+      </c>
+      <c r="C26" s="10">
+        <v>3640</v>
+      </c>
+      <c r="D26" s="10">
+        <v>3640</v>
+      </c>
+      <c r="E26" s="10">
+        <v>3640</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="8">
-        <v>480</v>
-      </c>
-      <c r="C27" s="8">
-        <v>480</v>
-      </c>
-      <c r="D27" s="8">
-        <v>480</v>
-      </c>
-      <c r="E27" s="8">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" s="8">
-        <f>B26*B27</f>
-        <v>9120</v>
-      </c>
-      <c r="C28" s="8">
-        <f t="shared" ref="C28:E28" si="10">C26*C27</f>
-        <v>9120</v>
-      </c>
-      <c r="D28" s="8">
+        <v>37</v>
+      </c>
+      <c r="B27" s="9">
+        <f>17.5%</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="C27" s="9">
+        <f t="shared" ref="C27:E27" si="9">17.5%</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="D27" s="9">
+        <f t="shared" si="9"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="E27" s="9">
+        <f t="shared" si="9"/>
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28">
+        <f>B27*B26</f>
+        <v>637</v>
+      </c>
+      <c r="C28">
+        <f t="shared" ref="C28:E28" si="10">C27*C26</f>
+        <v>637</v>
+      </c>
+      <c r="D28">
         <f t="shared" si="10"/>
-        <v>9120</v>
-      </c>
-      <c r="E28" s="8">
+        <v>637</v>
+      </c>
+      <c r="E28">
         <f t="shared" si="10"/>
-        <v>9120</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="8">
-        <f>7</f>
+        <v>637</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="2">
+        <f>B15+B24+B28</f>
+        <v>2825.25</v>
+      </c>
+      <c r="C29" s="2">
+        <f>C15+C24+C28</f>
+        <v>4104.25</v>
+      </c>
+      <c r="D29" s="2">
+        <f>D15+D24+D28</f>
+        <v>5383.25</v>
+      </c>
+      <c r="E29" s="2">
+        <f>E15+E24+E28</f>
+        <v>6662.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="2">
+        <f>759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="C30" s="2">
+        <f t="shared" ref="C30:E30" si="11">759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" si="11"/>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="E30" s="2">
+        <f t="shared" si="11"/>
+        <v>759.20990500000005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="2">
+        <f>523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="C31" s="2">
+        <f t="shared" ref="C31:E31" si="12">523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="D31" s="2">
+        <f t="shared" si="12"/>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="E31" s="2">
+        <f t="shared" si="12"/>
+        <v>523.24060299999996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="2">
+        <f>B30-B31</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="C32" s="2">
+        <f t="shared" ref="C32:E32" si="13">C30-C31</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="D32" s="2">
+        <f t="shared" si="13"/>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="E32" s="2">
+        <f t="shared" si="13"/>
+        <v>235.96930200000008</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="8">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="D29" s="8">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="E29" s="8">
-        <f>7</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="10">
-        <f>B27*B29</f>
-        <v>3360</v>
-      </c>
-      <c r="C30" s="10">
-        <f t="shared" ref="C30:E30" si="11">C27*C29</f>
-        <v>3360</v>
-      </c>
-      <c r="D30" s="10">
-        <f t="shared" si="11"/>
-        <v>3360</v>
-      </c>
-      <c r="E30" s="10">
-        <f t="shared" si="11"/>
-        <v>3360</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="10">
-        <f>B28-B30</f>
-        <v>5760</v>
-      </c>
-      <c r="C31" s="10">
-        <f t="shared" ref="C31:E31" si="12">C28-C30</f>
-        <v>5760</v>
-      </c>
-      <c r="D31" s="10">
-        <f t="shared" si="12"/>
-        <v>5760</v>
-      </c>
-      <c r="E31" s="10">
-        <f t="shared" si="12"/>
-        <v>5760</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="9">
-        <f>10%</f>
-        <v>0.1</v>
-      </c>
-      <c r="C32" s="9">
-        <f>10%</f>
-        <v>0.1</v>
-      </c>
-      <c r="D32" s="9">
-        <f>10%</f>
-        <v>0.1</v>
-      </c>
-      <c r="E32" s="9">
-        <f>10%</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33">
-        <f>B32*B31</f>
-        <v>576</v>
-      </c>
-      <c r="C33">
-        <f t="shared" ref="C33:E33" si="13">C32*C31</f>
-        <v>576</v>
-      </c>
-      <c r="D33">
-        <f t="shared" si="13"/>
-        <v>576</v>
-      </c>
-      <c r="E33">
-        <f t="shared" si="13"/>
-        <v>576</v>
+      <c r="B33" s="1">
+        <f>B29/B32</f>
+        <v>11.972955702517606</v>
+      </c>
+      <c r="C33" s="1">
+        <f t="shared" ref="C33:E33" si="14">C29/C32</f>
+        <v>17.393152266899524</v>
+      </c>
+      <c r="D33" s="1">
+        <f t="shared" si="14"/>
+        <v>22.813348831281445</v>
+      </c>
+      <c r="E33" s="1">
+        <f t="shared" si="14"/>
+        <v>28.233545395663363</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="2">
-        <f>B15+B24+B33</f>
-        <v>2681.25</v>
-      </c>
-      <c r="C34" s="2">
-        <f t="shared" ref="C34:E34" si="14">C15+C24+C33</f>
-        <v>3730.25</v>
-      </c>
-      <c r="D34" s="2">
-        <f t="shared" si="14"/>
-        <v>4779.25</v>
-      </c>
-      <c r="E34" s="2">
-        <f t="shared" si="14"/>
-        <v>5828.25</v>
+        <v>10</v>
+      </c>
+      <c r="B34">
+        <f>1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="C34">
+        <f t="shared" ref="C34:E34" si="15">1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="15"/>
+        <v>1.18</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="15"/>
+        <v>1.18</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="2">
-        <f>759209905/1000000</f>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="C35" s="2">
-        <f t="shared" ref="C35:E35" si="15">759209905/1000000</f>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="D35" s="2">
-        <f t="shared" si="15"/>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="E35" s="2">
-        <f t="shared" si="15"/>
-        <v>759.20990500000005</v>
+        <v>8</v>
+      </c>
+      <c r="B35" s="1">
+        <f>B33/B34</f>
+        <v>10.146572629252208</v>
+      </c>
+      <c r="C35" s="1">
+        <f t="shared" ref="C35:E35" si="16">C33/C34</f>
+        <v>14.739959548219936</v>
+      </c>
+      <c r="D35" s="1">
+        <f t="shared" si="16"/>
+        <v>19.333346467187667</v>
+      </c>
+      <c r="E35" s="1">
+        <f t="shared" si="16"/>
+        <v>23.926733386155394</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36" s="2">
-        <f>523240603/1000000</f>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="C36" s="2">
-        <f t="shared" ref="C36:E36" si="16">523240603/1000000</f>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="D36" s="2">
-        <f t="shared" si="16"/>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="E36" s="2">
-        <f t="shared" si="16"/>
-        <v>523.24060299999996</v>
+        <v>11</v>
+      </c>
+      <c r="B36">
+        <f>1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="C36">
+        <f t="shared" ref="C36:E36" si="17">1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="17"/>
+        <v>1.57</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="17"/>
+        <v>1.57</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="2">
-        <f>B35-B36</f>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="C37" s="2">
-        <f t="shared" ref="C37:E37" si="17">C35-C36</f>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="D37" s="2">
-        <f t="shared" si="17"/>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="E37" s="2">
-        <f t="shared" si="17"/>
-        <v>235.96930200000008</v>
+      <c r="A37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="1">
+        <f>B35+B36</f>
+        <v>11.716572629252209</v>
+      </c>
+      <c r="C37" s="1">
+        <f t="shared" ref="C37:E37" si="18">C35+C36</f>
+        <v>16.309959548219936</v>
+      </c>
+      <c r="D37" s="1">
+        <f t="shared" si="18"/>
+        <v>20.903346467187667</v>
+      </c>
+      <c r="E37" s="1">
+        <f t="shared" si="18"/>
+        <v>25.496733386155395</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="1">
-        <f>B34/B37</f>
-        <v>11.362706832094622</v>
-      </c>
-      <c r="C38" s="1">
-        <f t="shared" ref="C38:E38" si="18">C34/C37</f>
-        <v>15.808200339550941</v>
-      </c>
-      <c r="D38" s="1">
-        <f t="shared" si="18"/>
-        <v>20.253693847007263</v>
-      </c>
-      <c r="E38" s="1">
-        <f t="shared" si="18"/>
-        <v>24.699187354463582</v>
+      <c r="A38" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="2">
+        <f>B37*100</f>
+        <v>1171.6572629252209</v>
+      </c>
+      <c r="C38" s="2">
+        <f t="shared" ref="C38:E38" si="19">C37*100</f>
+        <v>1630.9959548219936</v>
+      </c>
+      <c r="D38" s="2">
+        <f t="shared" si="19"/>
+        <v>2090.3346467187666</v>
+      </c>
+      <c r="E38" s="2">
+        <f t="shared" si="19"/>
+        <v>2549.6733386155393</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B39">
-        <f>1.18</f>
-        <v>1.18</v>
+        <v>595</v>
       </c>
       <c r="C39">
-        <f t="shared" ref="C39:E39" si="19">1.18</f>
-        <v>1.18</v>
+        <v>595</v>
       </c>
       <c r="D39">
-        <f t="shared" si="19"/>
-        <v>1.18</v>
+        <v>595</v>
       </c>
       <c r="E39">
-        <f t="shared" si="19"/>
-        <v>1.18</v>
+        <v>595</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" s="1">
-        <f>B38/B39</f>
-        <v>9.6294125695717145</v>
-      </c>
-      <c r="C40" s="1">
-        <f t="shared" ref="C40:E40" si="20">C38/C39</f>
-        <v>13.396779948771984</v>
-      </c>
-      <c r="D40" s="1">
+      <c r="A40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="3">
+        <f>B38/B39-1</f>
+        <v>0.96917187046255626</v>
+      </c>
+      <c r="C40" s="3">
+        <f t="shared" ref="C40:E40" si="20">C38/C39-1</f>
+        <v>1.7411696719697369</v>
+      </c>
+      <c r="D40" s="3">
         <f t="shared" si="20"/>
-        <v>17.164147327972259</v>
-      </c>
-      <c r="E40" s="1">
+        <v>2.5131674734769187</v>
+      </c>
+      <c r="E40" s="3">
         <f t="shared" si="20"/>
-        <v>20.931514707172528</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41">
-        <f>1.57</f>
-        <v>1.57</v>
-      </c>
-      <c r="C41">
-        <f t="shared" ref="C41:E41" si="21">1.57</f>
-        <v>1.57</v>
-      </c>
-      <c r="D41">
-        <f t="shared" si="21"/>
-        <v>1.57</v>
-      </c>
-      <c r="E41">
-        <f t="shared" si="21"/>
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>22</v>
-      </c>
-      <c r="B42" s="1">
-        <f>B40+B41</f>
-        <v>11.199412569571715</v>
-      </c>
-      <c r="C42" s="1">
-        <f t="shared" ref="C42:E42" si="22">C40+C41</f>
-        <v>14.966779948771984</v>
-      </c>
-      <c r="D42" s="1">
-        <f t="shared" si="22"/>
-        <v>18.734147327972259</v>
-      </c>
-      <c r="E42" s="1">
-        <f t="shared" si="22"/>
-        <v>22.501514707172529</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B43" s="2">
-        <f>B42*100</f>
-        <v>1119.9412569571714</v>
-      </c>
-      <c r="C43" s="2">
-        <f t="shared" ref="C43:E43" si="23">C42*100</f>
-        <v>1496.6779948771984</v>
-      </c>
-      <c r="D43" s="2">
-        <f t="shared" si="23"/>
-        <v>1873.414732797226</v>
-      </c>
-      <c r="E43" s="2">
-        <f t="shared" si="23"/>
-        <v>2250.1514707172528</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44">
-        <v>595</v>
-      </c>
-      <c r="C44">
-        <v>595</v>
-      </c>
-      <c r="D44">
-        <v>595</v>
-      </c>
-      <c r="E44">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B45" s="3">
-        <f>B43/B44-1</f>
-        <v>0.88225421337339727</v>
-      </c>
-      <c r="C45" s="3">
-        <f t="shared" ref="C45:E45" si="24">C43/C44-1</f>
-        <v>1.5154252014742831</v>
-      </c>
-      <c r="D45" s="3">
-        <f t="shared" si="24"/>
-        <v>2.1485961895751697</v>
-      </c>
-      <c r="E45" s="3">
-        <f t="shared" si="24"/>
-        <v>2.7817671776760551</v>
+        <v>3.2851652749840996</v>
       </c>
     </row>
   </sheetData>
@@ -4418,7 +5081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C948590-68A6-476D-B63A-653E4BD7F956}">
   <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
+++ b/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Value Investing\Zegona Communications Plc - ZEG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF5FFAB-C3A4-4A1A-BA06-35DB25791329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFB4FA3-1ED0-4353-AEFE-FCB3438B3E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15600" firstSheet="3" activeTab="6" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
   </bookViews>
   <sheets>
     <sheet name="Dividendo parcial + Preferentes" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,9 @@
     <sheet name="Reestructuracion (+Div+Pre)" sheetId="4" r:id="rId3"/>
     <sheet name="Venta FibreCo MasOrange" sheetId="8" r:id="rId4"/>
     <sheet name="Venta FibreCo MasOrange + Reest" sheetId="9" r:id="rId5"/>
-    <sheet name="Gabriel Castro" sheetId="7" r:id="rId6"/>
+    <sheet name="Venta 2 FibreCos" sheetId="10" r:id="rId6"/>
+    <sheet name="Venta 2 FibreCos + Reestructura" sheetId="11" r:id="rId7"/>
+    <sheet name="Gabriel Castro" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="43">
   <si>
     <t>EV/EBITDAaL</t>
   </si>
@@ -378,7 +380,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -406,13 +408,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -444,7 +439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -453,22 +448,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -812,13 +806,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1106,150 +1100,150 @@
         <v>5150</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="7">
         <v>15</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>15</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>15</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="7">
         <v>125</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>125</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>125</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="7">
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <f>B17*B18</f>
         <v>1875</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <f t="shared" ref="C19:E19" si="5">C17*C18</f>
         <v>1875</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <f t="shared" si="5"/>
         <v>1875</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="7">
         <f t="shared" si="5"/>
         <v>1875</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="7">
         <f>2.5</f>
         <v>2.5</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <f t="shared" ref="C20:E20" si="6">2.5</f>
         <v>2.5</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="7">
         <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <f>B18*B20</f>
         <v>312.5</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <f t="shared" ref="C21:E21" si="7">C18*C20</f>
         <v>312.5</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <f t="shared" si="7"/>
         <v>312.5</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <f t="shared" si="7"/>
         <v>312.5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <f>B19-B21</f>
         <v>1562.5</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <f t="shared" ref="C22:E22" si="8">C19-C21</f>
         <v>1562.5</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <f t="shared" si="8"/>
         <v>1562.5</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <f t="shared" si="8"/>
         <v>1562.5</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
@@ -1275,150 +1269,150 @@
         <v>156.25</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="7">
         <v>15</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="7">
         <v>15</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="7">
         <v>15</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="7">
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="7">
         <v>480</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="7">
         <v>480</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="7">
         <v>480</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="7">
         <v>480</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="7">
         <f>B26*B27</f>
         <v>7200</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="7">
         <f t="shared" ref="C28:E28" si="10">C26*C27</f>
         <v>7200</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="7">
         <f t="shared" si="10"/>
         <v>7200</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="7">
         <f t="shared" si="10"/>
         <v>7200</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="7">
         <f>7</f>
         <v>7</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="7">
         <f>7</f>
         <v>7</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="7">
         <f>7</f>
         <v>7</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="7">
         <f>7</f>
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="9">
         <f>B27*B29</f>
         <v>3360</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="9">
         <f t="shared" ref="C30:E30" si="11">C27*C29</f>
         <v>3360</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="9">
         <f t="shared" si="11"/>
         <v>3360</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="9">
         <f t="shared" si="11"/>
         <v>3360</v>
       </c>
     </row>
-    <row r="31" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="9">
         <f>B28-B30</f>
         <v>3840</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="9">
         <f t="shared" ref="C31:E31" si="12">C28-C30</f>
         <v>3840</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <f t="shared" si="12"/>
         <v>3840</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="9">
         <f t="shared" si="12"/>
         <v>3840</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
@@ -1609,7 +1603,7 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
+      <c r="A42" t="s">
         <v>41</v>
       </c>
       <c r="B42" s="1">
@@ -1710,13 +1704,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2004,150 +1998,150 @@
         <v>5096</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="7">
         <v>15</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>15</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>15</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="7">
         <v>125</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>125</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>125</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="7">
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <f>B17*B18</f>
         <v>1875</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <f t="shared" ref="C19:E19" si="5">C17*C18</f>
         <v>1875</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <f t="shared" si="5"/>
         <v>1875</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="7">
         <f t="shared" si="5"/>
         <v>1875</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="7">
         <f>2.5</f>
         <v>2.5</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <f t="shared" ref="C20:E20" si="6">2.5</f>
         <v>2.5</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="7">
         <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <f>B18*B20</f>
         <v>312.5</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <f t="shared" ref="C21:E21" si="7">C18*C20</f>
         <v>312.5</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <f t="shared" si="7"/>
         <v>312.5</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <f t="shared" si="7"/>
         <v>312.5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <f>B19-B21</f>
         <v>1562.5</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <f t="shared" ref="C22:E22" si="8">C19-C21</f>
         <v>1562.5</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <f t="shared" si="8"/>
         <v>1562.5</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <f t="shared" si="8"/>
         <v>1562.5</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
@@ -2173,150 +2167,150 @@
         <v>156.25</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="7">
         <v>19</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="7">
         <v>19</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="7">
         <v>19</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="7">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="7">
         <v>480</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="7">
         <v>480</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="7">
         <v>480</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="7">
         <v>480</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="7">
         <f>B26*B27</f>
         <v>9120</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="7">
         <f t="shared" ref="C28" si="10">C26*C27</f>
         <v>9120</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="7">
         <f t="shared" ref="D28" si="11">D26*D27</f>
         <v>9120</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="7">
         <f t="shared" ref="E28" si="12">E26*E27</f>
         <v>9120</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="7">
         <f>7</f>
         <v>7</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="7">
         <f>7</f>
         <v>7</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="7">
         <f>7</f>
         <v>7</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="7">
         <f>7</f>
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="9">
         <f>B27*B29</f>
         <v>3360</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="9">
         <f t="shared" ref="C30" si="13">C27*C29</f>
         <v>3360</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="9">
         <f t="shared" ref="D30" si="14">D27*D29</f>
         <v>3360</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="9">
         <f t="shared" ref="E30" si="15">E27*E29</f>
         <v>3360</v>
       </c>
     </row>
-    <row r="31" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="9">
         <f>B28-B30</f>
         <v>5760</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="9">
         <f t="shared" ref="C31" si="16">C28-C30</f>
         <v>5760</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <f t="shared" ref="D31" si="17">D28-D30</f>
         <v>5760</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="9">
         <f t="shared" ref="E31" si="18">E28-E30</f>
         <v>5760</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
@@ -2612,13 +2606,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2923,150 +2917,150 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="7">
         <v>15</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>15</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>15</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="7">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <v>125</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <v>125</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>125</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="7">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="7">
         <f>B18*B19</f>
         <v>1875</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <f t="shared" ref="C20:E20" si="5">C18*C19</f>
         <v>1875</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <f t="shared" si="5"/>
         <v>1875</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="7">
         <f t="shared" si="5"/>
         <v>1875</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="7">
         <f>2.5</f>
         <v>2.5</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="7">
         <f t="shared" ref="C21:E21" si="6">2.5</f>
         <v>2.5</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="7">
         <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <f>B19*B21</f>
         <v>312.5</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <f t="shared" ref="C22:E22" si="7">C19*C21</f>
         <v>312.5</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <f t="shared" si="7"/>
         <v>312.5</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <f t="shared" si="7"/>
         <v>312.5</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="9">
         <f>B20-B22</f>
         <v>1562.5</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <f t="shared" ref="C23:E23" si="8">C20-C22</f>
         <v>1562.5</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <f t="shared" si="8"/>
         <v>1562.5</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="9">
         <f t="shared" si="8"/>
         <v>1562.5</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
@@ -3092,150 +3086,150 @@
         <v>156.25</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="7">
         <v>15</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="7">
         <v>15</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="7">
         <v>15</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="7">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="7">
         <v>480</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="7">
         <v>480</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="7">
         <v>480</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="7">
         <v>480</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="7">
         <f>B27*B28</f>
         <v>7200</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="7">
         <f t="shared" ref="C29:E29" si="10">C27*C28</f>
         <v>7200</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="7">
         <f t="shared" si="10"/>
         <v>7200</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="7">
         <f t="shared" si="10"/>
         <v>7200</v>
       </c>
     </row>
-    <row r="30" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="7">
         <f>7</f>
         <v>7</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="7">
         <f>7</f>
         <v>7</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="7">
         <f>7</f>
         <v>7</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="7">
         <f>7</f>
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="9">
         <f>B28*B30</f>
         <v>3360</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="9">
         <f t="shared" ref="C31:E31" si="11">C28*C30</f>
         <v>3360</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <f t="shared" si="11"/>
         <v>3360</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="9">
         <f t="shared" si="11"/>
         <v>3360</v>
       </c>
     </row>
-    <row r="32" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="9">
         <f>B29-B31</f>
         <v>3840</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="9">
         <f t="shared" ref="C32:E32" si="12">C29-C31</f>
         <v>3840</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="9">
         <f t="shared" si="12"/>
         <v>3840</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="9">
         <f t="shared" si="12"/>
         <v>3840</v>
       </c>
     </row>
-    <row r="33" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
@@ -3430,7 +3424,7 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
+      <c r="A43" t="s">
         <v>41</v>
       </c>
       <c r="B43" s="1">
@@ -3531,13 +3525,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -3796,150 +3790,150 @@
         <v>4259</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+    </row>
+    <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <v>15</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <v>15</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <v>15</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="7">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="7">
         <v>125</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>125</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>125</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="7">
         <f>B16*B17</f>
         <v>1875</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <f t="shared" ref="C18:E18" si="4">C16*C17</f>
         <v>1875</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <f t="shared" si="4"/>
         <v>1875</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="7">
         <f t="shared" si="4"/>
         <v>1875</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <f>2.5</f>
         <v>2.5</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <f t="shared" ref="C19:E19" si="5">2.5</f>
         <v>2.5</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <f t="shared" si="5"/>
         <v>2.5</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="7">
         <f t="shared" si="5"/>
         <v>2.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <f>B17*B19</f>
         <v>312.5</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <f t="shared" ref="C20:E20" si="6">C17*C19</f>
         <v>312.5</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <f t="shared" si="6"/>
         <v>312.5</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="9">
         <f t="shared" si="6"/>
         <v>312.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <f>B18-B20</f>
         <v>1562.5</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <f t="shared" ref="C21:E21" si="7">C18-C20</f>
         <v>1562.5</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <f t="shared" si="7"/>
         <v>1562.5</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <f t="shared" si="7"/>
         <v>1562.5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
@@ -3965,49 +3959,49 @@
         <v>156.25</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+    </row>
+    <row r="25" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="9">
         <v>3640</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="9">
         <v>3640</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <v>3640</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="9">
         <v>3640</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="8">
         <f>17.5%</f>
         <v>0.17499999999999999</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="8">
         <f t="shared" ref="C26:E26" si="9">17.5%</f>
         <v>0.17499999999999999</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="8">
         <f t="shared" si="9"/>
         <v>0.17499999999999999</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="8">
         <f t="shared" si="9"/>
         <v>0.17499999999999999</v>
       </c>
@@ -4303,13 +4297,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -4585,150 +4579,150 @@
         <v>5869</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="7">
         <v>15</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>15</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>15</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="7">
         <v>125</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>125</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>125</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="7">
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <f>B17*B18</f>
         <v>1875</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <f t="shared" ref="C19:E19" si="4">C17*C18</f>
         <v>1875</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <f t="shared" si="4"/>
         <v>1875</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="7">
         <f t="shared" si="4"/>
         <v>1875</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="7">
         <f>2.5</f>
         <v>2.5</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <f t="shared" ref="C20:E20" si="5">2.5</f>
         <v>2.5</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <f t="shared" si="5"/>
         <v>2.5</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="7">
         <f t="shared" si="5"/>
         <v>2.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <f>B18*B20</f>
         <v>312.5</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <f t="shared" ref="C21:E21" si="6">C18*C20</f>
         <v>312.5</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <f t="shared" si="6"/>
         <v>312.5</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <f t="shared" si="6"/>
         <v>312.5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <f>B19-B21</f>
         <v>1562.5</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <f t="shared" ref="C22:E22" si="7">C19-C21</f>
         <v>1562.5</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <f t="shared" si="7"/>
         <v>1562.5</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <f t="shared" si="7"/>
         <v>1562.5</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="8">
         <f>10%</f>
         <v>0.1</v>
       </c>
@@ -4754,49 +4748,49 @@
         <v>156.25</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="9">
         <v>3640</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="9">
         <v>3640</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="9">
         <v>3640</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="9">
         <v>3640</v>
       </c>
     </row>
-    <row r="27" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="8">
         <f>17.5%</f>
         <v>0.17499999999999999</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="8">
         <f t="shared" ref="C27:E27" si="9">17.5%</f>
         <v>0.17499999999999999</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="8">
         <f t="shared" si="9"/>
         <v>0.17499999999999999</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="8">
         <f t="shared" si="9"/>
         <v>0.17499999999999999</v>
       </c>
@@ -5082,6 +5076,1441 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74366883-82BB-4118-B928-54EC8BE46093}">
+  <dimension ref="A1:E36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="49.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1236</v>
+      </c>
+      <c r="C3">
+        <v>1236</v>
+      </c>
+      <c r="D3">
+        <v>1236</v>
+      </c>
+      <c r="E3">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="C4">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="D4">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="E4">
+        <f>47</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="C5">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="D5">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="E5">
+        <f>140</f>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <f>B3-B4-B5</f>
+        <v>1049</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:E6" si="0">C3-C4-C5</f>
+        <v>1049</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>1049</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>B6*B2</f>
+        <v>4196</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:E7" si="1">C6*C2</f>
+        <v>5245</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>6294</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>7343</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="2">
+        <f>3.1*B6</f>
+        <v>3251.9</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" ref="C8:E8" si="2">3.1*C6</f>
+        <v>3251.9</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="2"/>
+        <v>3251.9</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="2"/>
+        <v>3251.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>3617</v>
+      </c>
+      <c r="C9">
+        <v>3617</v>
+      </c>
+      <c r="D9">
+        <v>3617</v>
+      </c>
+      <c r="E9">
+        <v>3617</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="C10">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="D10">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="E10">
+        <f>400</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
+        <v>1400</v>
+      </c>
+      <c r="C11">
+        <v>1400</v>
+      </c>
+      <c r="D11">
+        <v>1400</v>
+      </c>
+      <c r="E11">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="C12">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="D12">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="E12">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <f>B9-B10-B11+B12</f>
+        <v>3222</v>
+      </c>
+      <c r="C13">
+        <f t="shared" ref="C13:E13" si="3">C9-C10-C11+C12</f>
+        <v>3222</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="3"/>
+        <v>3222</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="3"/>
+        <v>3222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14">
+        <f>B7-B13</f>
+        <v>974</v>
+      </c>
+      <c r="C14">
+        <f>C7-C13</f>
+        <v>2023</v>
+      </c>
+      <c r="D14">
+        <f>D7-D13</f>
+        <v>3072</v>
+      </c>
+      <c r="E14">
+        <f>E7-E13</f>
+        <v>4121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+    </row>
+    <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1250</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1250</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1250</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="9">
+        <v>0</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="9">
+        <f>B16-B17</f>
+        <v>1250</v>
+      </c>
+      <c r="C18" s="9">
+        <f t="shared" ref="C18:E18" si="4">C16-C17</f>
+        <v>1250</v>
+      </c>
+      <c r="D18" s="9">
+        <f t="shared" si="4"/>
+        <v>1250</v>
+      </c>
+      <c r="E18" s="9">
+        <f t="shared" si="4"/>
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="8">
+        <f>0.05</f>
+        <v>0.05</v>
+      </c>
+      <c r="C19" s="8">
+        <f t="shared" ref="C19:E19" si="5">0.05</f>
+        <v>0.05</v>
+      </c>
+      <c r="D19" s="8">
+        <f t="shared" si="5"/>
+        <v>0.05</v>
+      </c>
+      <c r="E19" s="8">
+        <f t="shared" si="5"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="2">
+        <f>B19*B18</f>
+        <v>62.5</v>
+      </c>
+      <c r="C20" s="2">
+        <f t="shared" ref="C20:E20" si="6">C19*C18</f>
+        <v>62.5</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" si="6"/>
+        <v>62.5</v>
+      </c>
+      <c r="E20" s="2">
+        <f t="shared" si="6"/>
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="9">
+        <v>3640</v>
+      </c>
+      <c r="C22" s="9">
+        <v>3640</v>
+      </c>
+      <c r="D22" s="9">
+        <v>3640</v>
+      </c>
+      <c r="E22" s="9">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="8">
+        <f>17.5%</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="C23" s="8">
+        <f t="shared" ref="C23:E23" si="7">17.5%</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="D23" s="8">
+        <f t="shared" si="7"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="E23" s="8">
+        <f t="shared" si="7"/>
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24">
+        <f>B23*B22</f>
+        <v>637</v>
+      </c>
+      <c r="C24">
+        <f t="shared" ref="C24:E24" si="8">C23*C22</f>
+        <v>637</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="8"/>
+        <v>637</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="8"/>
+        <v>637</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="2">
+        <f>B14+B20+B24</f>
+        <v>1673.5</v>
+      </c>
+      <c r="C25" s="2">
+        <f>C14+C20+C24</f>
+        <v>2722.5</v>
+      </c>
+      <c r="D25" s="2">
+        <f>D14+D20+D24</f>
+        <v>3771.5</v>
+      </c>
+      <c r="E25" s="2">
+        <f>E14+E20+E24</f>
+        <v>4820.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="2">
+        <f>759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="C26" s="2">
+        <f t="shared" ref="C26:E26" si="9">759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="9"/>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="E26" s="2">
+        <f t="shared" si="9"/>
+        <v>759.20990500000005</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <f>523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="C27" s="2">
+        <f t="shared" ref="C27:E27" si="10">523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="10"/>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="E27" s="2">
+        <f t="shared" si="10"/>
+        <v>523.24060299999996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="2">
+        <f>B26-B27</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="C28" s="2">
+        <f t="shared" ref="C28:E28" si="11">C26-C27</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="D28" s="2">
+        <f t="shared" si="11"/>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="E28" s="2">
+        <f t="shared" si="11"/>
+        <v>235.96930200000008</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="1">
+        <f>B25/B28</f>
+        <v>7.0920241989782191</v>
+      </c>
+      <c r="C29" s="1">
+        <f t="shared" ref="C29:E29" si="12">C25/C28</f>
+        <v>11.537517706434539</v>
+      </c>
+      <c r="D29" s="1">
+        <f t="shared" si="12"/>
+        <v>15.983011213890858</v>
+      </c>
+      <c r="E29" s="1">
+        <f t="shared" si="12"/>
+        <v>20.428504721347178</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30">
+        <f>1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="C30">
+        <f t="shared" ref="C30:E30" si="13">1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="13"/>
+        <v>1.18</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="13"/>
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="1">
+        <f>B29/B30</f>
+        <v>6.0101899991340844</v>
+      </c>
+      <c r="C31" s="1">
+        <f t="shared" ref="C31:E31" si="14">C29/C30</f>
+        <v>9.7775573783343557</v>
+      </c>
+      <c r="D31" s="1">
+        <f t="shared" si="14"/>
+        <v>13.544924757534627</v>
+      </c>
+      <c r="E31" s="1">
+        <f t="shared" si="14"/>
+        <v>17.312292136734897</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <f>1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="C32">
+        <f t="shared" ref="C32:E32" si="15">1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="15"/>
+        <v>1.57</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="15"/>
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="1">
+        <f>B31+B32</f>
+        <v>7.5801899991340846</v>
+      </c>
+      <c r="C33" s="1">
+        <f t="shared" ref="C33:E33" si="16">C31+C32</f>
+        <v>11.347557378334356</v>
+      </c>
+      <c r="D33" s="1">
+        <f t="shared" si="16"/>
+        <v>15.114924757534627</v>
+      </c>
+      <c r="E33" s="1">
+        <f t="shared" si="16"/>
+        <v>18.882292136734897</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="2">
+        <f>B33*100</f>
+        <v>758.01899991340849</v>
+      </c>
+      <c r="C34" s="2">
+        <f t="shared" ref="C34:E34" si="17">C33*100</f>
+        <v>1134.7557378334357</v>
+      </c>
+      <c r="D34" s="2">
+        <f t="shared" si="17"/>
+        <v>1511.4924757534627</v>
+      </c>
+      <c r="E34" s="2">
+        <f t="shared" si="17"/>
+        <v>1888.2292136734898</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35">
+        <v>595</v>
+      </c>
+      <c r="C35">
+        <v>595</v>
+      </c>
+      <c r="D35">
+        <v>595</v>
+      </c>
+      <c r="E35">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" s="3">
+        <f>B34/B35-1</f>
+        <v>0.27398151245950997</v>
+      </c>
+      <c r="C36" s="3">
+        <f t="shared" ref="C36:E36" si="18">C34/C35-1</f>
+        <v>0.90715250056039598</v>
+      </c>
+      <c r="D36" s="3">
+        <f t="shared" si="18"/>
+        <v>1.540323488661282</v>
+      </c>
+      <c r="E36" s="3">
+        <f t="shared" si="18"/>
+        <v>2.1734944767621678</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A21:E21"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{625777CA-B562-420E-9376-E898EEA474C9}">
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="49.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1236</v>
+      </c>
+      <c r="C3">
+        <v>1236</v>
+      </c>
+      <c r="D3">
+        <v>1236</v>
+      </c>
+      <c r="E3">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>230</v>
+      </c>
+      <c r="C4">
+        <v>230</v>
+      </c>
+      <c r="D4">
+        <v>230</v>
+      </c>
+      <c r="E4">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="C5">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="D5">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="E5">
+        <f>47</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="C6">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="D6">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="E6">
+        <f>140</f>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <f>B3+B4-B5-B6</f>
+        <v>1279</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:E7" si="0">C3+C4-C5-C6</f>
+        <v>1279</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>1279</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <f>B7*B2</f>
+        <v>5116</v>
+      </c>
+      <c r="C8">
+        <f t="shared" ref="C8:E8" si="1">C7*C2</f>
+        <v>6395</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>7674</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>8953</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="2">
+        <f>3.1*B7</f>
+        <v>3964.9</v>
+      </c>
+      <c r="C9" s="2">
+        <f t="shared" ref="C9:E9" si="2">3.1*C7</f>
+        <v>3964.9</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="2"/>
+        <v>3964.9</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="2"/>
+        <v>3964.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>3617</v>
+      </c>
+      <c r="C10">
+        <v>3617</v>
+      </c>
+      <c r="D10">
+        <v>3617</v>
+      </c>
+      <c r="E10">
+        <v>3617</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="C11">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="D11">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="E11">
+        <f>400</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12">
+        <v>1400</v>
+      </c>
+      <c r="C12">
+        <v>1400</v>
+      </c>
+      <c r="D12">
+        <v>1400</v>
+      </c>
+      <c r="E12">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="C13">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="D13">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="E13">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <f>B10-B11-B12+B13</f>
+        <v>3222</v>
+      </c>
+      <c r="C14">
+        <f t="shared" ref="C14:E14" si="3">C10-C11-C12+C13</f>
+        <v>3222</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="3"/>
+        <v>3222</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="3"/>
+        <v>3222</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <f>B8-B14</f>
+        <v>1894</v>
+      </c>
+      <c r="C15">
+        <f>C8-C14</f>
+        <v>3173</v>
+      </c>
+      <c r="D15">
+        <f>D8-D14</f>
+        <v>4452</v>
+      </c>
+      <c r="E15">
+        <f>E8-E14</f>
+        <v>5731</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="7">
+        <v>1250</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1250</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1250</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="9">
+        <v>0</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="9">
+        <f>B17-B18</f>
+        <v>1250</v>
+      </c>
+      <c r="C19" s="9">
+        <f>C17-C18</f>
+        <v>1250</v>
+      </c>
+      <c r="D19" s="9">
+        <f>D17-D18</f>
+        <v>1250</v>
+      </c>
+      <c r="E19" s="9">
+        <f>E17-E18</f>
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+      <c r="C20" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+      <c r="D20" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+      <c r="E20" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="2">
+        <f>B20*B19</f>
+        <v>62.5</v>
+      </c>
+      <c r="C21" s="2">
+        <f t="shared" ref="C21:E21" si="4">C20*C19</f>
+        <v>62.5</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="4"/>
+        <v>62.5</v>
+      </c>
+      <c r="E21" s="2">
+        <f t="shared" si="4"/>
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+    </row>
+    <row r="23" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="9">
+        <v>3640</v>
+      </c>
+      <c r="C23" s="9">
+        <v>3640</v>
+      </c>
+      <c r="D23" s="9">
+        <v>3640</v>
+      </c>
+      <c r="E23" s="9">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="8">
+        <f>17.5%</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="C24" s="8">
+        <f t="shared" ref="C24:E24" si="5">17.5%</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="D24" s="8">
+        <f t="shared" si="5"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="E24" s="8">
+        <f t="shared" si="5"/>
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25">
+        <f>B24*B23</f>
+        <v>637</v>
+      </c>
+      <c r="C25">
+        <f t="shared" ref="C25:E25" si="6">C24*C23</f>
+        <v>637</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="6"/>
+        <v>637</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="6"/>
+        <v>637</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="2">
+        <f>B15+B21+B25</f>
+        <v>2593.5</v>
+      </c>
+      <c r="C26" s="2">
+        <f>C15+C21+C25</f>
+        <v>3872.5</v>
+      </c>
+      <c r="D26" s="2">
+        <f>D15+D21+D25</f>
+        <v>5151.5</v>
+      </c>
+      <c r="E26" s="2">
+        <f>E15+E21+E25</f>
+        <v>6430.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="2">
+        <f>759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="C27" s="2">
+        <f t="shared" ref="C27:E27" si="7">759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="7"/>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="E27" s="2">
+        <f t="shared" si="7"/>
+        <v>759.20990500000005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="2">
+        <f>523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="C28" s="2">
+        <f t="shared" ref="C28:E28" si="8">523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="D28" s="2">
+        <f t="shared" si="8"/>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="E28" s="2">
+        <f t="shared" si="8"/>
+        <v>523.24060299999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="2">
+        <f>B27-B28</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="C29" s="2">
+        <f t="shared" ref="C29:E29" si="9">C27-C28</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="D29" s="2">
+        <f t="shared" si="9"/>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="E29" s="2">
+        <f t="shared" si="9"/>
+        <v>235.96930200000008</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="1">
+        <f>B26/B29</f>
+        <v>10.990836426680616</v>
+      </c>
+      <c r="C30" s="1">
+        <f t="shared" ref="C30:E30" si="10">C26/C29</f>
+        <v>16.411032991062534</v>
+      </c>
+      <c r="D30" s="1">
+        <f t="shared" si="10"/>
+        <v>21.831229555444455</v>
+      </c>
+      <c r="E30" s="1">
+        <f t="shared" si="10"/>
+        <v>27.251426119826373</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31">
+        <f>1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="C31">
+        <f t="shared" ref="C31:E31" si="11">1.18</f>
+        <v>1.18</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="11"/>
+        <v>1.18</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="11"/>
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="1">
+        <f>B30/B31</f>
+        <v>9.3142681582039124</v>
+      </c>
+      <c r="C32" s="1">
+        <f t="shared" ref="C32:E32" si="12">C30/C31</f>
+        <v>13.90765507717164</v>
+      </c>
+      <c r="D32" s="1">
+        <f t="shared" si="12"/>
+        <v>18.501041996139371</v>
+      </c>
+      <c r="E32" s="1">
+        <f t="shared" si="12"/>
+        <v>23.094428915107098</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33">
+        <f>1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="C33">
+        <f t="shared" ref="C33:E33" si="13">1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="13"/>
+        <v>1.57</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="13"/>
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="1">
+        <f>B32+B33</f>
+        <v>10.884268158203913</v>
+      </c>
+      <c r="C34" s="1">
+        <f t="shared" ref="C34:E34" si="14">C32+C33</f>
+        <v>15.47765507717164</v>
+      </c>
+      <c r="D34" s="1">
+        <f t="shared" si="14"/>
+        <v>20.071041996139371</v>
+      </c>
+      <c r="E34" s="1">
+        <f t="shared" si="14"/>
+        <v>24.664428915107099</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="2">
+        <f>B34*100</f>
+        <v>1088.4268158203913</v>
+      </c>
+      <c r="C35" s="2">
+        <f t="shared" ref="C35:E35" si="15">C34*100</f>
+        <v>1547.7655077171639</v>
+      </c>
+      <c r="D35" s="2">
+        <f t="shared" si="15"/>
+        <v>2007.104199613937</v>
+      </c>
+      <c r="E35" s="2">
+        <f t="shared" si="15"/>
+        <v>2466.4428915107101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36">
+        <v>595</v>
+      </c>
+      <c r="C36">
+        <v>595</v>
+      </c>
+      <c r="D36">
+        <v>595</v>
+      </c>
+      <c r="E36">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="3">
+        <f>B35/B36-1</f>
+        <v>0.82928876608469126</v>
+      </c>
+      <c r="C37" s="3">
+        <f t="shared" ref="C37:E37" si="16">C35/C36-1</f>
+        <v>1.6012865675918722</v>
+      </c>
+      <c r="D37" s="3">
+        <f t="shared" si="16"/>
+        <v>2.3732843690990539</v>
+      </c>
+      <c r="E37" s="3">
+        <f t="shared" si="16"/>
+        <v>3.1452821706062357</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A22:E22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C948590-68A6-476D-B63A-653E4BD7F956}">
   <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
+++ b/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Value Investing\Zegona Communications Plc - ZEG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFB4FA3-1ED0-4353-AEFE-FCB3438B3E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3EDDC8-54FB-4CC3-BE0D-333D4A978676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15600" firstSheet="3" activeTab="6" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="7" activeTab="7" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
   </bookViews>
   <sheets>
     <sheet name="Dividendo parcial + Preferentes" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,8 @@
     <sheet name="Venta FibreCo MasOrange + Reest" sheetId="9" r:id="rId5"/>
     <sheet name="Venta 2 FibreCos" sheetId="10" r:id="rId6"/>
     <sheet name="Venta 2 FibreCos + Reestructura" sheetId="11" r:id="rId7"/>
-    <sheet name="Gabriel Castro" sheetId="7" r:id="rId8"/>
+    <sheet name="FibreCo Ret Capital Allocation" sheetId="12" r:id="rId8"/>
+    <sheet name="Gabriel Castro" sheetId="7" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="45">
   <si>
     <t>EV/EBITDAaL</t>
   </si>
@@ -374,6 +375,12 @@
   </si>
   <si>
     <t>Covenant financiero (3,1xEBITDAaL)</t>
+  </si>
+  <si>
+    <t>Recompra de acciones</t>
+  </si>
+  <si>
+    <t>Recompra de acciones (-)</t>
   </si>
 </sst>
 </file>
@@ -6511,6 +6518,774 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228A45E1-6A44-40F3-96A6-F2D7B83F7F63}">
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="49.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1236</v>
+      </c>
+      <c r="C3">
+        <v>1236</v>
+      </c>
+      <c r="D3">
+        <v>1236</v>
+      </c>
+      <c r="E3">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>230</v>
+      </c>
+      <c r="C4">
+        <v>230</v>
+      </c>
+      <c r="D4">
+        <v>230</v>
+      </c>
+      <c r="E4">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="C5">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="D5">
+        <f>47</f>
+        <v>47</v>
+      </c>
+      <c r="E5">
+        <f>47</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="C6">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="D6">
+        <f>140</f>
+        <v>140</v>
+      </c>
+      <c r="E6">
+        <f>140</f>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <f>B3+B4-B5-B6</f>
+        <v>1279</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:E7" si="0">C3+C4-C5-C6</f>
+        <v>1279</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>1279</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <f>B7*B2</f>
+        <v>5116</v>
+      </c>
+      <c r="C8">
+        <f t="shared" ref="C8:E8" si="1">C7*C2</f>
+        <v>6395</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>7674</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>8953</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="2">
+        <f>3.1*B7</f>
+        <v>3964.9</v>
+      </c>
+      <c r="C9" s="2">
+        <f t="shared" ref="C9:E9" si="2">3.1*C7</f>
+        <v>3964.9</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="2"/>
+        <v>3964.9</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="2"/>
+        <v>3964.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <f>3630</f>
+        <v>3630</v>
+      </c>
+      <c r="C10">
+        <f>3630</f>
+        <v>3630</v>
+      </c>
+      <c r="D10">
+        <f>3630</f>
+        <v>3630</v>
+      </c>
+      <c r="E10">
+        <f>3630</f>
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="C11">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="D11">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="E11">
+        <f>400</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12">
+        <v>1400</v>
+      </c>
+      <c r="C12">
+        <v>1400</v>
+      </c>
+      <c r="D12">
+        <v>1400</v>
+      </c>
+      <c r="E12">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <f>1415</f>
+        <v>1415</v>
+      </c>
+      <c r="C13">
+        <f>1415</f>
+        <v>1415</v>
+      </c>
+      <c r="D13">
+        <f>1415</f>
+        <v>1415</v>
+      </c>
+      <c r="E13">
+        <f>1415</f>
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14">
+        <v>200</v>
+      </c>
+      <c r="C14">
+        <v>200</v>
+      </c>
+      <c r="D14">
+        <v>200</v>
+      </c>
+      <c r="E14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <f>B10-B11-B12+B13+B14</f>
+        <v>3445</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:E15" si="3">C10-C11-C12+C13+C14</f>
+        <v>3445</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="3"/>
+        <v>3445</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="3"/>
+        <v>3445</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16">
+        <f>B8-B15</f>
+        <v>1671</v>
+      </c>
+      <c r="C16">
+        <f>C8-C15</f>
+        <v>2950</v>
+      </c>
+      <c r="D16">
+        <f>D8-D15</f>
+        <v>4229</v>
+      </c>
+      <c r="E16">
+        <f>E8-E15</f>
+        <v>5508</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1250</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1250</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1250</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="9">
+        <v>0</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="9">
+        <f>B18-B19</f>
+        <v>1250</v>
+      </c>
+      <c r="C20" s="9">
+        <f>C18-C19</f>
+        <v>1250</v>
+      </c>
+      <c r="D20" s="9">
+        <f>D18-D19</f>
+        <v>1250</v>
+      </c>
+      <c r="E20" s="9">
+        <f>E18-E19</f>
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+      <c r="C21" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+      <c r="D21" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+      <c r="E21" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="2">
+        <f>B21*B20</f>
+        <v>62.5</v>
+      </c>
+      <c r="C22" s="2">
+        <f t="shared" ref="C22:E22" si="4">C21*C20</f>
+        <v>62.5</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="4"/>
+        <v>62.5</v>
+      </c>
+      <c r="E22" s="2">
+        <f t="shared" si="4"/>
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="9">
+        <v>3640</v>
+      </c>
+      <c r="C24" s="9">
+        <v>3640</v>
+      </c>
+      <c r="D24" s="9">
+        <v>3640</v>
+      </c>
+      <c r="E24" s="9">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="8">
+        <f>17.5%</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="C25" s="8">
+        <f t="shared" ref="C25:E25" si="5">17.5%</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="D25" s="8">
+        <f t="shared" si="5"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="E25" s="8">
+        <f t="shared" si="5"/>
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26">
+        <f>B25*B24</f>
+        <v>637</v>
+      </c>
+      <c r="C26">
+        <f t="shared" ref="C26:E26" si="6">C25*C24</f>
+        <v>637</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="6"/>
+        <v>637</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="6"/>
+        <v>637</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="2">
+        <f>B16+B22+B26</f>
+        <v>2370.5</v>
+      </c>
+      <c r="C27" s="2">
+        <f>C16+C22+C26</f>
+        <v>3649.5</v>
+      </c>
+      <c r="D27" s="2">
+        <f>D16+D22+D26</f>
+        <v>4928.5</v>
+      </c>
+      <c r="E27" s="2">
+        <f>E16+E22+E26</f>
+        <v>6207.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="2">
+        <f>759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="C28" s="2">
+        <f t="shared" ref="C28:E28" si="7">759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="D28" s="2">
+        <f t="shared" si="7"/>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="E28" s="2">
+        <f t="shared" si="7"/>
+        <v>759.20990500000005</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="2">
+        <f>523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="C29" s="2">
+        <f t="shared" ref="C29:E30" si="8">523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="D29" s="2">
+        <f t="shared" si="8"/>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="E29" s="2">
+        <f t="shared" si="8"/>
+        <v>523.24060299999996</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="2">
+        <f>12500000/1000000</f>
+        <v>12.5</v>
+      </c>
+      <c r="C30" s="2">
+        <f t="shared" ref="C30:E30" si="9">12500000/1000000</f>
+        <v>12.5</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" si="9"/>
+        <v>12.5</v>
+      </c>
+      <c r="E30" s="2">
+        <f t="shared" si="9"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="2">
+        <f>B28-B29-B30</f>
+        <v>223.46930200000008</v>
+      </c>
+      <c r="C31" s="2">
+        <f t="shared" ref="C31:E31" si="10">C28-C29-C30</f>
+        <v>223.46930200000008</v>
+      </c>
+      <c r="D31" s="2">
+        <f t="shared" si="10"/>
+        <v>223.46930200000008</v>
+      </c>
+      <c r="E31" s="2">
+        <f t="shared" si="10"/>
+        <v>223.46930200000008</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="1">
+        <f>B27/B31</f>
+        <v>10.607720965629539</v>
+      </c>
+      <c r="C32" s="1">
+        <f t="shared" ref="C32:E32" si="11">C27/C31</f>
+        <v>16.33110215737819</v>
+      </c>
+      <c r="D32" s="1">
+        <f t="shared" si="11"/>
+        <v>22.054483349126844</v>
+      </c>
+      <c r="E32" s="1">
+        <f t="shared" si="11"/>
+        <v>27.777864540875495</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33">
+        <f>1.15</f>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="C33">
+        <f t="shared" ref="C33:E33" si="12">1.15</f>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="12"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="12"/>
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="1">
+        <f>B32/B33</f>
+        <v>9.2241051875039481</v>
+      </c>
+      <c r="C34" s="1">
+        <f t="shared" ref="C34:E34" si="13">C32/C33</f>
+        <v>14.200958397720166</v>
+      </c>
+      <c r="D34" s="1">
+        <f t="shared" si="13"/>
+        <v>19.177811607936388</v>
+      </c>
+      <c r="E34" s="1">
+        <f t="shared" si="13"/>
+        <v>24.154664818152607</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35">
+        <f>1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="C35">
+        <f t="shared" ref="C35:E35" si="14">1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="14"/>
+        <v>1.57</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="14"/>
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="1">
+        <f>B34+B35</f>
+        <v>10.794105187503948</v>
+      </c>
+      <c r="C36" s="1">
+        <f t="shared" ref="C36:E36" si="15">C34+C35</f>
+        <v>15.770958397720166</v>
+      </c>
+      <c r="D36" s="1">
+        <f t="shared" si="15"/>
+        <v>20.747811607936388</v>
+      </c>
+      <c r="E36" s="1">
+        <f t="shared" si="15"/>
+        <v>25.724664818152608</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="2">
+        <f>B36*100</f>
+        <v>1079.4105187503949</v>
+      </c>
+      <c r="C37" s="2">
+        <f t="shared" ref="C37:E37" si="16">C36*100</f>
+        <v>1577.0958397720167</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" si="16"/>
+        <v>2074.7811607936387</v>
+      </c>
+      <c r="E37" s="2">
+        <f t="shared" si="16"/>
+        <v>2572.466481815261</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38">
+        <v>595</v>
+      </c>
+      <c r="C38">
+        <v>595</v>
+      </c>
+      <c r="D38">
+        <v>595</v>
+      </c>
+      <c r="E38">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="3">
+        <f>B37/B38-1</f>
+        <v>0.81413532563091584</v>
+      </c>
+      <c r="C39" s="3">
+        <f t="shared" ref="C39:E39" si="17">C37/C38-1</f>
+        <v>1.6505812433143139</v>
+      </c>
+      <c r="D39" s="3">
+        <f t="shared" si="17"/>
+        <v>2.4870271609977119</v>
+      </c>
+      <c r="E39" s="3">
+        <f t="shared" si="17"/>
+        <v>3.3234730786811113</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A23:E23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C948590-68A6-476D-B63A-653E4BD7F956}">
   <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
+++ b/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Value Investing\Zegona Communications Plc - ZEG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3EDDC8-54FB-4CC3-BE0D-333D4A978676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3036119C-23FC-4BA1-93EB-665D31F6C4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="7" activeTab="7" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="9" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
   </bookViews>
   <sheets>
     <sheet name="Dividendo parcial + Preferentes" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,9 @@
     <sheet name="Venta 2 FibreCos" sheetId="10" r:id="rId6"/>
     <sheet name="Venta 2 FibreCos + Reestructura" sheetId="11" r:id="rId7"/>
     <sheet name="FibreCo Ret Capital Allocation" sheetId="12" r:id="rId8"/>
-    <sheet name="Gabriel Castro" sheetId="7" r:id="rId9"/>
+    <sheet name="Resultados FY26 EV-EBITDAaL" sheetId="13" r:id="rId9"/>
+    <sheet name="Resultados FY26 EV-OpCF" sheetId="14" r:id="rId10"/>
+    <sheet name="Gabriel Castro" sheetId="7" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="50">
   <si>
     <t>EV/EBITDAaL</t>
   </si>
@@ -382,6 +384,44 @@
   <si>
     <t>Recompra de acciones (-)</t>
   </si>
+  <si>
+    <t>Número de acciones</t>
+  </si>
+  <si>
+    <r>
+      <t>Precio por acción (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>GBX</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>EV/OpCF</t>
+  </si>
+  <si>
+    <t>EBITDAaL 26</t>
+  </si>
+  <si>
+    <t>OpCF 26</t>
+  </si>
 </sst>
 </file>
 
@@ -446,7 +486,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -469,6 +509,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1700,6 +1743,1126 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FF6010C-99CD-479C-8139-EA6F317E2069}">
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="49.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2">
+        <f>10</f>
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <f>11</f>
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <f>12</f>
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <f>13</f>
+        <v>13</v>
+      </c>
+      <c r="F2">
+        <f>14</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3">
+        <f>763</f>
+        <v>763</v>
+      </c>
+      <c r="C3">
+        <f>763</f>
+        <v>763</v>
+      </c>
+      <c r="D3">
+        <f>763</f>
+        <v>763</v>
+      </c>
+      <c r="E3">
+        <f>763</f>
+        <v>763</v>
+      </c>
+      <c r="F3">
+        <f>763</f>
+        <v>763</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>B3*B2</f>
+        <v>7630</v>
+      </c>
+      <c r="C4">
+        <f>C3*C2</f>
+        <v>8393</v>
+      </c>
+      <c r="D4">
+        <f>D3*D2</f>
+        <v>9156</v>
+      </c>
+      <c r="E4">
+        <f>E3*E2</f>
+        <v>9919</v>
+      </c>
+      <c r="F4">
+        <f>F3*F2</f>
+        <v>10682</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <f>3733</f>
+        <v>3733</v>
+      </c>
+      <c r="C5">
+        <f>3733</f>
+        <v>3733</v>
+      </c>
+      <c r="D5">
+        <f>3733</f>
+        <v>3733</v>
+      </c>
+      <c r="E5">
+        <f>3733</f>
+        <v>3733</v>
+      </c>
+      <c r="F5">
+        <f>3733</f>
+        <v>3733</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6">
+        <f>519</f>
+        <v>519</v>
+      </c>
+      <c r="C6">
+        <f>519</f>
+        <v>519</v>
+      </c>
+      <c r="D6">
+        <f>519</f>
+        <v>519</v>
+      </c>
+      <c r="E6">
+        <f>519</f>
+        <v>519</v>
+      </c>
+      <c r="F6">
+        <f>519</f>
+        <v>519</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <f>B5-B6</f>
+        <v>3214</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:F7" si="0">C5-C6</f>
+        <v>3214</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>3214</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>3214</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>3214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8">
+        <f>B4-B7</f>
+        <v>4416</v>
+      </c>
+      <c r="C8">
+        <f>C4-C7</f>
+        <v>5179</v>
+      </c>
+      <c r="D8">
+        <f>D4-D7</f>
+        <v>5942</v>
+      </c>
+      <c r="E8">
+        <f>E4-E7</f>
+        <v>6705</v>
+      </c>
+      <c r="F8">
+        <f>F4-F7</f>
+        <v>7468</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="7">
+        <v>1250</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1250</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1250</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1250</v>
+      </c>
+      <c r="F10" s="7">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="9">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="9">
+        <f>B10-B11</f>
+        <v>1250</v>
+      </c>
+      <c r="C12" s="9">
+        <f>C10-C11</f>
+        <v>1250</v>
+      </c>
+      <c r="D12" s="9">
+        <f>D10-D11</f>
+        <v>1250</v>
+      </c>
+      <c r="E12" s="9">
+        <f>E10-E11</f>
+        <v>1250</v>
+      </c>
+      <c r="F12" s="9">
+        <f>F10-F11</f>
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+      <c r="C13" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+      <c r="D13" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+      <c r="E13" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+      <c r="F13" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="2">
+        <f>B13*B12</f>
+        <v>62.5</v>
+      </c>
+      <c r="C14" s="2">
+        <f t="shared" ref="C14:E14" si="1">C13*C12</f>
+        <v>62.5</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="1"/>
+        <v>62.5</v>
+      </c>
+      <c r="E14" s="2">
+        <f t="shared" si="1"/>
+        <v>62.5</v>
+      </c>
+      <c r="F14" s="2">
+        <f t="shared" ref="F14" si="2">F13*F12</f>
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="9">
+        <v>3640</v>
+      </c>
+      <c r="C16" s="9">
+        <v>3640</v>
+      </c>
+      <c r="D16" s="9">
+        <v>3640</v>
+      </c>
+      <c r="E16" s="9">
+        <v>3640</v>
+      </c>
+      <c r="F16" s="9">
+        <v>3641</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="8">
+        <f>17.5%</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="C17" s="8">
+        <f t="shared" ref="C17:F17" si="3">17.5%</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="D17" s="8">
+        <f t="shared" si="3"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="E17" s="8">
+        <f t="shared" si="3"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="F17" s="8">
+        <f t="shared" si="3"/>
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18">
+        <f>B17*B16</f>
+        <v>637</v>
+      </c>
+      <c r="C18">
+        <f t="shared" ref="C18:E18" si="4">C17*C16</f>
+        <v>637</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="4"/>
+        <v>637</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="4"/>
+        <v>637</v>
+      </c>
+      <c r="F18">
+        <f t="shared" ref="F18" si="5">F17*F16</f>
+        <v>637.17499999999995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="2">
+        <f>B8+B14+B18</f>
+        <v>5115.5</v>
+      </c>
+      <c r="C19" s="2">
+        <f>C8+C14+C18</f>
+        <v>5878.5</v>
+      </c>
+      <c r="D19" s="2">
+        <f>D8+D14+D18</f>
+        <v>6641.5</v>
+      </c>
+      <c r="E19" s="2">
+        <f>E8+E14+E18</f>
+        <v>7404.5</v>
+      </c>
+      <c r="F19" s="2">
+        <f>F8+F14+F18</f>
+        <v>8167.6750000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="2">
+        <f>225713802/1000000</f>
+        <v>225.71380199999999</v>
+      </c>
+      <c r="C20" s="2">
+        <f t="shared" ref="C20:F20" si="6">225713802/1000000</f>
+        <v>225.71380199999999</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" si="6"/>
+        <v>225.71380199999999</v>
+      </c>
+      <c r="E20" s="2">
+        <f t="shared" si="6"/>
+        <v>225.71380199999999</v>
+      </c>
+      <c r="F20" s="2">
+        <f t="shared" si="6"/>
+        <v>225.71380199999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="1">
+        <f>B19/B20</f>
+        <v>22.663656164012515</v>
+      </c>
+      <c r="C21" s="1">
+        <f>C19/C20</f>
+        <v>26.044043155145648</v>
+      </c>
+      <c r="D21" s="1">
+        <f>D19/D20</f>
+        <v>29.424430146278784</v>
+      </c>
+      <c r="E21" s="1">
+        <f>E19/E20</f>
+        <v>32.804817137411916</v>
+      </c>
+      <c r="F21" s="1">
+        <f>F19/F20</f>
+        <v>36.185979446662287</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22">
+        <f>1.17</f>
+        <v>1.17</v>
+      </c>
+      <c r="C22">
+        <f t="shared" ref="C22:F22" si="7">1.17</f>
+        <v>1.17</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="7"/>
+        <v>1.17</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="7"/>
+        <v>1.17</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="7"/>
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1">
+        <f>B21/B22</f>
+        <v>19.370646294027793</v>
+      </c>
+      <c r="C23" s="1">
+        <f t="shared" ref="C23:E23" si="8">C21/C22</f>
+        <v>22.259865944568929</v>
+      </c>
+      <c r="D23" s="1">
+        <f t="shared" si="8"/>
+        <v>25.149085595110073</v>
+      </c>
+      <c r="E23" s="1">
+        <f t="shared" si="8"/>
+        <v>28.038305245651213</v>
+      </c>
+      <c r="F23" s="1">
+        <f t="shared" ref="F23" si="9">F21/F22</f>
+        <v>30.928187561249821</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="2">
+        <f>B23*100</f>
+        <v>1937.0646294027792</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" ref="C24:F24" si="10">C23*100</f>
+        <v>2225.9865944568928</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="10"/>
+        <v>2514.9085595110073</v>
+      </c>
+      <c r="E24" s="2">
+        <f t="shared" si="10"/>
+        <v>2803.8305245651213</v>
+      </c>
+      <c r="F24" s="2">
+        <f t="shared" si="10"/>
+        <v>3092.818756124982</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25">
+        <f>595</f>
+        <v>595</v>
+      </c>
+      <c r="C25">
+        <f>595</f>
+        <v>595</v>
+      </c>
+      <c r="D25">
+        <f>595</f>
+        <v>595</v>
+      </c>
+      <c r="E25">
+        <f>595</f>
+        <v>595</v>
+      </c>
+      <c r="F25">
+        <f>595</f>
+        <v>595</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="3">
+        <f>B24/B25-1</f>
+        <v>2.2555708057189565</v>
+      </c>
+      <c r="C26" s="3">
+        <f t="shared" ref="C26:E26" si="11">C24/C25-1</f>
+        <v>2.7411539402636853</v>
+      </c>
+      <c r="D26" s="3">
+        <f t="shared" si="11"/>
+        <v>3.2267370748084154</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="11"/>
+        <v>3.7123202093531447</v>
+      </c>
+      <c r="F26" s="3">
+        <f t="shared" ref="F26" si="12">F24/F25-1</f>
+        <v>4.1980147161764405</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C948590-68A6-476D-B63A-653E4BD7F956}">
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>4</v>
+      </c>
+      <c r="C1">
+        <v>5</v>
+      </c>
+      <c r="D1">
+        <v>6</v>
+      </c>
+      <c r="E1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>1300</f>
+        <v>1300</v>
+      </c>
+      <c r="C2">
+        <f>1300</f>
+        <v>1300</v>
+      </c>
+      <c r="D2">
+        <f>1300</f>
+        <v>1300</v>
+      </c>
+      <c r="E2">
+        <f>1300</f>
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <f>-50</f>
+        <v>-50</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:E4" si="0">-50</f>
+        <v>-50</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="0"/>
+        <v>-50</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="0"/>
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <f>-50</f>
+        <v>-50</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>-50</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>-50</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <f>SUM(B2:B4)</f>
+        <v>1200</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ref="C5:E5" si="1">SUM(C2:C4)</f>
+        <v>1200</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>1200</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <f>B5*B1</f>
+        <v>4800</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:E6" si="2">C5*C1</f>
+        <v>6000</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="2"/>
+        <v>7200</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="2"/>
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="C7">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="D7">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+      <c r="E7">
+        <f>3800</f>
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="C8">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="D8">
+        <f>260</f>
+        <v>260</v>
+      </c>
+      <c r="E8">
+        <f>260</f>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="C9">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="D9">
+        <f>538</f>
+        <v>538</v>
+      </c>
+      <c r="E9">
+        <f>538</f>
+        <v>538</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10">
+        <f>1776</f>
+        <v>1776</v>
+      </c>
+      <c r="C10">
+        <f>1776</f>
+        <v>1776</v>
+      </c>
+      <c r="D10">
+        <f>1776</f>
+        <v>1776</v>
+      </c>
+      <c r="E10">
+        <f>1776</f>
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="C11">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="D11">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+      <c r="E11">
+        <f>1405</f>
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <f>B7-B8-B9-B10+B11</f>
+        <v>2631</v>
+      </c>
+      <c r="C12">
+        <f t="shared" ref="C12:E12" si="3">C7-C8-C9-C10+C11</f>
+        <v>2631</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="3"/>
+        <v>2631</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="3"/>
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <f>B6-B12</f>
+        <v>2169</v>
+      </c>
+      <c r="C13">
+        <f t="shared" ref="C13:E13" si="4">C6-C12</f>
+        <v>3369</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="4"/>
+        <v>4569</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="4"/>
+        <v>5769</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="2">
+        <f>759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="C14" s="2">
+        <f t="shared" ref="C14:E14" si="5">759209905/1000000</f>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="5"/>
+        <v>759.20990500000005</v>
+      </c>
+      <c r="E14" s="2">
+        <f t="shared" si="5"/>
+        <v>759.20990500000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="2">
+        <f>523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="C15" s="2">
+        <f t="shared" ref="C15:E15" si="6">523240603/1000000</f>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="6"/>
+        <v>523.24060299999996</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" si="6"/>
+        <v>523.24060299999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="2">
+        <f>B14-B15</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="C16" s="2">
+        <f t="shared" ref="C16:E16" si="7">C14-C15</f>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="7"/>
+        <v>235.96930200000008</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="7"/>
+        <v>235.96930200000008</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="1">
+        <f>B13/B16</f>
+        <v>9.1918736107461942</v>
+      </c>
+      <c r="C17" s="1">
+        <f t="shared" ref="C17:E17" si="8">C13/C16</f>
+        <v>14.277280864271059</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" si="8"/>
+        <v>19.362688117795926</v>
+      </c>
+      <c r="E17" s="1">
+        <f t="shared" si="8"/>
+        <v>24.44809537132079</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18">
+        <f>1.2</f>
+        <v>1.2</v>
+      </c>
+      <c r="C18">
+        <f t="shared" ref="C18:E18" si="9">1.2</f>
+        <v>1.2</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="9"/>
+        <v>1.2</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="9"/>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="1">
+        <f>B17/B18</f>
+        <v>7.6598946756218291</v>
+      </c>
+      <c r="C19" s="1">
+        <f t="shared" ref="C19:E19" si="10">C17/C18</f>
+        <v>11.897734053559217</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="10"/>
+        <v>16.135573431496606</v>
+      </c>
+      <c r="E19" s="1">
+        <f t="shared" si="10"/>
+        <v>20.373412809433994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <f>1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="C20">
+        <f t="shared" ref="C20:E20" si="11">1.57</f>
+        <v>1.57</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="11"/>
+        <v>1.57</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="11"/>
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1">
+        <f>B19+B20</f>
+        <v>9.2298946756218285</v>
+      </c>
+      <c r="C21" s="1">
+        <f t="shared" ref="C21:E21" si="12">C19+C20</f>
+        <v>13.467734053559218</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" si="12"/>
+        <v>17.705573431496607</v>
+      </c>
+      <c r="E21" s="1">
+        <f t="shared" si="12"/>
+        <v>21.943412809433994</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <f>B21*100</f>
+        <v>922.98946756218288</v>
+      </c>
+      <c r="C22" s="2">
+        <f t="shared" ref="C22:E22" si="13">C21*100</f>
+        <v>1346.7734053559218</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="13"/>
+        <v>1770.5573431496607</v>
+      </c>
+      <c r="E22" s="2">
+        <f t="shared" si="13"/>
+        <v>2194.3412809433994</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23">
+        <v>595</v>
+      </c>
+      <c r="C23">
+        <v>595</v>
+      </c>
+      <c r="D23">
+        <v>595</v>
+      </c>
+      <c r="E23">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="3">
+        <f>B22/B23-1</f>
+        <v>0.55124280262551739</v>
+      </c>
+      <c r="C24" s="3">
+        <f t="shared" ref="C24:E24" si="14">C22/C23-1</f>
+        <v>1.2634847148839023</v>
+      </c>
+      <c r="D24" s="3">
+        <f t="shared" si="14"/>
+        <v>1.9757266271422869</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" si="14"/>
+        <v>2.6879685394006714</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FC67936-1270-4D10-AE0F-8072EC119D20}">
   <dimension ref="A1:E45"/>
@@ -7056,7 +8219,7 @@
         <v>523.24060299999996</v>
       </c>
       <c r="C29" s="2">
-        <f t="shared" ref="C29:E30" si="8">523240603/1000000</f>
+        <f t="shared" ref="C29:E29" si="8">523240603/1000000</f>
         <v>523.24060299999996</v>
       </c>
       <c r="D29" s="2">
@@ -7286,512 +8449,540 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C948590-68A6-476D-B63A-653E4BD7F956}">
-  <dimension ref="A1:E24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC14BCD5-8FB7-42A8-A809-865887FCF150}">
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
+      <c r="B2">
         <v>4</v>
       </c>
-      <c r="C1">
+      <c r="C2">
         <v>5</v>
       </c>
-      <c r="D1">
+      <c r="D2">
         <v>6</v>
       </c>
-      <c r="E1">
+      <c r="E2">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <f>1300</f>
-        <v>1300</v>
-      </c>
-      <c r="C2">
-        <f>1300</f>
-        <v>1300</v>
-      </c>
-      <c r="D2">
-        <f>1300</f>
-        <v>1300</v>
-      </c>
-      <c r="E2">
-        <f>1300</f>
-        <v>1300</v>
-      </c>
-    </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
+      <c r="A3" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="B3">
-        <f>-50</f>
-        <v>-50</v>
+        <f>1341</f>
+        <v>1341</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:E4" si="0">-50</f>
-        <v>-50</v>
+        <f>1341</f>
+        <v>1341</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
-        <v>-50</v>
+        <f>1341</f>
+        <v>1341</v>
       </c>
       <c r="E3">
-        <f t="shared" si="0"/>
-        <v>-50</v>
+        <f>1341</f>
+        <v>1341</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
+      <c r="A4" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="B4">
-        <f>-50</f>
-        <v>-50</v>
+        <f>B3*B2</f>
+        <v>5364</v>
       </c>
       <c r="C4">
-        <f t="shared" si="0"/>
-        <v>-50</v>
+        <f>C3*C2</f>
+        <v>6705</v>
       </c>
       <c r="D4">
-        <f t="shared" si="0"/>
-        <v>-50</v>
+        <f>D3*D2</f>
+        <v>8046</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
-        <v>-50</v>
+        <f>E3*E2</f>
+        <v>9387</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5">
-        <f>SUM(B2:B4)</f>
-        <v>1200</v>
-      </c>
-      <c r="C5">
-        <f t="shared" ref="C5:E5" si="1">SUM(C2:C4)</f>
-        <v>1200</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="1"/>
-        <v>1200</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>42</v>
+      </c>
+      <c r="B5" s="2">
+        <f>3.1*B3</f>
+        <v>4157.1000000000004</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" ref="C5:E5" si="0">3.1*C3</f>
+        <v>4157.1000000000004</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="0"/>
+        <v>4157.1000000000004</v>
+      </c>
+      <c r="E5" s="2">
+        <f t="shared" si="0"/>
+        <v>4157.1000000000004</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>2</v>
+      <c r="A6" t="s">
+        <v>3</v>
       </c>
       <c r="B6">
-        <f>B5*B1</f>
-        <v>4800</v>
+        <f>3733</f>
+        <v>3733</v>
       </c>
       <c r="C6">
-        <f t="shared" ref="C6:E6" si="2">C5*C1</f>
-        <v>6000</v>
+        <f>3733</f>
+        <v>3733</v>
       </c>
       <c r="D6">
-        <f t="shared" si="2"/>
-        <v>7200</v>
+        <f>3733</f>
+        <v>3733</v>
       </c>
       <c r="E6">
-        <f t="shared" si="2"/>
-        <v>8400</v>
+        <f>3733</f>
+        <v>3733</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B7">
-        <f>3800</f>
-        <v>3800</v>
+        <f>519</f>
+        <v>519</v>
       </c>
       <c r="C7">
-        <f>3800</f>
-        <v>3800</v>
+        <f>519</f>
+        <v>519</v>
       </c>
       <c r="D7">
-        <f>3800</f>
-        <v>3800</v>
+        <f>519</f>
+        <v>519</v>
       </c>
       <c r="E7">
-        <f>3800</f>
-        <v>3800</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>24</v>
+        <f>519</f>
+        <v>519</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="B8">
-        <f>260</f>
-        <v>260</v>
+        <f>B6-B7</f>
+        <v>3214</v>
       </c>
       <c r="C8">
-        <f>260</f>
-        <v>260</v>
+        <f t="shared" ref="C8:E8" si="1">C6-C7</f>
+        <v>3214</v>
       </c>
       <c r="D8">
-        <f>260</f>
-        <v>260</v>
+        <f t="shared" si="1"/>
+        <v>3214</v>
       </c>
       <c r="E8">
-        <f>260</f>
-        <v>260</v>
+        <f t="shared" si="1"/>
+        <v>3214</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>25</v>
+      <c r="A9" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="B9">
-        <f>538</f>
-        <v>538</v>
+        <f>B4-B8</f>
+        <v>2150</v>
       </c>
       <c r="C9">
-        <f>538</f>
-        <v>538</v>
+        <f>C4-C8</f>
+        <v>3491</v>
       </c>
       <c r="D9">
-        <f>538</f>
-        <v>538</v>
+        <f>D4-D8</f>
+        <v>4832</v>
       </c>
       <c r="E9">
-        <f>538</f>
-        <v>538</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-      <c r="C10">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-      <c r="D10">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-      <c r="E10">
-        <f>1776</f>
-        <v>1776</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <f>1405</f>
-        <v>1405</v>
-      </c>
-      <c r="C11">
-        <f>1405</f>
-        <v>1405</v>
-      </c>
-      <c r="D11">
-        <f>1405</f>
-        <v>1405</v>
-      </c>
-      <c r="E11">
-        <f>1405</f>
-        <v>1405</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12">
-        <f>B7-B8-B9-B10+B11</f>
-        <v>2631</v>
-      </c>
-      <c r="C12">
-        <f t="shared" ref="C12:E12" si="3">C7-C8-C9-C10+C11</f>
-        <v>2631</v>
-      </c>
-      <c r="D12">
+        <f>E4-E8</f>
+        <v>6173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+    </row>
+    <row r="11" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="7">
+        <v>1250</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7">
+        <f t="shared" ref="D11:E11" si="2">D11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="9">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="9">
+        <f>B11-B12</f>
+        <v>1250</v>
+      </c>
+      <c r="C13" s="9">
+        <f>C11-C12</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="9">
+        <f>D11-D12</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="9">
+        <f>E11-E12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+      <c r="C14" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+      <c r="D14" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+      <c r="E14" s="8">
+        <f>5%</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="2">
+        <f>B14*B13</f>
+        <v>62.5</v>
+      </c>
+      <c r="C15" s="2">
+        <f t="shared" ref="C15:E15" si="3">C14*C13</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
         <f t="shared" si="3"/>
-        <v>2631</v>
-      </c>
-      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
         <f t="shared" si="3"/>
-        <v>2631</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B13">
-        <f>B6-B12</f>
-        <v>2169</v>
-      </c>
-      <c r="C13">
-        <f t="shared" ref="C13:E13" si="4">C6-C12</f>
-        <v>3369</v>
-      </c>
-      <c r="D13">
+      <c r="B17" s="9">
+        <v>3640</v>
+      </c>
+      <c r="C17" s="9">
+        <f>B17</f>
+        <v>3640</v>
+      </c>
+      <c r="D17" s="9">
+        <f t="shared" ref="D17:E17" si="4">C17</f>
+        <v>3640</v>
+      </c>
+      <c r="E17" s="9">
         <f t="shared" si="4"/>
-        <v>4569</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="4"/>
-        <v>5769</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="2">
-        <f>759209905/1000000</f>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="C14" s="2">
-        <f t="shared" ref="C14:E14" si="5">759209905/1000000</f>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="D14" s="2">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="8">
+        <f>17.5%</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="C18" s="8">
+        <f t="shared" ref="C18:E18" si="5">17.5%</f>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="D18" s="8">
         <f t="shared" si="5"/>
-        <v>759.20990500000005</v>
-      </c>
-      <c r="E14" s="2">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="E18" s="8">
         <f t="shared" si="5"/>
-        <v>759.20990500000005</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="2">
-        <f>523240603/1000000</f>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="C15" s="2">
-        <f t="shared" ref="C15:E15" si="6">523240603/1000000</f>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="D15" s="2">
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19">
+        <f>B18*B17</f>
+        <v>637</v>
+      </c>
+      <c r="C19">
+        <f t="shared" ref="C19:E19" si="6">C18*C17</f>
+        <v>637</v>
+      </c>
+      <c r="D19">
         <f t="shared" si="6"/>
-        <v>523.24060299999996</v>
-      </c>
-      <c r="E15" s="2">
+        <v>637</v>
+      </c>
+      <c r="E19">
         <f t="shared" si="6"/>
-        <v>523.24060299999996</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2">
-        <f>B14-B15</f>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="C16" s="2">
-        <f t="shared" ref="C16:E16" si="7">C14-C15</f>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="D16" s="2">
-        <f t="shared" si="7"/>
-        <v>235.96930200000008</v>
-      </c>
-      <c r="E16" s="2">
-        <f t="shared" si="7"/>
-        <v>235.96930200000008</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="1">
-        <f>B13/B16</f>
-        <v>9.1918736107461942</v>
-      </c>
-      <c r="C17" s="1">
-        <f t="shared" ref="C17:E17" si="8">C13/C16</f>
-        <v>14.277280864271059</v>
-      </c>
-      <c r="D17" s="1">
-        <f t="shared" si="8"/>
-        <v>19.362688117795926</v>
-      </c>
-      <c r="E17" s="1">
-        <f t="shared" si="8"/>
-        <v>24.44809537132079</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18">
-        <f>1.2</f>
-        <v>1.2</v>
-      </c>
-      <c r="C18">
-        <f t="shared" ref="C18:E18" si="9">1.2</f>
-        <v>1.2</v>
-      </c>
-      <c r="D18">
-        <f t="shared" si="9"/>
-        <v>1.2</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="9"/>
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="1">
-        <f>B17/B18</f>
-        <v>7.6598946756218291</v>
-      </c>
-      <c r="C19" s="1">
-        <f t="shared" ref="C19:E19" si="10">C17/C18</f>
-        <v>11.897734053559217</v>
-      </c>
-      <c r="D19" s="1">
-        <f t="shared" si="10"/>
-        <v>16.135573431496606</v>
-      </c>
-      <c r="E19" s="1">
-        <f t="shared" si="10"/>
-        <v>20.373412809433994</v>
+        <v>637</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20">
-        <f>1.57</f>
-        <v>1.57</v>
-      </c>
-      <c r="C20">
-        <f t="shared" ref="C20:E20" si="11">1.57</f>
-        <v>1.57</v>
-      </c>
-      <c r="D20">
-        <f t="shared" si="11"/>
-        <v>1.57</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="11"/>
-        <v>1.57</v>
+      <c r="A20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="2">
+        <f>B9+B15+B19</f>
+        <v>2849.5</v>
+      </c>
+      <c r="C20" s="2">
+        <f>C9+C15+C19</f>
+        <v>4128</v>
+      </c>
+      <c r="D20" s="2">
+        <f>D9+D15+D19</f>
+        <v>5469</v>
+      </c>
+      <c r="E20" s="2">
+        <f>E9+E15+E19</f>
+        <v>6810</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="1">
-        <f>B19+B20</f>
-        <v>9.2298946756218285</v>
-      </c>
-      <c r="C21" s="1">
-        <f t="shared" ref="C21:E21" si="12">C19+C20</f>
-        <v>13.467734053559218</v>
-      </c>
-      <c r="D21" s="1">
-        <f t="shared" si="12"/>
-        <v>17.705573431496607</v>
-      </c>
-      <c r="E21" s="1">
-        <f t="shared" si="12"/>
-        <v>21.943412809433994</v>
+        <v>45</v>
+      </c>
+      <c r="B21" s="2">
+        <f>225713802/1000000</f>
+        <v>225.71380199999999</v>
+      </c>
+      <c r="C21" s="2">
+        <f t="shared" ref="C21:E21" si="7">225713802/1000000</f>
+        <v>225.71380199999999</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="7"/>
+        <v>225.71380199999999</v>
+      </c>
+      <c r="E21" s="2">
+        <f t="shared" si="7"/>
+        <v>225.71380199999999</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2">
-        <f>B21*100</f>
-        <v>922.98946756218288</v>
-      </c>
-      <c r="C22" s="2">
-        <f t="shared" ref="C22:E22" si="13">C21*100</f>
-        <v>1346.7734053559218</v>
-      </c>
-      <c r="D22" s="2">
-        <f t="shared" si="13"/>
-        <v>1770.5573431496607</v>
-      </c>
-      <c r="E22" s="2">
-        <f t="shared" si="13"/>
-        <v>2194.3412809433994</v>
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1">
+        <f>B20/B21</f>
+        <v>12.624394143163652</v>
+      </c>
+      <c r="C22" s="1">
+        <f>C20/C21</f>
+        <v>18.288646788201284</v>
+      </c>
+      <c r="D22" s="1">
+        <f>D20/D21</f>
+        <v>24.229798760821904</v>
+      </c>
+      <c r="E22" s="1">
+        <f>E20/E21</f>
+        <v>30.170950733442524</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23">
+        <f>1.17</f>
+        <v>1.17</v>
+      </c>
+      <c r="C23">
+        <f t="shared" ref="C23:E23" si="8">1.17</f>
+        <v>1.17</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="8"/>
+        <v>1.17</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="8"/>
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="1">
+        <f>B22/B23</f>
+        <v>10.790080464242438</v>
+      </c>
+      <c r="C24" s="1">
+        <f t="shared" ref="C24:E24" si="9">C22/C23</f>
+        <v>15.631322041197679</v>
+      </c>
+      <c r="D24" s="1">
+        <f t="shared" si="9"/>
+        <v>20.709229710104193</v>
+      </c>
+      <c r="E24" s="1">
+        <f t="shared" si="9"/>
+        <v>25.787137379010705</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="2">
+        <f>B24*100</f>
+        <v>1079.0080464242437</v>
+      </c>
+      <c r="C25" s="2">
+        <f t="shared" ref="C25:E25" si="10">C24*100</f>
+        <v>1563.1322041197679</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="10"/>
+        <v>2070.9229710104191</v>
+      </c>
+      <c r="E25" s="2">
+        <f t="shared" si="10"/>
+        <v>2578.7137379010705</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B23">
+      <c r="B26">
+        <f>595</f>
         <v>595</v>
       </c>
-      <c r="C23">
+      <c r="C26">
+        <f>595</f>
         <v>595</v>
       </c>
-      <c r="D23">
+      <c r="D26">
+        <f>595</f>
         <v>595</v>
       </c>
-      <c r="E23">
+      <c r="E26">
+        <f>595</f>
         <v>595</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="3">
-        <f>B22/B23-1</f>
-        <v>0.55124280262551739</v>
-      </c>
-      <c r="C24" s="3">
-        <f t="shared" ref="C24:E24" si="14">C22/C23-1</f>
-        <v>1.2634847148839023</v>
-      </c>
-      <c r="D24" s="3">
-        <f t="shared" si="14"/>
-        <v>1.9757266271422869</v>
-      </c>
-      <c r="E24" s="3">
-        <f t="shared" si="14"/>
-        <v>2.6879685394006714</v>
+      <c r="B27" s="3">
+        <f>B25/B26-1</f>
+        <v>0.81345890155335088</v>
+      </c>
+      <c r="C27" s="3">
+        <f t="shared" ref="C27:E27" si="11">C25/C26-1</f>
+        <v>1.6271129481004505</v>
+      </c>
+      <c r="D27" s="3">
+        <f t="shared" si="11"/>
+        <v>2.4805428084208727</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" si="11"/>
+        <v>3.3339726687412954</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A16:E16"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
+++ b/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Value Investing\Zegona Communications Plc - ZEG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3036119C-23FC-4BA1-93EB-665D31F6C4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEE3FB3-FE58-4C0B-BE6A-53B870C366A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="9" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="8" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
   </bookViews>
   <sheets>
     <sheet name="Dividendo parcial + Preferentes" sheetId="2" r:id="rId1"/>
@@ -508,10 +508,10 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -856,13 +856,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1151,13 +1151,13 @@
       </c>
     </row>
     <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
@@ -1320,13 +1320,13 @@
       </c>
     </row>
     <row r="25" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
@@ -1754,13 +1754,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1938,14 +1939,14 @@
       </c>
     </row>
     <row r="9" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
@@ -2063,13 +2064,13 @@
       </c>
     </row>
     <row r="15" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
@@ -2343,8 +2344,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2874,13 +2875,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -3169,13 +3170,13 @@
       </c>
     </row>
     <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
@@ -3338,13 +3339,13 @@
       </c>
     </row>
     <row r="25" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
@@ -3776,13 +3777,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -4088,13 +4089,13 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
@@ -4257,13 +4258,13 @@
       </c>
     </row>
     <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
@@ -4695,13 +4696,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -4961,13 +4962,13 @@
       </c>
     </row>
     <row r="15" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
@@ -5130,13 +5131,13 @@
       </c>
     </row>
     <row r="24" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
@@ -5467,13 +5468,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5750,13 +5751,13 @@
       </c>
     </row>
     <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
@@ -5919,13 +5920,13 @@
       </c>
     </row>
     <row r="25" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
@@ -6256,13 +6257,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -6522,13 +6523,13 @@
       </c>
     </row>
     <row r="15" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
@@ -6628,13 +6629,13 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
@@ -6965,13 +6966,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -7248,13 +7249,13 @@
       </c>
     </row>
     <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
@@ -7354,13 +7355,13 @@
       </c>
     </row>
     <row r="22" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
@@ -7691,13 +7692,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -7995,13 +7996,13 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
@@ -8101,13 +8102,13 @@
       </c>
     </row>
     <row r="23" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -8459,13 +8460,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -8632,13 +8633,13 @@
       </c>
     </row>
     <row r="10" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
     </row>
     <row r="11" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
@@ -8654,7 +8655,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="7">
-        <f t="shared" ref="D11:E11" si="2">D11</f>
+        <f t="shared" ref="E11" si="2">D11</f>
         <v>0</v>
       </c>
     </row>
@@ -8739,13 +8740,13 @@
       </c>
     </row>
     <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
